--- a/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2318.4</v>
+        <v>27725.4</v>
       </c>
       <c r="C4" t="n">
-        <v>593712</v>
+        <v>5364072</v>
       </c>
       <c r="D4" t="n">
-        <v>466488</v>
+        <v>4214628</v>
       </c>
       <c r="E4" t="n">
-        <v>150300</v>
+        <v>1481400</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>6570</v>
+        <v>81150</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>8910</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>20250</v>
+        <v>192690</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3878.82</v>
+        <v>28839.42</v>
       </c>
       <c r="C5" t="n">
-        <v>684432</v>
+        <v>4562712</v>
       </c>
       <c r="D5" t="n">
-        <v>537768</v>
+        <v>3584988</v>
       </c>
       <c r="E5" t="n">
-        <v>120600</v>
+        <v>1051200</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>8700</v>
+        <v>83460</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>7440</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20730</v>
+        <v>186450</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4027.14</v>
+        <v>34689.96</v>
       </c>
       <c r="C6" t="n">
-        <v>425880</v>
+        <v>4920552</v>
       </c>
       <c r="D6" t="n">
-        <v>334620</v>
+        <v>3866148</v>
       </c>
       <c r="E6" t="n">
-        <v>65700</v>
+        <v>932400</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>8310</v>
+        <v>86190</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>12180</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>23220</v>
+        <v>208890</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2670.57</v>
+        <v>28669.41</v>
       </c>
       <c r="C7" t="n">
-        <v>225792</v>
+        <v>2518488</v>
       </c>
       <c r="D7" t="n">
-        <v>177408</v>
+        <v>1978812</v>
       </c>
       <c r="E7" t="n">
-        <v>37800</v>
+        <v>295200</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>4740</v>
+        <v>66240</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10410</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1389.24</v>
+        <v>23511.33</v>
       </c>
       <c r="C8" t="n">
-        <v>75600</v>
+        <v>1760976</v>
       </c>
       <c r="D8" t="n">
-        <v>59400</v>
+        <v>1383624</v>
       </c>
       <c r="E8" t="n">
-        <v>12600</v>
+        <v>150300</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2160</v>
+        <v>35550</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3990</v>
+        <v>84780</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>663.5700000000001</v>
+        <v>15232.5</v>
       </c>
       <c r="C9" t="n">
-        <v>19656</v>
+        <v>983304</v>
       </c>
       <c r="D9" t="n">
-        <v>15444</v>
+        <v>772596</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>55800</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>810</v>
+        <v>28230</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10057,13 +10051,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>810</v>
+        <v>43950</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>394.38</v>
+        <v>2215.98</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>154224</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>121176</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>3090</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>600</v>
+        <v>11940</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>230.13</v>
+        <v>398.43</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>51408</v>
       </c>
       <c r="D11" t="n">
-        <v>1980</v>
+        <v>40392</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>1320</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.77</v>
+        <v>191.97</v>
       </c>
       <c r="C12" t="n">
-        <v>1512</v>
+        <v>11592</v>
       </c>
       <c r="D12" t="n">
-        <v>1188</v>
+        <v>9108</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>120</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>159.66</v>
+        <v>136.62</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>65.06999999999999</v>
+        <v>13.95</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2520</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1980</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>990</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.95</v>
+        <v>17.1</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>11.16</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>5.31</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.35</v>
+        <v>2.97</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19">
@@ -10416,10 +10410,10 @@
         <v>0.18</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1745.47</v>
+        <v>12977.74</v>
       </c>
       <c r="C5" t="n">
-        <v>376437.6</v>
+        <v>2509491.6</v>
       </c>
       <c r="D5" t="n">
-        <v>178001.21</v>
+        <v>1186631.03</v>
       </c>
       <c r="E5" t="n">
-        <v>13302.18</v>
+        <v>115947.36</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06</v>
+        <v>0.42</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2678.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4353.3</v>
+        <v>39154.5</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3221.71</v>
+        <v>27751.97</v>
       </c>
       <c r="C6" t="n">
-        <v>383292</v>
+        <v>4428496.8</v>
       </c>
       <c r="D6" t="n">
-        <v>169652.34</v>
+        <v>1960137.04</v>
       </c>
       <c r="E6" t="n">
-        <v>11103.3</v>
+        <v>157575.6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>415.5</v>
+        <v>4309.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6942.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8591.4</v>
+        <v>77289.3</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2537.04</v>
+        <v>27235.94</v>
       </c>
       <c r="C7" t="n">
-        <v>225792</v>
+        <v>2518488</v>
       </c>
       <c r="D7" t="n">
-        <v>113186.3</v>
+        <v>1262482.06</v>
       </c>
       <c r="E7" t="n">
-        <v>8040.06</v>
+        <v>62789.04</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>711</v>
+        <v>9936</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3285</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6246</v>
+        <v>85860</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1389.24</v>
+        <v>23511.33</v>
       </c>
       <c r="C8" t="n">
-        <v>75600</v>
+        <v>1760976</v>
       </c>
       <c r="D8" t="n">
-        <v>43718.4</v>
+        <v>1018347.26</v>
       </c>
       <c r="E8" t="n">
-        <v>3090.78</v>
+        <v>36868.59</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1404</v>
+        <v>23107.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2832.9</v>
+        <v>60193.8</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>663.5700000000001</v>
+        <v>15232.5</v>
       </c>
       <c r="C9" t="n">
-        <v>19656</v>
+        <v>983304</v>
       </c>
       <c r="D9" t="n">
-        <v>12401.53</v>
+        <v>620394.59</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>14937.66</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>688.5</v>
+        <v>23995.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11921,13 +11915,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>656.1</v>
+        <v>35599.5</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>394.38</v>
+        <v>2215.98</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>154224</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>105423.12</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2610</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>3090</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>534</v>
+        <v>10626.6</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>230.13</v>
+        <v>398.43</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>51408</v>
       </c>
       <c r="D11" t="n">
-        <v>1779.03</v>
+        <v>36292.21</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>368.82</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>1320</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.77</v>
+        <v>191.97</v>
       </c>
       <c r="C12" t="n">
-        <v>1512</v>
+        <v>11592</v>
       </c>
       <c r="D12" t="n">
-        <v>1101.28</v>
+        <v>8443.120000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>120</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>159.66</v>
+        <v>136.62</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2632.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>65.06999999999999</v>
+        <v>13.95</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2520</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1924.56</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>990</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.95</v>
+        <v>17.1</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1171.37</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>11.16</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>5.31</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.35</v>
+        <v>2.97</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19">
@@ -12280,10 +12274,10 @@
         <v>0.18</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3720</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3840031.8</v>
+        <v>28551025.8</v>
       </c>
       <c r="C5" t="n">
-        <v>20704068</v>
+        <v>138022038</v>
       </c>
       <c r="D5" t="n">
-        <v>18036862.41</v>
+        <v>120241322.07</v>
       </c>
       <c r="E5" t="n">
-        <v>2450793.64</v>
+        <v>21362141.61</v>
       </c>
       <c r="F5" t="n">
-        <v>2500.02</v>
+        <v>17500.14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>740979.36</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>192498.9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>41008.09</v>
+        <v>368835.39</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7087766.4</v>
+        <v>61054329.6</v>
       </c>
       <c r="C6" t="n">
-        <v>21081060</v>
+        <v>243567324</v>
       </c>
       <c r="D6" t="n">
-        <v>17190871.61</v>
+        <v>198620685.86</v>
       </c>
       <c r="E6" t="n">
-        <v>2045671.99</v>
+        <v>29031728.54</v>
       </c>
       <c r="F6" t="n">
-        <v>25000.2</v>
+        <v>12500.1</v>
       </c>
       <c r="G6" t="n">
-        <v>7686.75</v>
+        <v>79725.75</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1920670.29</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>58333</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>80930.99000000001</v>
+        <v>728065.21</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5581491.3</v>
+        <v>59919066.9</v>
       </c>
       <c r="C7" t="n">
-        <v>12418560</v>
+        <v>138516840</v>
       </c>
       <c r="D7" t="n">
-        <v>11469168.18</v>
+        <v>127927306.73</v>
       </c>
       <c r="E7" t="n">
-        <v>1481300.65</v>
+        <v>11568252.73</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>13153.5</v>
+        <v>183816</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>908795.25</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>58837.32</v>
+        <v>808801.2</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3056328</v>
+        <v>51724926</v>
       </c>
       <c r="C8" t="n">
-        <v>4158000</v>
+        <v>96853680</v>
       </c>
       <c r="D8" t="n">
-        <v>4429985.47</v>
+        <v>103189128.26</v>
       </c>
       <c r="E8" t="n">
-        <v>569445.3100000001</v>
+        <v>6792669.02</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>25974</v>
+        <v>427488.75</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>141091.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>49583.05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26685.92</v>
+        <v>567025.6</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1459854</v>
+        <v>33511500</v>
       </c>
       <c r="C9" t="n">
-        <v>1081080</v>
+        <v>54081720</v>
       </c>
       <c r="D9" t="n">
-        <v>1256647.24</v>
+        <v>62864583.6</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>2752114.48</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>12737.25</v>
+        <v>443916.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12853,13 +12847,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>110832.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6180.46</v>
+        <v>335347.29</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>867636</v>
+        <v>4875156</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>8482320</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>10682524.75</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>480866.4</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7770</v>
+        <v>57165</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5030.28</v>
+        <v>100102.57</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>506286</v>
+        <v>876546</v>
       </c>
       <c r="C11" t="n">
-        <v>138600</v>
+        <v>2827440</v>
       </c>
       <c r="D11" t="n">
-        <v>180269.11</v>
+        <v>3677489.84</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>67951.39999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>24420</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>47476.8</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>347094</v>
+        <v>422334</v>
       </c>
       <c r="C12" t="n">
-        <v>83160</v>
+        <v>637560</v>
       </c>
       <c r="D12" t="n">
-        <v>111592.3</v>
+        <v>855540.9399999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>79260.05</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>5550</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1130.4</v>
+        <v>33346.8</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>351252</v>
+        <v>300564</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>266701.98</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>7215</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>18086.4</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>143154</v>
+        <v>30690</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>138600</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>195015.66</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>1110</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>9325.799999999999</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>10890</v>
+        <v>37620</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>118694.72</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3391.2</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>24552</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>120380.04</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>11682</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3108.6</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2970</v>
+        <v>6534</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6217.2</v>
       </c>
     </row>
     <row r="19">
@@ -13212,10 +13206,10 @@
         <v>396</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>68820</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1130.4</v>
       </c>
     </row>
     <row r="20">
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>160506.72</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>166320</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>240760.08</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>27725.4</v>
+        <v>29694.42</v>
       </c>
       <c r="C4" t="n">
-        <v>5364072</v>
+        <v>2962008</v>
       </c>
       <c r="D4" t="n">
-        <v>4214628</v>
+        <v>2327292</v>
       </c>
       <c r="E4" t="n">
-        <v>1481400</v>
+        <v>919800</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>81150</v>
+        <v>89010</v>
       </c>
       <c r="H4" t="n">
-        <v>8910</v>
+        <v>10320</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>192690</v>
+        <v>287370</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>28839.42</v>
+        <v>8563.950000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>4562712</v>
+        <v>579600</v>
       </c>
       <c r="D5" t="n">
-        <v>3584988</v>
+        <v>455400</v>
       </c>
       <c r="E5" t="n">
-        <v>1051200</v>
+        <v>215100</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>83460</v>
+        <v>20160</v>
       </c>
       <c r="H5" t="n">
-        <v>7440</v>
+        <v>2010</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>186450</v>
+        <v>85080</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>34689.96</v>
+        <v>757.4400000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>4920552</v>
+        <v>65520</v>
       </c>
       <c r="D6" t="n">
-        <v>3866148</v>
+        <v>51480</v>
       </c>
       <c r="E6" t="n">
-        <v>932400</v>
+        <v>20700</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>86190</v>
+        <v>2100</v>
       </c>
       <c r="H6" t="n">
-        <v>12180</v>
+        <v>300</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>208890</v>
+        <v>12750</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>28669.41</v>
+        <v>109.89</v>
       </c>
       <c r="C7" t="n">
-        <v>2518488</v>
+        <v>14112</v>
       </c>
       <c r="D7" t="n">
-        <v>1978812</v>
+        <v>11088</v>
       </c>
       <c r="E7" t="n">
-        <v>295200</v>
+        <v>2700</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>66240</v>
+        <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>143100</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23511.33</v>
+        <v>8.1</v>
       </c>
       <c r="C8" t="n">
-        <v>1760976</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1383624</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>150300</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>35550</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>84780</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>15232.5</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>983304</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>772596</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>55800</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>28230</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13785,13 +13779,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>43950</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>2215.98</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154224</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>121176</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3090</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11940</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>398.43</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>51408</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>40392</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1320</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5040</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>191.97</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11592</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>9108</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>136.62</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>13.95</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>11.16</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>5.31</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,13 +14135,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>12977.74</v>
+        <v>3853.78</v>
       </c>
       <c r="C5" t="n">
-        <v>2509491.6</v>
+        <v>318780</v>
       </c>
       <c r="D5" t="n">
-        <v>1186631.03</v>
+        <v>150737.4</v>
       </c>
       <c r="E5" t="n">
-        <v>115947.36</v>
+        <v>23725.53</v>
       </c>
       <c r="F5" t="n">
-        <v>0.42</v>
+        <v>0.14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2678.4</v>
+        <v>723.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>39154.5</v>
+        <v>17866.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>27751.97</v>
+        <v>605.95</v>
       </c>
       <c r="C6" t="n">
-        <v>4428496.8</v>
+        <v>58968</v>
       </c>
       <c r="D6" t="n">
-        <v>1960137.04</v>
+        <v>26100.36</v>
       </c>
       <c r="E6" t="n">
-        <v>157575.6</v>
+        <v>3498.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4309.5</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
-        <v>6942.6</v>
+        <v>171</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>77289.3</v>
+        <v>4717.5</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>27235.94</v>
+        <v>104.4</v>
       </c>
       <c r="C7" t="n">
-        <v>2518488</v>
+        <v>14112</v>
       </c>
       <c r="D7" t="n">
-        <v>1262482.06</v>
+        <v>7074.14</v>
       </c>
       <c r="E7" t="n">
-        <v>62789.04</v>
+        <v>574.29</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>9936</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>3285</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>85860</v>
+        <v>738</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23511.33</v>
+        <v>8.1</v>
       </c>
       <c r="C8" t="n">
-        <v>1760976</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1018347.26</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>36868.59</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>23107.5</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>60193.8</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>15232.5</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>983304</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>620394.59</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>14937.66</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>23995.5</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14717,13 +14711,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>35599.5</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>2215.98</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154224</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>105423.12</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2610</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3090</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>10626.6</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>398.43</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>51408</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>36292.21</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>368.82</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1320</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5040</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>191.97</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11592</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>8443.120000000001</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>430.2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>136.62</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2632.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>13.95</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1924.56</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1171.37</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>11.16</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>5.31</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,13 +15067,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>28551025.8</v>
+        <v>8478310.5</v>
       </c>
       <c r="C5" t="n">
-        <v>138022038</v>
+        <v>17532900</v>
       </c>
       <c r="D5" t="n">
-        <v>120241322.07</v>
+        <v>15274220.74</v>
       </c>
       <c r="E5" t="n">
-        <v>21362141.61</v>
+        <v>4371191.65</v>
       </c>
       <c r="F5" t="n">
-        <v>17500.14</v>
+        <v>5833.38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>740979.36</v>
+        <v>200183.94</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>192498.9</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>368835.39</v>
+        <v>168305.26</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>61054329.6</v>
+        <v>1333094.4</v>
       </c>
       <c r="C6" t="n">
-        <v>243567324</v>
+        <v>3243240</v>
       </c>
       <c r="D6" t="n">
-        <v>198620685.86</v>
+        <v>2644749.48</v>
       </c>
       <c r="E6" t="n">
-        <v>29031728.54</v>
+        <v>644526.79</v>
       </c>
       <c r="F6" t="n">
-        <v>12500.1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>79725.75</v>
+        <v>1942.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1920670.29</v>
+        <v>47307.15</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>728065.21</v>
+        <v>44438.85</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>59919066.9</v>
+        <v>229670.1</v>
       </c>
       <c r="C7" t="n">
-        <v>138516840</v>
+        <v>776160</v>
       </c>
       <c r="D7" t="n">
-        <v>127927306.73</v>
+        <v>716823.01</v>
       </c>
       <c r="E7" t="n">
-        <v>11568252.73</v>
+        <v>105807.19</v>
       </c>
       <c r="F7" t="n">
-        <v>50000.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>183816</v>
+        <v>166.5</v>
       </c>
       <c r="H7" t="n">
-        <v>908795.25</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>808801.2</v>
+        <v>6951.96</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>51724926</v>
+        <v>17820</v>
       </c>
       <c r="C8" t="n">
-        <v>96853680</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>103189128.26</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6792669.02</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>427488.75</v>
+        <v>721.5</v>
       </c>
       <c r="H8" t="n">
-        <v>141091.5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>567025.6</v>
+        <v>1404.52</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>33511500</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>54081720</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>62864583.6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2752114.48</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>443916.75</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,13 +15643,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>335347.29</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>4875156</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8482320</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>10682524.75</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>480866.4</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>57165</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>100102.57</v>
+        <v>1257.57</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>876546</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2827440</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3677489.84</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>24420</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47476.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>422334</v>
-      </c>
-      <c r="C12" t="n">
-        <v>637560</v>
-      </c>
-      <c r="D12" t="n">
-        <v>855540.9399999999</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5550</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>33346.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>300564</v>
-      </c>
-      <c r="C13" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D13" t="n">
-        <v>266701.98</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7215</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>18086.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>30690</v>
-      </c>
-      <c r="C14" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D14" t="n">
-        <v>195015.66</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>9325.799999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>37620</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>24552</v>
-      </c>
-      <c r="C16" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D16" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>11682</v>
-      </c>
-      <c r="C17" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D17" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3108.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>6534</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6217.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>396</v>
-      </c>
-      <c r="C19" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D19" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>68820</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1130.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D20" t="n">
-        <v>160506.72</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D24" t="n">
-        <v>240760.08</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4085.37</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1096200</v>
-      </c>
-      <c r="D4" t="n">
-        <v>861300</v>
-      </c>
-      <c r="E4" t="n">
-        <v>337500</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14250</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3630</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>36570</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5336.37</v>
-      </c>
-      <c r="C5" t="n">
-        <v>850248</v>
-      </c>
-      <c r="D5" t="n">
-        <v>668052</v>
-      </c>
-      <c r="E5" t="n">
-        <v>190800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17700</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2490</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>34410</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4900.05</v>
-      </c>
-      <c r="C6" t="n">
-        <v>520128</v>
-      </c>
-      <c r="D6" t="n">
-        <v>408672</v>
-      </c>
-      <c r="E6" t="n">
-        <v>100800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8250</v>
-      </c>
-      <c r="H6" t="n">
-        <v>930</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20640</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4686.66</v>
-      </c>
-      <c r="C7" t="n">
-        <v>303408</v>
-      </c>
-      <c r="D7" t="n">
-        <v>238392</v>
-      </c>
-      <c r="E7" t="n">
-        <v>53100</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4590</v>
-      </c>
-      <c r="H7" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15150</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4381.11</v>
-      </c>
-      <c r="C8" t="n">
-        <v>210672</v>
-      </c>
-      <c r="D8" t="n">
-        <v>165528</v>
-      </c>
-      <c r="E8" t="n">
-        <v>33300</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3960</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>12270</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3030.57</v>
-      </c>
-      <c r="C9" t="n">
-        <v>127512</v>
-      </c>
-      <c r="D9" t="n">
-        <v>100188</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9900</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3450</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8280</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2207.79</v>
-      </c>
-      <c r="C10" t="n">
-        <v>46872</v>
-      </c>
-      <c r="D10" t="n">
-        <v>36828</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>930</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2310</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1223.28</v>
-      </c>
-      <c r="C11" t="n">
-        <v>12600</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9900</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>330</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>727.5599999999999</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3168</v>
-      </c>
-      <c r="E12" t="n">
-        <v>900</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>440.19</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3024</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2376</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>368.01</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>315.99</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D15" t="n">
-        <v>792</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>410.76</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>160.11</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>38.79</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2401.37</v>
-      </c>
-      <c r="C5" t="n">
-        <v>467636.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>221125.21</v>
-      </c>
-      <c r="E5" t="n">
-        <v>21045.24</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>896.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7226.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3920.04</v>
-      </c>
-      <c r="C6" t="n">
-        <v>468115.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>207196.7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17035.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>412.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>530.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7636.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4452.33</v>
-      </c>
-      <c r="C7" t="n">
-        <v>303408</v>
-      </c>
-      <c r="D7" t="n">
-        <v>152094.1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>11294.37</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>688.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9090</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4381.11</v>
-      </c>
-      <c r="C8" t="n">
-        <v>210672</v>
-      </c>
-      <c r="D8" t="n">
-        <v>121828.61</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8168.49</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2574</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8711.700000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3030.57</v>
-      </c>
-      <c r="C9" t="n">
-        <v>127512</v>
-      </c>
-      <c r="D9" t="n">
-        <v>80450.96000000001</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2650.23</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2932.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6706.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2207.79</v>
-      </c>
-      <c r="C10" t="n">
-        <v>46872</v>
-      </c>
-      <c r="D10" t="n">
-        <v>32040.36</v>
-      </c>
-      <c r="E10" t="n">
-        <v>522</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>930</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2055.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1223.28</v>
-      </c>
-      <c r="C11" t="n">
-        <v>12600</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8895.15</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>330</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>727.5599999999999</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2936.74</v>
-      </c>
-      <c r="E12" t="n">
-        <v>430.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>440.19</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3024</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2256.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>368.01</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1154.74</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>315.99</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D15" t="n">
-        <v>780.91</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>410.76</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>160.11</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>38.79</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5283006.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>25720002</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22406617.73</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3877375.02</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5833.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>247989.06</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>68069.86</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>8624088</v>
-      </c>
-      <c r="C6" t="n">
-        <v>25746336</v>
-      </c>
-      <c r="D6" t="n">
-        <v>20995242.02</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3138565.25</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12500.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7631.25</v>
-      </c>
-      <c r="H6" t="n">
-        <v>146652.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>71938.66</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>9795119.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16687440</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15411694.75</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2080874.73</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>12737.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6058.63</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>85627.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9638442</v>
-      </c>
-      <c r="C8" t="n">
-        <v>11586960</v>
-      </c>
-      <c r="D8" t="n">
-        <v>12344892.85</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1504962.6</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>47619</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>82064.21000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>6667254</v>
-      </c>
-      <c r="C9" t="n">
-        <v>7013160</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8152096.18</v>
-      </c>
-      <c r="E9" t="n">
-        <v>488278.38</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>54251.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>63178.06</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>4857138</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2577960</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3246649.68</v>
-      </c>
-      <c r="E10" t="n">
-        <v>96173.28</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>17205</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>19366.58</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2691216</v>
-      </c>
-      <c r="C11" t="n">
-        <v>693000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>901345.55</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6105</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4804.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1600632</v>
-      </c>
-      <c r="C12" t="n">
-        <v>221760</v>
-      </c>
-      <c r="D12" t="n">
-        <v>297579.46</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>968418</v>
-      </c>
-      <c r="C13" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D13" t="n">
-        <v>228601.7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>809622</v>
-      </c>
-      <c r="C14" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>117009.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>695178</v>
-      </c>
-      <c r="C15" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D15" t="n">
-        <v>79129.81</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>903672</v>
-      </c>
-      <c r="C16" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D16" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>352242</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>85338</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>41778</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>29694.42</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2962008</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2327292</v>
-      </c>
-      <c r="E4" t="n">
-        <v>919800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>33</v>
-      </c>
-      <c r="G4" t="n">
-        <v>89010</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10320</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>287370</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>8563.950000000001</v>
-      </c>
-      <c r="C5" t="n">
-        <v>579600</v>
-      </c>
-      <c r="D5" t="n">
-        <v>455400</v>
-      </c>
-      <c r="E5" t="n">
-        <v>215100</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20160</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2010</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>85080</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>757.4400000000001</v>
-      </c>
-      <c r="C6" t="n">
-        <v>65520</v>
-      </c>
-      <c r="D6" t="n">
-        <v>51480</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20700</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="H6" t="n">
-        <v>300</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>12750</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>109.89</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14112</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11088</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3853.78</v>
-      </c>
-      <c r="C5" t="n">
-        <v>318780</v>
-      </c>
-      <c r="D5" t="n">
-        <v>150737.4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>23725.53</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>723.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>17866.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>605.95</v>
-      </c>
-      <c r="C6" t="n">
-        <v>58968</v>
-      </c>
-      <c r="D6" t="n">
-        <v>26100.36</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3498.3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>105</v>
-      </c>
-      <c r="H6" t="n">
-        <v>171</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4717.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14112</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7074.14</v>
-      </c>
-      <c r="E7" t="n">
-        <v>574.29</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>149.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>133.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>8478310.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>17532900</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15274220.74</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4371191.65</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5833.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>200183.94</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>168305.26</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1333094.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3243240</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2644749.48</v>
-      </c>
-      <c r="E6" t="n">
-        <v>644526.79</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1942.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>47307.15</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>44438.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>229670.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>776160</v>
-      </c>
-      <c r="D7" t="n">
-        <v>716823.01</v>
-      </c>
-      <c r="E7" t="n">
-        <v>105807.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>166.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6951.96</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>17820</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>721.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1404.52</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1257.57</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>67860</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
         <v>40</v>
@@ -576,7 +576,7 @@
         <v>49350</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>26</v>
@@ -614,7 +614,7 @@
         <v>51750</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>9</v>
@@ -652,7 +652,7 @@
         <v>32640</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>14</v>
@@ -690,7 +690,7 @@
         <v>11010</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
@@ -766,7 +766,7 @@
         <v>4290</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -804,7 +804,7 @@
         <v>5640</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>3960</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1698,7 +1698,7 @@
         <v>3810</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1736,7 +1736,7 @@
         <v>5580</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>3366</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
@@ -2630,7 +2630,7 @@
         <v>3810</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -2668,7 +2668,7 @@
         <v>5580</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -2744,7 +2744,7 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         <v>931203.9</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>49583.05</v>
@@ -3562,7 +3562,7 @@
         <v>1054036.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>58333</v>
@@ -3600,7 +3600,7 @@
         <v>1543707</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>58333</v>
@@ -3676,7 +3676,7 @@
         <v>232386</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>8910</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>7440</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>11</v>
@@ -9934,7 +9934,7 @@
         <v>12180</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -9972,7 +9972,7 @@
         <v>4500</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -10086,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>17766</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>7.8</v>
@@ -10866,7 +10866,7 @@
         <v>29497.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>4.5</v>
@@ -10904,7 +10904,7 @@
         <v>23827.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
         <v>9.800000000000001</v>
@@ -10942,7 +10942,7 @@
         <v>9358.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>4.25</v>
@@ -11018,7 +11018,7 @@
         <v>4290</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -11056,7 +11056,7 @@
         <v>5640</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -11132,7 +11132,7 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>2678.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
@@ -11798,7 +11798,7 @@
         <v>6942.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -11836,7 +11836,7 @@
         <v>3285</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
@@ -11950,7 +11950,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>740979.36</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>192498.9</v>
@@ -12730,7 +12730,7 @@
         <v>1920670.29</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>58333</v>
@@ -12768,7 +12768,7 @@
         <v>908795.25</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>632494.5</v>
       </c>
       <c r="J7" t="n">
         <v>122499.3</v>
@@ -12882,7 +12882,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>10320</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -16420,7 +16420,7 @@
         <v>4914963.9</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>454997.4</v>
@@ -16458,7 +16458,7 @@
         <v>8160483.37</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>262498.5</v>
@@ -16496,7 +16496,7 @@
         <v>6591794.88</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>843326</v>
       </c>
       <c r="J7" t="n">
         <v>571663.4</v>
@@ -16534,7 +16534,7 @@
         <v>2589029.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>247915.25</v>
@@ -16610,7 +16610,7 @@
         <v>1186828.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>735993.6</v>
       </c>
       <c r="J10" t="n">
         <v>174999</v>
@@ -16648,7 +16648,7 @@
         <v>1560306</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>174999</v>
@@ -16724,7 +16724,7 @@
         <v>232386</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>7410</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -17428,7 +17428,7 @@
         <v>20940</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
@@ -18360,7 +18360,7 @@
         <v>15286.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
@@ -19292,7 +19292,7 @@
         <v>4228927.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>408331</v>
@@ -20110,7 +20110,7 @@
         <v>24660</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>12</v>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1028</v>
       </c>
       <c r="L4" t="n">
         <v>1351440</v>
@@ -582,7 +582,7 @@
         <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="L5" t="n">
         <v>836340</v>
@@ -620,7 +620,7 @@
         <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="L6" t="n">
         <v>619440</v>
@@ -658,7 +658,7 @@
         <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>395</v>
       </c>
       <c r="L7" t="n">
         <v>494130</v>
@@ -696,7 +696,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="L8" t="n">
         <v>397500</v>
@@ -734,7 +734,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="L9" t="n">
         <v>315810</v>
@@ -772,7 +772,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="L10" t="n">
         <v>192570</v>
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="L11" t="n">
         <v>163770</v>
@@ -848,7 +848,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L12" t="n">
         <v>120780</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L13" t="n">
         <v>49500</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L14" t="n">
         <v>23880</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>10230</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>3000</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>1860</v>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
         <v>17400</v>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
         <v>24150</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
         <v>26160</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L7" t="n">
         <v>35490</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
         <v>44160</v>
@@ -1666,7 +1666,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
         <v>45090</v>
@@ -1704,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
         <v>49200</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
         <v>86940</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
         <v>81240</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L13" t="n">
         <v>36810</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
         <v>17580</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>8790</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2370</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>1380</v>
@@ -2446,7 +2446,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="L5" t="n">
         <v>5071.5</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="L6" t="n">
         <v>9679.200000000001</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>13.94</v>
       </c>
       <c r="L7" t="n">
         <v>21294</v>
@@ -2560,7 +2560,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="L8" t="n">
         <v>31353.6</v>
@@ -2598,7 +2598,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
         <v>36522.9</v>
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
         <v>43788</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
         <v>86940</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
         <v>81240</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L13" t="n">
         <v>36810</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
         <v>17580</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>8790</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2370</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>1380</v>
@@ -3378,7 +3378,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>143364.48</v>
       </c>
       <c r="L5" t="n">
         <v>47773.53</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>346677.5</v>
       </c>
       <c r="L6" t="n">
         <v>91178.06</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>297395.96</v>
       </c>
       <c r="L7" t="n">
         <v>200589.48</v>
@@ -3492,7 +3492,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>460814.4</v>
       </c>
       <c r="L8" t="n">
         <v>295350.91</v>
@@ -3530,7 +3530,7 @@
         <v>277081.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>469348</v>
       </c>
       <c r="L9" t="n">
         <v>344045.72</v>
@@ -3568,7 +3568,7 @@
         <v>58333</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>554684</v>
       </c>
       <c r="L10" t="n">
         <v>412482.96</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>810692</v>
       </c>
       <c r="L11" t="n">
         <v>818974.8</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>810692</v>
       </c>
       <c r="L12" t="n">
         <v>765280.8</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>490682</v>
       </c>
       <c r="L13" t="n">
         <v>346750.2</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L14" t="n">
         <v>165603.6</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L15" t="n">
         <v>82801.8</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>22325.4</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>12999.6</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L4" t="n">
         <v>126420</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
         <v>47220</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>9570</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>2190</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="L5" t="n">
         <v>9916.200000000001</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>3540.9</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1314</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>188165.88</v>
       </c>
       <c r="L5" t="n">
         <v>93410.60000000001</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>33355.28</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>12377.88</v>
@@ -7068,7 +7068,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L4" t="n">
         <v>107100</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
         <v>34800</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>8700</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>3210</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>1320</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>11.34</v>
       </c>
       <c r="L5" t="n">
         <v>7308</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>3219</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>1926</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L8" t="n">
         <v>937.2</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>241927.56</v>
       </c>
       <c r="L5" t="n">
         <v>68841.36</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>110936.8</v>
       </c>
       <c r="L6" t="n">
         <v>30322.98</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>18142.92</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>19200.6</v>
       </c>
       <c r="L8" t="n">
         <v>8828.42</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="L4" t="n">
         <v>192690</v>
@@ -9902,7 +9902,7 @@
         <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="L5" t="n">
         <v>186450</v>
@@ -9940,7 +9940,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="L6" t="n">
         <v>208890</v>
@@ -9978,7 +9978,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="L7" t="n">
         <v>143100</v>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L8" t="n">
         <v>84780</v>
@@ -10054,7 +10054,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="L9" t="n">
         <v>43950</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
         <v>11940</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>5040</v>
@@ -10358,7 +10358,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>330</v>
@@ -10834,7 +10834,7 @@
         <v>7.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>235.62</v>
       </c>
       <c r="L5" t="n">
         <v>175631.4</v>
@@ -10872,7 +10872,7 @@
         <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>319.15</v>
       </c>
       <c r="L6" t="n">
         <v>229192.8</v>
@@ -10910,7 +10910,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>323.9</v>
       </c>
       <c r="L7" t="n">
         <v>296478</v>
@@ -10948,7 +10948,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>303.3</v>
       </c>
       <c r="L8" t="n">
         <v>282225</v>
@@ -10986,7 +10986,7 @@
         <v>9.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="L9" t="n">
         <v>255806.1</v>
@@ -11024,7 +11024,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="L10" t="n">
         <v>171387.3</v>
@@ -11062,7 +11062,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="L11" t="n">
         <v>163770</v>
@@ -11100,7 +11100,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L12" t="n">
         <v>120780</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L13" t="n">
         <v>49500</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L14" t="n">
         <v>23880</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>10230</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>3000</v>
@@ -11290,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>1860</v>
@@ -11766,7 +11766,7 @@
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>70.14</v>
       </c>
       <c r="L5" t="n">
         <v>39154.5</v>
@@ -11804,7 +11804,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>141.05</v>
       </c>
       <c r="L6" t="n">
         <v>77289.3</v>
@@ -11842,7 +11842,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>113.16</v>
       </c>
       <c r="L7" t="n">
         <v>85860</v>
@@ -11880,7 +11880,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>60193.8</v>
@@ -11918,7 +11918,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="L9" t="n">
         <v>35599.5</v>
@@ -11956,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
         <v>10626.6</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>5040</v>
@@ -12222,7 +12222,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>330</v>
@@ -12698,7 +12698,7 @@
         <v>192498.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1496366.76</v>
       </c>
       <c r="L5" t="n">
         <v>368835.39</v>
@@ -12736,7 +12736,7 @@
         <v>58333</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3009160.7</v>
       </c>
       <c r="L6" t="n">
         <v>728065.21</v>
@@ -12774,7 +12774,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2414155.44</v>
       </c>
       <c r="L7" t="n">
         <v>808801.2</v>
@@ -12812,7 +12812,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1708853.4</v>
       </c>
       <c r="L8" t="n">
         <v>567025.6</v>
@@ -12850,7 +12850,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1152036</v>
       </c>
       <c r="L9" t="n">
         <v>335347.29</v>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>192006</v>
       </c>
       <c r="L10" t="n">
         <v>100102.57</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L11" t="n">
         <v>47476.8</v>
@@ -13154,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>3108.6</v>
@@ -13592,7 +13592,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L4" t="n">
         <v>287370</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
         <v>85080</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="L5" t="n">
         <v>17866.8</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>179205.6</v>
       </c>
       <c r="L5" t="n">
         <v>168305.26</v>
@@ -16426,7 +16426,7 @@
         <v>454997.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5026717.08</v>
       </c>
       <c r="L5" t="n">
         <v>1654447.79</v>
@@ -16464,7 +16464,7 @@
         <v>262498.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6808746.1</v>
       </c>
       <c r="L6" t="n">
         <v>2158996.18</v>
@@ -16502,7 +16502,7 @@
         <v>571663.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6910082.6</v>
       </c>
       <c r="L7" t="n">
         <v>2792822.76</v>
@@ -16540,7 +16540,7 @@
         <v>247915.25</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6470602.2</v>
       </c>
       <c r="L8" t="n">
         <v>2658559.5</v>
@@ -16578,7 +16578,7 @@
         <v>554163.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5973520</v>
       </c>
       <c r="L9" t="n">
         <v>2409693.46</v>
@@ -16616,7 +16616,7 @@
         <v>174999</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3733450</v>
       </c>
       <c r="L10" t="n">
         <v>1614468.37</v>
@@ -16654,7 +16654,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2496078</v>
       </c>
       <c r="L11" t="n">
         <v>1542713.4</v>
@@ -16692,7 +16692,7 @@
         <v>174999</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1749388</v>
       </c>
       <c r="L12" t="n">
         <v>1137747.6</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>725356</v>
       </c>
       <c r="L13" t="n">
         <v>466290</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>277342</v>
       </c>
       <c r="L14" t="n">
         <v>224949.6</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L15" t="n">
         <v>96366.60000000001</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L16" t="n">
         <v>28260</v>
@@ -16882,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L17" t="n">
         <v>17521.2</v>
@@ -17320,7 +17320,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="L4" t="n">
         <v>157080</v>
@@ -17358,7 +17358,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="L5" t="n">
         <v>180060</v>
@@ -17396,7 +17396,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="L6" t="n">
         <v>186090</v>
@@ -17434,7 +17434,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="L7" t="n">
         <v>233910</v>
@@ -17472,7 +17472,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="L8" t="n">
         <v>242610</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="L9" t="n">
         <v>215190</v>
@@ -17548,7 +17548,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L10" t="n">
         <v>127260</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L11" t="n">
         <v>70410</v>
@@ -17624,7 +17624,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L12" t="n">
         <v>35760</v>
@@ -17662,7 +17662,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>10620</v>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>4770</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>1080</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>330</v>
@@ -18290,7 +18290,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>37812.6</v>
@@ -18328,7 +18328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>68853.3</v>
@@ -18366,7 +18366,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>164.82</v>
       </c>
       <c r="L7" t="n">
         <v>140346</v>
@@ -18404,7 +18404,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>196.2</v>
       </c>
       <c r="L8" t="n">
         <v>172253.1</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="L9" t="n">
         <v>174303.9</v>
@@ -18480,7 +18480,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L10" t="n">
         <v>113261.4</v>
@@ -18518,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L11" t="n">
         <v>70410</v>
@@ -18556,7 +18556,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L12" t="n">
         <v>35760</v>
@@ -18594,7 +18594,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>10620</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>4770</v>
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>1080</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>330</v>
@@ -19222,7 +19222,7 @@
         <v>69999.60000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1388843.4</v>
       </c>
       <c r="L5" t="n">
         <v>356194.69</v>
@@ -19260,7 +19260,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2024596.6</v>
       </c>
       <c r="L6" t="n">
         <v>648598.09</v>
@@ -19298,7 +19298,7 @@
         <v>408331</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3516269.88</v>
       </c>
       <c r="L7" t="n">
         <v>1322059.32</v>
@@ -19336,7 +19336,7 @@
         <v>148749.15</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4185730.8</v>
       </c>
       <c r="L8" t="n">
         <v>1622624.2</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4309468</v>
       </c>
       <c r="L9" t="n">
         <v>1641942.74</v>
@@ -19412,7 +19412,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2986760</v>
       </c>
       <c r="L10" t="n">
         <v>1066922.39</v>
@@ -19450,7 +19450,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1642718</v>
       </c>
       <c r="L11" t="n">
         <v>663262.2</v>
@@ -19488,7 +19488,7 @@
         <v>174999</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>917362</v>
       </c>
       <c r="L12" t="n">
         <v>336859.2</v>
@@ -19526,7 +19526,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L13" t="n">
         <v>100040.4</v>
@@ -19564,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L14" t="n">
         <v>44933.4</v>
@@ -19602,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L15" t="n">
         <v>10173.6</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>3108.6</v>
@@ -20116,7 +20116,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
         <v>402390</v>
@@ -20154,7 +20154,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L5" t="n">
         <v>216270</v>
@@ -20192,7 +20192,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="L6" t="n">
         <v>115140</v>
@@ -20230,7 +20230,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
         <v>46500</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>7020</v>
@@ -21086,7 +21086,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>45416.7</v>
@@ -21124,7 +21124,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>60.45</v>
       </c>
       <c r="L6" t="n">
         <v>42601.8</v>
@@ -21162,7 +21162,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>27.88</v>
       </c>
       <c r="L7" t="n">
         <v>27900</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L8" t="n">
         <v>4984.2</v>
@@ -22018,7 +22018,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1370922.84</v>
       </c>
       <c r="L5" t="n">
         <v>427825.31</v>
@@ -22056,7 +22056,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1289640.3</v>
       </c>
       <c r="L6" t="n">
         <v>401308.96</v>
@@ -22094,7 +22094,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>594791.92</v>
       </c>
       <c r="L7" t="n">
         <v>262818</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>57601.8</v>
       </c>
       <c r="L8" t="n">
         <v>46951.16</v>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>162213.48</v>
+        <v>162050.13</v>
       </c>
       <c r="C4" t="n">
         <v>34037640</v>
@@ -529,10 +534,10 @@
         <v>8136000</v>
       </c>
       <c r="F4" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G4" t="n">
-        <v>514980</v>
+        <v>512430</v>
       </c>
       <c r="H4" t="n">
         <v>67860</v>
@@ -544,10 +549,13 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>1028</v>
+        <v>1014</v>
       </c>
       <c r="L4" t="n">
-        <v>1351440</v>
+        <v>1348260</v>
+      </c>
+      <c r="M4" t="n">
+        <v>63720</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>108583.74</v>
+        <v>108419.58</v>
       </c>
       <c r="C5" t="n">
         <v>19191816</v>
@@ -570,7 +578,7 @@
         <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>334230</v>
+        <v>332760</v>
       </c>
       <c r="H5" t="n">
         <v>49350</v>
@@ -582,10 +590,13 @@
         <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="L5" t="n">
-        <v>836340</v>
+        <v>834330</v>
+      </c>
+      <c r="M5" t="n">
+        <v>48510</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>84232.98</v>
+        <v>84085.64999999999</v>
       </c>
       <c r="C6" t="n">
         <v>13977432</v>
@@ -608,7 +619,7 @@
         <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>245400</v>
+        <v>244650</v>
       </c>
       <c r="H6" t="n">
         <v>51750</v>
@@ -620,10 +631,13 @@
         <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L6" t="n">
-        <v>619440</v>
+        <v>617700</v>
+      </c>
+      <c r="M6" t="n">
+        <v>30060</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>70820.91</v>
+        <v>70773.66</v>
       </c>
       <c r="C7" t="n">
         <v>8814960</v>
@@ -646,7 +660,7 @@
         <v>33</v>
       </c>
       <c r="G7" t="n">
-        <v>196170</v>
+        <v>195720</v>
       </c>
       <c r="H7" t="n">
         <v>32640</v>
@@ -661,7 +675,10 @@
         <v>395</v>
       </c>
       <c r="L7" t="n">
-        <v>494130</v>
+        <v>493140</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20610</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +686,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>61194.78</v>
+        <v>61194.15</v>
       </c>
       <c r="C8" t="n">
         <v>6895728</v>
@@ -684,7 +701,7 @@
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>156060</v>
+        <v>155610</v>
       </c>
       <c r="H8" t="n">
         <v>11010</v>
@@ -699,7 +716,10 @@
         <v>337</v>
       </c>
       <c r="L8" t="n">
-        <v>397500</v>
+        <v>396780</v>
+      </c>
+      <c r="M8" t="n">
+        <v>13440</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +742,7 @@
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>152940</v>
+        <v>152610</v>
       </c>
       <c r="H9" t="n">
         <v>3780</v>
@@ -737,7 +757,10 @@
         <v>280</v>
       </c>
       <c r="L9" t="n">
-        <v>315810</v>
+        <v>315450</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10080</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +768,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>34246.89</v>
+        <v>34246.62</v>
       </c>
       <c r="C10" t="n">
         <v>3190824</v>
@@ -775,7 +798,10 @@
         <v>175</v>
       </c>
       <c r="L10" t="n">
-        <v>192570</v>
+        <v>192480</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6810</v>
       </c>
     </row>
     <row r="11">
@@ -783,7 +809,7 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>24060.06</v>
+        <v>24059.97</v>
       </c>
       <c r="C11" t="n">
         <v>1797768</v>
@@ -813,7 +839,10 @@
         <v>117</v>
       </c>
       <c r="L11" t="n">
-        <v>163770</v>
+        <v>163500</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4410</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>82</v>
       </c>
       <c r="L12" t="n">
-        <v>120780</v>
+        <v>120570</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3180</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>49500</v>
       </c>
+      <c r="M13" t="n">
+        <v>2310</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>23880</v>
       </c>
+      <c r="M14" t="n">
+        <v>960</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>10230</v>
       </c>
+      <c r="M15" t="n">
+        <v>960</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>3000</v>
       </c>
+      <c r="M16" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>1860</v>
       </c>
+      <c r="M17" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>3810</v>
       </c>
+      <c r="M18" t="n">
+        <v>2940</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>1200</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>30</v>
       </c>
+      <c r="M20" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1479,7 +1556,10 @@
         <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>17400</v>
+        <v>17520</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4170</v>
       </c>
     </row>
     <row r="5">
@@ -1502,7 +1582,7 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>8820</v>
+        <v>8850</v>
       </c>
       <c r="H5" t="n">
         <v>2580</v>
@@ -1517,7 +1597,10 @@
         <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>24150</v>
+        <v>24090</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10620</v>
       </c>
     </row>
     <row r="6">
@@ -1540,10 +1623,10 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>8310</v>
+        <v>8190</v>
       </c>
       <c r="H6" t="n">
-        <v>1890</v>
+        <v>1860</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1555,7 +1638,10 @@
         <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>26160</v>
+        <v>26250</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9450</v>
       </c>
     </row>
     <row r="7">
@@ -1563,7 +1649,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>4223.7</v>
+        <v>4223.61</v>
       </c>
       <c r="C7" t="n">
         <v>564984</v>
@@ -1578,10 +1664,10 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>12990</v>
+        <v>13320</v>
       </c>
       <c r="H7" t="n">
-        <v>3480</v>
+        <v>3510</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1593,7 +1679,10 @@
         <v>17</v>
       </c>
       <c r="L7" t="n">
-        <v>35490</v>
+        <v>35700</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6660</v>
       </c>
     </row>
     <row r="8">
@@ -1616,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>18360</v>
+        <v>18300</v>
       </c>
       <c r="H8" t="n">
         <v>3960</v>
@@ -1631,7 +1720,10 @@
         <v>24</v>
       </c>
       <c r="L8" t="n">
-        <v>44160</v>
+        <v>44370</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4500</v>
       </c>
     </row>
     <row r="9">
@@ -1654,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>21240</v>
+        <v>21270</v>
       </c>
       <c r="H9" t="n">
         <v>2910</v>
@@ -1669,7 +1761,10 @@
         <v>22</v>
       </c>
       <c r="L9" t="n">
-        <v>45090</v>
+        <v>45120</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2760</v>
       </c>
     </row>
     <row r="10">
@@ -1692,7 +1787,7 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>17400</v>
+        <v>17430</v>
       </c>
       <c r="H10" t="n">
         <v>3810</v>
@@ -1707,7 +1802,10 @@
         <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>49200</v>
+        <v>49320</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1830</v>
       </c>
     </row>
     <row r="11">
@@ -1730,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>28500</v>
+        <v>28530</v>
       </c>
       <c r="H11" t="n">
         <v>5580</v>
@@ -1745,7 +1843,10 @@
         <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>86940</v>
+        <v>87180</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1290</v>
       </c>
     </row>
     <row r="12">
@@ -1768,7 +1869,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>30960</v>
+        <v>30930</v>
       </c>
       <c r="H12" t="n">
         <v>1890</v>
@@ -1783,7 +1884,10 @@
         <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>81240</v>
+        <v>81270</v>
+      </c>
+      <c r="M12" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="13">
@@ -1806,7 +1910,7 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>19560</v>
+        <v>19590</v>
       </c>
       <c r="H13" t="n">
         <v>840</v>
@@ -1821,7 +1925,10 @@
         <v>23</v>
       </c>
       <c r="L13" t="n">
-        <v>36810</v>
+        <v>36870</v>
+      </c>
+      <c r="M13" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="14">
@@ -1859,7 +1966,10 @@
         <v>11</v>
       </c>
       <c r="L14" t="n">
-        <v>17580</v>
+        <v>17640</v>
+      </c>
+      <c r="M14" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>8790</v>
       </c>
+      <c r="M15" t="n">
+        <v>870</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>2370</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>1380</v>
       </c>
+      <c r="M17" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>2910</v>
       </c>
+      <c r="M18" t="n">
+        <v>2310</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>1080</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>30</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2446,10 +2598,13 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>6.72</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>5071.5</v>
+        <v>5058.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>212.4</v>
       </c>
     </row>
     <row r="6">
@@ -2472,10 +2627,10 @@
         <v>0.6</v>
       </c>
       <c r="G6" t="n">
-        <v>415.5</v>
+        <v>409.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1077.3</v>
+        <v>1060.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -2484,10 +2639,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>16.25</v>
+        <v>12.68</v>
       </c>
       <c r="L6" t="n">
-        <v>9679.200000000001</v>
+        <v>9712.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -2495,7 +2653,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>4012.51</v>
+        <v>4012.43</v>
       </c>
       <c r="C7" t="n">
         <v>564984</v>
@@ -2510,10 +2668,10 @@
         <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1948.5</v>
+        <v>1998</v>
       </c>
       <c r="H7" t="n">
-        <v>2540.4</v>
+        <v>2562.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2522,10 +2680,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>13.94</v>
+        <v>10.85</v>
       </c>
       <c r="L7" t="n">
-        <v>21294</v>
+        <v>21420</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2331</v>
       </c>
     </row>
     <row r="8">
@@ -2548,22 +2709,25 @@
         <v>6.65</v>
       </c>
       <c r="G8" t="n">
-        <v>11934</v>
+        <v>11895</v>
       </c>
       <c r="H8" t="n">
         <v>3366</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>21.6</v>
+        <v>17.66</v>
       </c>
       <c r="L8" t="n">
-        <v>31353.6</v>
+        <v>31502.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2700</v>
       </c>
     </row>
     <row r="9">
@@ -2586,7 +2750,7 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>18054</v>
+        <v>18079.5</v>
       </c>
       <c r="H9" t="n">
         <v>2910</v>
@@ -2598,10 +2762,13 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>17.67</v>
       </c>
       <c r="L9" t="n">
-        <v>36522.9</v>
+        <v>36547.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2760</v>
       </c>
     </row>
     <row r="10">
@@ -2624,22 +2791,25 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>17400</v>
+        <v>17430</v>
       </c>
       <c r="H10" t="n">
         <v>3810</v>
       </c>
       <c r="I10" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>22.62</v>
       </c>
       <c r="L10" t="n">
-        <v>43788</v>
+        <v>43894.8</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1830</v>
       </c>
     </row>
     <row r="11">
@@ -2662,22 +2832,25 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>28500</v>
+        <v>28530</v>
       </c>
       <c r="H11" t="n">
         <v>5580</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
+        <v>34.14</v>
       </c>
       <c r="L11" t="n">
-        <v>86940</v>
+        <v>87180</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1290</v>
       </c>
     </row>
     <row r="12">
@@ -2700,7 +2873,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>30960</v>
+        <v>30930</v>
       </c>
       <c r="H12" t="n">
         <v>1890</v>
@@ -2712,10 +2885,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>35.23</v>
       </c>
       <c r="L12" t="n">
-        <v>81240</v>
+        <v>81270</v>
+      </c>
+      <c r="M12" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="13">
@@ -2738,22 +2914,25 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>19560</v>
+        <v>19590</v>
       </c>
       <c r="H13" t="n">
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>23</v>
+        <v>21.84</v>
       </c>
       <c r="L13" t="n">
-        <v>36810</v>
+        <v>36870</v>
+      </c>
+      <c r="M13" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="14">
@@ -2788,10 +2967,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>10.69</v>
       </c>
       <c r="L14" t="n">
-        <v>17580</v>
+        <v>17640</v>
+      </c>
+      <c r="M14" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -2826,10 +3008,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L15" t="n">
         <v>8790</v>
+      </c>
+      <c r="M15" t="n">
+        <v>870</v>
       </c>
     </row>
     <row r="16">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>2370</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>1380</v>
       </c>
+      <c r="M17" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>2910</v>
       </c>
+      <c r="M18" t="n">
+        <v>2310</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>1080</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>30</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3354,13 +3578,13 @@
         <v>1361448</v>
       </c>
       <c r="C5" t="n">
-        <v>14392224</v>
+        <v>10990425.6</v>
       </c>
       <c r="D5" t="n">
-        <v>12538142.94</v>
+        <v>23757262.85</v>
       </c>
       <c r="E5" t="n">
-        <v>6748827.27</v>
+        <v>12637567.35</v>
       </c>
       <c r="F5" t="n">
         <v>4166.7</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>256952.52</v>
+        <v>5294160</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>34999.8</v>
+        <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>143364.48</v>
+        <v>257152.58</v>
       </c>
       <c r="L5" t="n">
-        <v>47773.53</v>
+        <v>910602</v>
+      </c>
+      <c r="M5" t="n">
+        <v>63720</v>
       </c>
     </row>
     <row r="6">
@@ -3392,22 +3619,22 @@
         <v>5087966.4</v>
       </c>
       <c r="C6" t="n">
-        <v>25446960</v>
+        <v>19432224</v>
       </c>
       <c r="D6" t="n">
-        <v>20751111.3</v>
+        <v>39319188.48</v>
       </c>
       <c r="E6" t="n">
-        <v>8462917.01</v>
+        <v>15847299</v>
       </c>
       <c r="F6" t="n">
         <v>25000.2</v>
       </c>
       <c r="G6" t="n">
-        <v>7686.75</v>
+        <v>22113</v>
       </c>
       <c r="H6" t="n">
-        <v>298035.04</v>
+        <v>6043140</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3416,10 +3643,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>346677.5</v>
+        <v>615447.3</v>
       </c>
       <c r="L6" t="n">
-        <v>91178.06</v>
+        <v>1748250</v>
+      </c>
+      <c r="M6" t="n">
+        <v>226800</v>
       </c>
     </row>
     <row r="7">
@@ -3427,25 +3657,25 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>8827533</v>
+        <v>8827344.9</v>
       </c>
       <c r="C7" t="n">
-        <v>31074120</v>
+        <v>23729328</v>
       </c>
       <c r="D7" t="n">
-        <v>28698521.28</v>
+        <v>54377934.34</v>
       </c>
       <c r="E7" t="n">
-        <v>15342042.49</v>
+        <v>28728857.25</v>
       </c>
       <c r="F7" t="n">
         <v>150001.2</v>
       </c>
       <c r="G7" t="n">
-        <v>36047.25</v>
+        <v>107892</v>
       </c>
       <c r="H7" t="n">
-        <v>702801.66</v>
+        <v>14605110</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3454,10 +3684,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>297395.96</v>
+        <v>526638.38</v>
       </c>
       <c r="L7" t="n">
-        <v>200589.48</v>
+        <v>3855600</v>
+      </c>
+      <c r="M7" t="n">
+        <v>699300</v>
       </c>
     </row>
     <row r="8">
@@ -3468,34 +3701,37 @@
         <v>9652698</v>
       </c>
       <c r="C8" t="n">
-        <v>37394280</v>
+        <v>28555632</v>
       </c>
       <c r="D8" t="n">
-        <v>39840336.01</v>
+        <v>75489435.65000001</v>
       </c>
       <c r="E8" t="n">
-        <v>16757961.9</v>
+        <v>31380247.8</v>
       </c>
       <c r="F8" t="n">
         <v>277085.55</v>
       </c>
       <c r="G8" t="n">
-        <v>220779</v>
+        <v>642330</v>
       </c>
       <c r="H8" t="n">
-        <v>931203.9</v>
+        <v>19186200</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>460814.4</v>
+        <v>857693.1800000001</v>
       </c>
       <c r="L8" t="n">
-        <v>295350.91</v>
+        <v>5670486</v>
+      </c>
+      <c r="M8" t="n">
+        <v>810000</v>
       </c>
     </row>
     <row r="9">
@@ -3506,34 +3742,37 @@
         <v>9900198</v>
       </c>
       <c r="C9" t="n">
-        <v>39417840</v>
+        <v>30100896</v>
       </c>
       <c r="D9" t="n">
-        <v>45819291.58</v>
+        <v>86818355.70999999</v>
       </c>
       <c r="E9" t="n">
-        <v>16912187.36</v>
+        <v>31669043.85</v>
       </c>
       <c r="F9" t="n">
         <v>166668</v>
       </c>
       <c r="G9" t="n">
-        <v>333999</v>
+        <v>976293</v>
       </c>
       <c r="H9" t="n">
-        <v>805051.5</v>
+        <v>16587000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>277081.75</v>
+        <v>115320.5</v>
       </c>
       <c r="K9" t="n">
-        <v>469348</v>
+        <v>857790.3</v>
       </c>
       <c r="L9" t="n">
-        <v>344045.72</v>
+        <v>6578496</v>
+      </c>
+      <c r="M9" t="n">
+        <v>828000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,34 +3783,37 @@
         <v>8783082</v>
       </c>
       <c r="C10" t="n">
-        <v>32681880</v>
+        <v>24957072</v>
       </c>
       <c r="D10" t="n">
-        <v>41159139.48</v>
+        <v>77988303.36</v>
       </c>
       <c r="E10" t="n">
-        <v>10627147.44</v>
+        <v>19899945</v>
       </c>
       <c r="F10" t="n">
         <v>291669</v>
       </c>
       <c r="G10" t="n">
-        <v>321900</v>
+        <v>941220</v>
       </c>
       <c r="H10" t="n">
-        <v>1054036.5</v>
+        <v>21717000</v>
       </c>
       <c r="I10" t="n">
-        <v>367996.8</v>
+        <v>168974.88</v>
       </c>
       <c r="J10" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>554684</v>
+        <v>1098336.72</v>
       </c>
       <c r="L10" t="n">
-        <v>412482.96</v>
+        <v>7901064</v>
+      </c>
+      <c r="M10" t="n">
+        <v>549000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,34 +3824,37 @@
         <v>11841588</v>
       </c>
       <c r="C11" t="n">
-        <v>35232120</v>
+        <v>26904528</v>
       </c>
       <c r="D11" t="n">
-        <v>45824407.74</v>
+        <v>86828049.79000001</v>
       </c>
       <c r="E11" t="n">
-        <v>13658230.76</v>
+        <v>25575822.9</v>
       </c>
       <c r="F11" t="n">
         <v>416670</v>
       </c>
       <c r="G11" t="n">
-        <v>527250</v>
+        <v>1540620</v>
       </c>
       <c r="H11" t="n">
-        <v>1543707</v>
+        <v>31806000</v>
       </c>
       <c r="I11" t="n">
-        <v>383330</v>
+        <v>174510.26</v>
       </c>
       <c r="J11" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>810692</v>
+        <v>1657847.51</v>
       </c>
       <c r="L11" t="n">
-        <v>818974.8</v>
+        <v>15692400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>387000</v>
       </c>
     </row>
     <row r="12">
@@ -3620,22 +3865,22 @@
         <v>14438160</v>
       </c>
       <c r="C12" t="n">
-        <v>30020760</v>
+        <v>22924944</v>
       </c>
       <c r="D12" t="n">
-        <v>40284819.25</v>
+        <v>76331642.11</v>
       </c>
       <c r="E12" t="n">
-        <v>11334186.86</v>
+        <v>21223917</v>
       </c>
       <c r="F12" t="n">
         <v>291669</v>
       </c>
       <c r="G12" t="n">
-        <v>572760</v>
+        <v>1670220</v>
       </c>
       <c r="H12" t="n">
-        <v>522868.5</v>
+        <v>10773000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3644,10 +3889,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>810692</v>
+        <v>1710433.66</v>
       </c>
       <c r="L12" t="n">
-        <v>765280.8</v>
+        <v>14628600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>135000</v>
       </c>
     </row>
     <row r="13">
@@ -3658,34 +3906,37 @@
         <v>8890200</v>
       </c>
       <c r="C13" t="n">
-        <v>16632000</v>
+        <v>12700800</v>
       </c>
       <c r="D13" t="n">
-        <v>22860169.6</v>
+        <v>43315430.4</v>
       </c>
       <c r="E13" t="n">
-        <v>7809734.62</v>
+        <v>14624177.4</v>
       </c>
       <c r="F13" t="n">
         <v>166668</v>
       </c>
       <c r="G13" t="n">
-        <v>361860</v>
+        <v>1057860</v>
       </c>
       <c r="H13" t="n">
-        <v>232386</v>
+        <v>4788000</v>
       </c>
       <c r="I13" t="n">
-        <v>383330</v>
+        <v>184415.69</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>490682</v>
+        <v>1060390.21</v>
       </c>
       <c r="L13" t="n">
-        <v>346750.2</v>
+        <v>6636600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>144000</v>
       </c>
     </row>
     <row r="14">
@@ -3696,22 +3947,22 @@
         <v>3439854</v>
       </c>
       <c r="C14" t="n">
-        <v>10062360</v>
+        <v>7683984</v>
       </c>
       <c r="D14" t="n">
-        <v>14158137.26</v>
+        <v>26826826.75</v>
       </c>
       <c r="E14" t="n">
-        <v>4153558.15</v>
+        <v>7777776.6</v>
       </c>
       <c r="F14" t="n">
         <v>41667</v>
       </c>
       <c r="G14" t="n">
-        <v>117105</v>
+        <v>341820</v>
       </c>
       <c r="H14" t="n">
-        <v>124492.5</v>
+        <v>2565000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3720,10 +3971,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>234674</v>
+        <v>519160.75</v>
       </c>
       <c r="L14" t="n">
-        <v>165603.6</v>
+        <v>3175200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="15">
@@ -3734,22 +3988,22 @@
         <v>2588454</v>
       </c>
       <c r="C15" t="n">
-        <v>3825360</v>
+        <v>2921184</v>
       </c>
       <c r="D15" t="n">
-        <v>5459957.09</v>
+        <v>10345522.18</v>
       </c>
       <c r="E15" t="n">
-        <v>1186512.97</v>
+        <v>2221813.8</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>61605</v>
+        <v>179820</v>
       </c>
       <c r="H15" t="n">
-        <v>33198</v>
+        <v>684000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3758,10 +4012,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>64002</v>
+        <v>143628.65</v>
       </c>
       <c r="L15" t="n">
-        <v>82801.8</v>
+        <v>1582200</v>
+      </c>
+      <c r="M15" t="n">
+        <v>261000</v>
       </c>
     </row>
     <row r="16">
@@ -3772,22 +4029,22 @@
         <v>1025046</v>
       </c>
       <c r="C16" t="n">
-        <v>1053360</v>
+        <v>804384</v>
       </c>
       <c r="D16" t="n">
-        <v>1524813.84</v>
+        <v>2889216</v>
       </c>
       <c r="E16" t="n">
-        <v>206706.23</v>
+        <v>387069.3</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>15540</v>
+        <v>45360</v>
       </c>
       <c r="H16" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3796,10 +4053,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>22325.4</v>
+        <v>426600</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="17">
@@ -3810,22 +4070,22 @@
         <v>464310</v>
       </c>
       <c r="C17" t="n">
-        <v>471240</v>
+        <v>359856</v>
       </c>
       <c r="D17" t="n">
-        <v>682153.5600000001</v>
+        <v>1292544</v>
       </c>
       <c r="E17" t="n">
-        <v>123234.45</v>
+        <v>230763.6</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3834,10 +4094,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L17" t="n">
-        <v>12999.6</v>
+        <v>248400</v>
+      </c>
+      <c r="M17" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="18">
@@ -3848,34 +4111,37 @@
         <v>187506</v>
       </c>
       <c r="C18" t="n">
+        <v>529200</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1900800</v>
+      </c>
+      <c r="E18" t="n">
+        <v>251908.65</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>171000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>523800</v>
+      </c>
+      <c r="M18" t="n">
         <v>693000</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1003167</v>
-      </c>
-      <c r="E18" t="n">
-        <v>134526.52</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>8299.5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>27412.2</v>
       </c>
     </row>
     <row r="19">
@@ -3898,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -3913,7 +4179,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10173.6</v>
+        <v>194400</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3939,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -3951,7 +4220,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>41670</v>
+        <v>41700</v>
       </c>
       <c r="H4" t="n">
         <v>4440</v>
@@ -4275,7 +4568,10 @@
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>126420</v>
+        <v>126300</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4298,7 +4594,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>14550</v>
+        <v>14610</v>
       </c>
       <c r="H5" t="n">
         <v>510</v>
@@ -4313,7 +4609,10 @@
         <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>47220</v>
+        <v>47700</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4336,7 +4635,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>1710</v>
+        <v>1740</v>
       </c>
       <c r="H6" t="n">
         <v>150</v>
@@ -4351,7 +4650,10 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>9570</v>
+        <v>9540</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>2190</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>420</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>150</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.82</v>
+        <v>6.95</v>
       </c>
       <c r="L5" t="n">
-        <v>9916.200000000001</v>
+        <v>10017</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5268,7 +5639,7 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>85.5</v>
+        <v>87</v>
       </c>
       <c r="H6" t="n">
         <v>85.5</v>
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>3540.9</v>
+        <v>3529.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5318,10 +5692,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
         <v>1314</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>298.2</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>121.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>4089066.3</v>
       </c>
       <c r="C5" t="n">
-        <v>16572402</v>
+        <v>12655288.8</v>
       </c>
       <c r="D5" t="n">
-        <v>14437459.08</v>
+        <v>27356085.5</v>
       </c>
       <c r="E5" t="n">
-        <v>2871452.25</v>
+        <v>5376959.55</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>50792.94</v>
+        <v>1046520</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>188165.88</v>
+        <v>337512.76</v>
       </c>
       <c r="L5" t="n">
-        <v>93410.60000000001</v>
+        <v>1803060</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>637560</v>
       </c>
       <c r="C6" t="n">
-        <v>4914756</v>
+        <v>3753086.4</v>
       </c>
       <c r="D6" t="n">
-        <v>4007812.67</v>
+        <v>7594000.13</v>
       </c>
       <c r="E6" t="n">
-        <v>1485213.91</v>
+        <v>2781148.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1581.75</v>
+        <v>4698</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>33355.28</v>
+        <v>635364</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>77873.39999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>970200</v>
+        <v>740880</v>
       </c>
       <c r="D7" t="n">
-        <v>896028.76</v>
+        <v>1697794.56</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1332</v>
+        <v>3888</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6250,10 +6696,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>17493.88</v>
+        <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>12377.88</v>
+        <v>236520</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6264,10 +6713,10 @@
         <v>43758</v>
       </c>
       <c r="C8" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D8" t="n">
-        <v>118132.95</v>
+        <v>223838.21</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2164.5</v>
+        <v>6318</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2809.04</v>
+        <v>53676</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6302,19 +6754,19 @@
         <v>21384</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -6329,7 +6781,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1144.53</v>
+        <v>21870</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>72060</v>
+        <v>72120</v>
       </c>
       <c r="H4" t="n">
         <v>4650</v>
@@ -7071,7 +7580,10 @@
         <v>137</v>
       </c>
       <c r="L4" t="n">
-        <v>107100</v>
+        <v>107190</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7094,7 +7606,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>19050</v>
+        <v>19080</v>
       </c>
       <c r="H5" t="n">
         <v>3060</v>
@@ -7110,6 +7622,9 @@
       </c>
       <c r="L5" t="n">
         <v>34800</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>8700</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>3210</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>1320</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11.34</v>
+        <v>8.94</v>
       </c>
       <c r="L5" t="n">
         <v>7308</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>4.06</v>
       </c>
       <c r="L6" t="n">
         <v>3219</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>1926</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8152,10 +8745,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>937.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>4860761.4</v>
       </c>
       <c r="C5" t="n">
-        <v>20231442</v>
+        <v>15449464.8</v>
       </c>
       <c r="D5" t="n">
-        <v>17625122.54</v>
+        <v>33396067.58</v>
       </c>
       <c r="E5" t="n">
-        <v>2341056.61</v>
+        <v>4383763.2</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>304757.64</v>
+        <v>6279120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>241927.56</v>
+        <v>433944.97</v>
       </c>
       <c r="L5" t="n">
-        <v>68841.36</v>
+        <v>1315440</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>1238846.4</v>
       </c>
       <c r="C6" t="n">
-        <v>7833672</v>
+        <v>5982076.8</v>
       </c>
       <c r="D6" t="n">
-        <v>6388087.2</v>
+        <v>12104142.34</v>
       </c>
       <c r="E6" t="n">
-        <v>1204984.87</v>
+        <v>2256403.5</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5883</v>
+        <v>17172</v>
       </c>
       <c r="H6" t="n">
-        <v>179767.17</v>
+        <v>3703860</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>110936.8</v>
+        <v>196943.14</v>
       </c>
       <c r="L6" t="n">
-        <v>30322.98</v>
+        <v>579420</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,22 +9684,22 @@
         <v>384852.6</v>
       </c>
       <c r="C7" t="n">
-        <v>3742200</v>
+        <v>2857680</v>
       </c>
       <c r="D7" t="n">
-        <v>3456110.95</v>
+        <v>6548636.16</v>
       </c>
       <c r="E7" t="n">
-        <v>529035.95</v>
+        <v>990650.25</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5661</v>
+        <v>16524</v>
       </c>
       <c r="H7" t="n">
-        <v>36351.81</v>
+        <v>748980</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>52481.64</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>18142.92</v>
+        <v>346680</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,19 +9725,19 @@
         <v>137412</v>
       </c>
       <c r="C8" t="n">
-        <v>748440</v>
+        <v>571536</v>
       </c>
       <c r="D8" t="n">
-        <v>797397.38</v>
+        <v>1510907.9</v>
       </c>
       <c r="E8" t="n">
-        <v>122023.99</v>
+        <v>228496.95</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4689.75</v>
+        <v>13689</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -9084,10 +9749,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>19200.6</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>8828.42</v>
+        <v>168696</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>81150</v>
+        <v>81210</v>
       </c>
       <c r="H4" t="n">
-        <v>8910</v>
+        <v>8880</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -9867,7 +10592,10 @@
         <v>235</v>
       </c>
       <c r="L4" t="n">
-        <v>192690</v>
+        <v>193230</v>
+      </c>
+      <c r="M4" t="n">
+        <v>16890</v>
       </c>
     </row>
     <row r="5">
@@ -9890,7 +10618,7 @@
         <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>83460</v>
+        <v>83490</v>
       </c>
       <c r="H5" t="n">
         <v>7440</v>
@@ -9905,7 +10633,10 @@
         <v>167</v>
       </c>
       <c r="L5" t="n">
-        <v>186450</v>
+        <v>186390</v>
+      </c>
+      <c r="M5" t="n">
+        <v>18450</v>
       </c>
     </row>
     <row r="6">
@@ -9928,10 +10659,10 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>86190</v>
+        <v>86220</v>
       </c>
       <c r="H6" t="n">
-        <v>12180</v>
+        <v>12150</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -9943,7 +10674,10 @@
         <v>217</v>
       </c>
       <c r="L6" t="n">
-        <v>208890</v>
+        <v>208980</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11100</v>
       </c>
     </row>
     <row r="7">
@@ -9966,10 +10700,10 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>66240</v>
+        <v>66270</v>
       </c>
       <c r="H7" t="n">
-        <v>4500</v>
+        <v>4530</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -9981,7 +10715,10 @@
         <v>138</v>
       </c>
       <c r="L7" t="n">
-        <v>143100</v>
+        <v>143190</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7020</v>
       </c>
     </row>
     <row r="8">
@@ -10004,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>35550</v>
+        <v>35610</v>
       </c>
       <c r="H8" t="n">
         <v>600</v>
@@ -10019,7 +10756,10 @@
         <v>89</v>
       </c>
       <c r="L8" t="n">
-        <v>84780</v>
+        <v>84840</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3630</v>
       </c>
     </row>
     <row r="9">
@@ -10042,7 +10782,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>28230</v>
+        <v>28290</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10054,10 +10794,13 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L9" t="n">
         <v>43950</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2220</v>
       </c>
     </row>
     <row r="10">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>11940</v>
       </c>
+      <c r="M10" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>5040</v>
       </c>
+      <c r="M11" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>3540</v>
       </c>
+      <c r="M12" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>1920</v>
       </c>
+      <c r="M13" t="n">
+        <v>480</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>990</v>
       </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>360</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>330</v>
       </c>
+      <c r="M17" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>660</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>120</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>48862.68</v>
+        <v>48788.81</v>
       </c>
       <c r="C5" t="n">
         <v>10555498.8</v>
@@ -10828,16 +11628,19 @@
         <v>17766</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>7.8</v>
       </c>
       <c r="K5" t="n">
-        <v>235.62</v>
+        <v>182.38</v>
       </c>
       <c r="L5" t="n">
-        <v>175631.4</v>
+        <v>175209.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>970.2</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>67386.38</v>
+        <v>67268.52</v>
       </c>
       <c r="C6" t="n">
         <v>12579688.8</v>
@@ -10860,22 +11663,25 @@
         <v>4.9</v>
       </c>
       <c r="G6" t="n">
-        <v>12270</v>
+        <v>12232.5</v>
       </c>
       <c r="H6" t="n">
         <v>29497.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>319.15</v>
+        <v>248.43</v>
       </c>
       <c r="L6" t="n">
-        <v>229192.8</v>
+        <v>228549</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2404.8</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>67279.86</v>
+        <v>67234.98</v>
       </c>
       <c r="C7" t="n">
         <v>8814960</v>
@@ -10898,22 +11704,25 @@
         <v>19.8</v>
       </c>
       <c r="G7" t="n">
-        <v>29425.5</v>
+        <v>29358</v>
       </c>
       <c r="H7" t="n">
         <v>23827.2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="J7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>323.9</v>
+        <v>252.01</v>
       </c>
       <c r="L7" t="n">
-        <v>296478</v>
+        <v>295884</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7213.5</v>
       </c>
     </row>
     <row r="8">
@@ -10921,7 +11730,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>61194.78</v>
+        <v>61194.15</v>
       </c>
       <c r="C8" t="n">
         <v>6895728</v>
@@ -10936,22 +11745,25 @@
         <v>17.1</v>
       </c>
       <c r="G8" t="n">
-        <v>101439</v>
+        <v>101146.5</v>
       </c>
       <c r="H8" t="n">
         <v>9358.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>303.3</v>
+        <v>248.03</v>
       </c>
       <c r="L8" t="n">
-        <v>282225</v>
+        <v>281713.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8064</v>
       </c>
     </row>
     <row r="9">
@@ -10974,7 +11786,7 @@
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>129999</v>
+        <v>129718.5</v>
       </c>
       <c r="H9" t="n">
         <v>3780</v>
@@ -10986,10 +11798,13 @@
         <v>9.5</v>
       </c>
       <c r="K9" t="n">
-        <v>280</v>
+        <v>224.84</v>
       </c>
       <c r="L9" t="n">
-        <v>255806.1</v>
+        <v>255514.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10080</v>
       </c>
     </row>
     <row r="10">
@@ -10997,7 +11812,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>34246.89</v>
+        <v>34246.62</v>
       </c>
       <c r="C10" t="n">
         <v>3190824</v>
@@ -11018,16 +11833,19 @@
         <v>4290</v>
       </c>
       <c r="I10" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>175</v>
+        <v>152.25</v>
       </c>
       <c r="L10" t="n">
-        <v>171387.3</v>
+        <v>171307.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6810</v>
       </c>
     </row>
     <row r="11">
@@ -11035,7 +11853,7 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>24060.06</v>
+        <v>24059.97</v>
       </c>
       <c r="C11" t="n">
         <v>1797768</v>
@@ -11056,16 +11874,19 @@
         <v>5640</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>117</v>
+        <v>105.12</v>
       </c>
       <c r="L11" t="n">
-        <v>163770</v>
+        <v>163500</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4410</v>
       </c>
     </row>
     <row r="12">
@@ -11100,10 +11921,13 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>82</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>120780</v>
+        <v>120570</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3180</v>
       </c>
     </row>
     <row r="13">
@@ -11132,16 +11956,19 @@
         <v>840</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>34</v>
+        <v>32.28</v>
       </c>
       <c r="L13" t="n">
         <v>49500</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2310</v>
       </c>
     </row>
     <row r="14">
@@ -11176,10 +12003,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>12.64</v>
       </c>
       <c r="L14" t="n">
         <v>23880</v>
+      </c>
+      <c r="M14" t="n">
+        <v>960</v>
       </c>
     </row>
     <row r="15">
@@ -11214,10 +12044,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="L15" t="n">
         <v>10230</v>
+      </c>
+      <c r="M15" t="n">
+        <v>960</v>
       </c>
     </row>
     <row r="16">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>3000</v>
       </c>
+      <c r="M16" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>1860</v>
       </c>
+      <c r="M17" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>3810</v>
       </c>
+      <c r="M18" t="n">
+        <v>2940</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>1200</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>30</v>
       </c>
+      <c r="M20" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11760,16 +12632,19 @@
         <v>2678.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>70.14</v>
+        <v>55.28</v>
       </c>
       <c r="L5" t="n">
-        <v>39154.5</v>
+        <v>39141.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>369</v>
       </c>
     </row>
     <row r="6">
@@ -11792,22 +12667,25 @@
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>4309.5</v>
+        <v>4311</v>
       </c>
       <c r="H6" t="n">
-        <v>6942.6</v>
+        <v>6925.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>141.05</v>
+        <v>110.02</v>
       </c>
       <c r="L6" t="n">
-        <v>77289.3</v>
+        <v>77322.60000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>888</v>
       </c>
     </row>
     <row r="7">
@@ -11830,22 +12708,25 @@
         <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>9936</v>
+        <v>9940.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3285</v>
+        <v>3306.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>113.16</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>85860</v>
+        <v>85914</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2457</v>
       </c>
     </row>
     <row r="8">
@@ -11868,7 +12749,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>23107.5</v>
+        <v>23146.5</v>
       </c>
       <c r="H8" t="n">
         <v>510</v>
@@ -11880,10 +12761,13 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>80.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="L8" t="n">
-        <v>60193.8</v>
+        <v>60236.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2178</v>
       </c>
     </row>
     <row r="9">
@@ -11906,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>23995.5</v>
+        <v>24046.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11918,10 +12802,13 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>54</v>
+        <v>44.16</v>
       </c>
       <c r="L9" t="n">
         <v>35599.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2220</v>
       </c>
     </row>
     <row r="10">
@@ -11950,16 +12837,19 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>7.83</v>
       </c>
       <c r="L10" t="n">
         <v>10626.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1170</v>
       </c>
     </row>
     <row r="11">
@@ -11994,10 +12884,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>5040</v>
+      </c>
+      <c r="M11" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="12">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>3540</v>
       </c>
+      <c r="M12" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>1920</v>
       </c>
+      <c r="M13" t="n">
+        <v>480</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>990</v>
       </c>
+      <c r="M14" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>360</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>330</v>
       </c>
+      <c r="M17" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>660</v>
       </c>
+      <c r="M18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>120</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>28551025.8</v>
       </c>
       <c r="C5" t="n">
-        <v>138022038</v>
+        <v>105398647.2</v>
       </c>
       <c r="D5" t="n">
-        <v>120241322.07</v>
+        <v>227833157.38</v>
       </c>
       <c r="E5" t="n">
-        <v>21362141.61</v>
+        <v>40001839.2</v>
       </c>
       <c r="F5" t="n">
         <v>17500.14</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>740979.36</v>
+        <v>15266880</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>192498.9</v>
+        <v>80117.39999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1496366.76</v>
+        <v>2684030.01</v>
       </c>
       <c r="L5" t="n">
-        <v>368835.39</v>
+        <v>7045542</v>
+      </c>
+      <c r="M5" t="n">
+        <v>110700</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>61054329.6</v>
       </c>
       <c r="C6" t="n">
-        <v>243567324</v>
+        <v>185996865.6</v>
       </c>
       <c r="D6" t="n">
-        <v>198620685.86</v>
+        <v>376346310.91</v>
       </c>
       <c r="E6" t="n">
-        <v>29031728.54</v>
+        <v>54363582</v>
       </c>
       <c r="F6" t="n">
         <v>12500.1</v>
       </c>
       <c r="G6" t="n">
-        <v>79725.75</v>
+        <v>232794</v>
       </c>
       <c r="H6" t="n">
-        <v>1920670.29</v>
+        <v>39475350</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>3009160.7</v>
+        <v>5342082.56</v>
       </c>
       <c r="L6" t="n">
-        <v>728065.21</v>
+        <v>13918068</v>
+      </c>
+      <c r="M6" t="n">
+        <v>266400</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>59919066.9</v>
       </c>
       <c r="C7" t="n">
-        <v>138516840</v>
+        <v>105776496</v>
       </c>
       <c r="D7" t="n">
-        <v>127927306.73</v>
+        <v>242396554.75</v>
       </c>
       <c r="E7" t="n">
-        <v>11568252.73</v>
+        <v>21662218.8</v>
       </c>
       <c r="F7" t="n">
         <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>183816</v>
+        <v>536787</v>
       </c>
       <c r="H7" t="n">
-        <v>908795.25</v>
+        <v>18849330</v>
       </c>
       <c r="I7" t="n">
-        <v>632494.5</v>
+        <v>371744.74</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2414155.44</v>
+        <v>4275064.46</v>
       </c>
       <c r="L7" t="n">
-        <v>808801.2</v>
+        <v>15464520</v>
+      </c>
+      <c r="M7" t="n">
+        <v>737100</v>
       </c>
     </row>
     <row r="8">
@@ -12788,34 +13741,37 @@
         <v>51724926</v>
       </c>
       <c r="C8" t="n">
-        <v>96853680</v>
+        <v>73960992</v>
       </c>
       <c r="D8" t="n">
-        <v>103189128.26</v>
+        <v>195522674.69</v>
       </c>
       <c r="E8" t="n">
-        <v>6792669.02</v>
+        <v>12719663.55</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>427488.75</v>
+        <v>1249911</v>
       </c>
       <c r="H8" t="n">
-        <v>141091.5</v>
+        <v>2907000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1708853.4</v>
+        <v>3180612.22</v>
       </c>
       <c r="L8" t="n">
-        <v>567025.6</v>
+        <v>10842552</v>
+      </c>
+      <c r="M8" t="n">
+        <v>653400</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>33511500</v>
       </c>
       <c r="C9" t="n">
-        <v>54081720</v>
+        <v>41298768</v>
       </c>
       <c r="D9" t="n">
-        <v>62864583.6</v>
+        <v>119115760.9</v>
       </c>
       <c r="E9" t="n">
-        <v>2752114.48</v>
+        <v>5153492.7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>443916.75</v>
+        <v>1298511</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12847,13 +13803,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1152036</v>
+        <v>2144475.74</v>
       </c>
       <c r="L9" t="n">
-        <v>335347.29</v>
+        <v>6407910</v>
+      </c>
+      <c r="M9" t="n">
+        <v>666000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,34 +13823,37 @@
         <v>4875156</v>
       </c>
       <c r="C10" t="n">
-        <v>8482320</v>
+        <v>6477408</v>
       </c>
       <c r="D10" t="n">
-        <v>10682524.75</v>
+        <v>20241239.04</v>
       </c>
       <c r="E10" t="n">
-        <v>480866.4</v>
+        <v>900450</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>57165</v>
+        <v>166860</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>367996.8</v>
+        <v>168974.88</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>192006</v>
+        <v>380193.48</v>
       </c>
       <c r="L10" t="n">
-        <v>100102.57</v>
+        <v>1912788</v>
+      </c>
+      <c r="M10" t="n">
+        <v>351000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,22 +13864,22 @@
         <v>876546</v>
       </c>
       <c r="C11" t="n">
-        <v>2827440</v>
+        <v>2159136</v>
       </c>
       <c r="D11" t="n">
-        <v>3677489.84</v>
+        <v>6968104.7</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>127242.9</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>24420</v>
+        <v>71280</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12926,10 +13888,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>42668</v>
+        <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>47476.8</v>
+        <v>907200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,19 +13905,19 @@
         <v>422334</v>
       </c>
       <c r="C12" t="n">
-        <v>637560</v>
+        <v>486864</v>
       </c>
       <c r="D12" t="n">
-        <v>855540.9399999999</v>
+        <v>1621078.27</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>5550</v>
+        <v>16200</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>33346.8</v>
+        <v>637200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>81000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>300564</v>
       </c>
       <c r="C13" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D13" t="n">
-        <v>266701.98</v>
+        <v>505346.69</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>7215</v>
+        <v>21060</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>18086.4</v>
+        <v>345600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>144000</v>
       </c>
     </row>
     <row r="14">
@@ -13016,19 +13987,19 @@
         <v>30690</v>
       </c>
       <c r="C14" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D14" t="n">
-        <v>195015.66</v>
+        <v>369515.52</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>9325.799999999999</v>
+        <v>178200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>37620</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13081,7 +14055,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3391.2</v>
+        <v>64800</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="16">
@@ -13092,10 +14069,10 @@
         <v>24552</v>
       </c>
       <c r="C16" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D16" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13119,7 +14096,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="17">
@@ -13130,10 +14110,10 @@
         <v>11682</v>
       </c>
       <c r="C17" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D17" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13142,7 +14122,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13154,10 +14134,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L17" t="n">
-        <v>3108.6</v>
+        <v>59400</v>
+      </c>
+      <c r="M17" t="n">
+        <v>81000</v>
       </c>
     </row>
     <row r="18">
@@ -13168,10 +14151,10 @@
         <v>6534</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13180,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13195,7 +14178,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>6217.2</v>
+        <v>118800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="19">
@@ -13206,10 +14192,10 @@
         <v>396</v>
       </c>
       <c r="C19" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D19" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13218,7 +14204,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>68820</v>
+        <v>200880</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13233,7 +14219,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D20" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D24" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>89010</v>
+        <v>89070</v>
       </c>
       <c r="H4" t="n">
         <v>10320</v>
@@ -13595,7 +14608,10 @@
         <v>102</v>
       </c>
       <c r="L4" t="n">
-        <v>287370</v>
+        <v>289500</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13618,7 +14634,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>20160</v>
+        <v>20280</v>
       </c>
       <c r="H5" t="n">
         <v>2010</v>
@@ -13633,7 +14649,10 @@
         <v>20</v>
       </c>
       <c r="L5" t="n">
-        <v>85080</v>
+        <v>85830</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2100</v>
+        <v>2130</v>
       </c>
       <c r="H6" t="n">
         <v>300</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12750</v>
+        <v>12930</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>1230</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>210</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>60</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>150</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>90</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.4</v>
+        <v>6.62</v>
       </c>
       <c r="L5" t="n">
-        <v>17866.8</v>
+        <v>18024.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>106.5</v>
       </c>
       <c r="H6" t="n">
         <v>171</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4717.5</v>
+        <v>4784.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>738</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>149.1</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>48.6</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>133.5</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>90</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>8478310.5</v>
       </c>
       <c r="C5" t="n">
-        <v>17532900</v>
+        <v>13388760</v>
       </c>
       <c r="D5" t="n">
-        <v>15274220.74</v>
+        <v>28941580.8</v>
       </c>
       <c r="E5" t="n">
-        <v>4371191.65</v>
+        <v>8185307.85</v>
       </c>
       <c r="F5" t="n">
         <v>5833.38</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>200183.94</v>
+        <v>4124520</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>179205.6</v>
+        <v>321440.72</v>
       </c>
       <c r="L5" t="n">
-        <v>168305.26</v>
+        <v>3244374</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>1333094.4</v>
       </c>
       <c r="C6" t="n">
-        <v>3243240</v>
+        <v>2476656</v>
       </c>
       <c r="D6" t="n">
-        <v>2644749.48</v>
+        <v>5011269.12</v>
       </c>
       <c r="E6" t="n">
-        <v>644526.79</v>
+        <v>1206913.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1942.5</v>
+        <v>5751</v>
       </c>
       <c r="H6" t="n">
-        <v>47307.15</v>
+        <v>974700</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>44438.85</v>
+        <v>861138</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>229670.1</v>
       </c>
       <c r="C7" t="n">
-        <v>776160</v>
+        <v>592704</v>
       </c>
       <c r="D7" t="n">
-        <v>716823.01</v>
+        <v>1358235.65</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>166.5</v>
+        <v>486</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6951.96</v>
+        <v>132840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1404.52</v>
+        <v>26838</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>457.81</v>
+        <v>8748</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1257.57</v>
+        <v>24030</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>107497902.6</v>
+        <v>107335384.2</v>
       </c>
       <c r="C5" t="n">
-        <v>580552434</v>
+        <v>443330949.6</v>
       </c>
       <c r="D5" t="n">
-        <v>505762653.6</v>
+        <v>958318656.77</v>
       </c>
       <c r="E5" t="n">
-        <v>97922008.7</v>
+        <v>183364595.1</v>
       </c>
       <c r="F5" t="n">
         <v>71667.24000000001</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4914963.9</v>
+        <v>101266200</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>454997.4</v>
+        <v>189368.4</v>
       </c>
       <c r="K5" t="n">
-        <v>5026717.08</v>
+        <v>8855691.84</v>
       </c>
       <c r="L5" t="n">
-        <v>1654447.79</v>
+        <v>31537674</v>
+      </c>
+      <c r="M5" t="n">
+        <v>291060</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>148250044.8</v>
+        <v>147990744</v>
       </c>
       <c r="C6" t="n">
-        <v>691882884</v>
+        <v>528346929.6</v>
       </c>
       <c r="D6" t="n">
-        <v>564206440.74</v>
+        <v>1069057896.19</v>
       </c>
       <c r="E6" t="n">
-        <v>111615226.63</v>
+        <v>209005933.5</v>
       </c>
       <c r="F6" t="n">
         <v>204168.3</v>
       </c>
       <c r="G6" t="n">
-        <v>226995</v>
+        <v>660555</v>
       </c>
       <c r="H6" t="n">
-        <v>8160483.37</v>
+        <v>168135750</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>262498.5</v>
+        <v>109251</v>
       </c>
       <c r="K6" t="n">
-        <v>6808746.1</v>
+        <v>12062767.08</v>
       </c>
       <c r="L6" t="n">
-        <v>2158996.18</v>
+        <v>41138820</v>
+      </c>
+      <c r="M6" t="n">
+        <v>721440</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>148015701.9</v>
+        <v>147916949.4</v>
       </c>
       <c r="C7" t="n">
-        <v>484822800</v>
+        <v>370228320</v>
       </c>
       <c r="D7" t="n">
-        <v>447758373.98</v>
+        <v>848412195.84</v>
       </c>
       <c r="E7" t="n">
-        <v>95367546.89</v>
+        <v>178581218.4</v>
       </c>
       <c r="F7" t="n">
         <v>825006.6</v>
       </c>
       <c r="G7" t="n">
-        <v>544371.75</v>
+        <v>1585332</v>
       </c>
       <c r="H7" t="n">
-        <v>6591794.88</v>
+        <v>135815040</v>
       </c>
       <c r="I7" t="n">
-        <v>843326</v>
+        <v>495659.65</v>
       </c>
       <c r="J7" t="n">
-        <v>571663.4</v>
+        <v>237924.4</v>
       </c>
       <c r="K7" t="n">
-        <v>6910082.6</v>
+        <v>12236597.56</v>
       </c>
       <c r="L7" t="n">
-        <v>2792822.76</v>
+        <v>53259120</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2164050</v>
       </c>
     </row>
     <row r="8">
@@ -16513,37 +17754,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>134628516</v>
+        <v>134627130</v>
       </c>
       <c r="C8" t="n">
-        <v>379265040</v>
+        <v>289620576</v>
       </c>
       <c r="D8" t="n">
-        <v>404073741.52</v>
+        <v>765638590.46</v>
       </c>
       <c r="E8" t="n">
-        <v>87043782.67</v>
+        <v>162994491</v>
       </c>
       <c r="F8" t="n">
         <v>712505.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1876621.5</v>
+        <v>5461911</v>
       </c>
       <c r="H8" t="n">
-        <v>2589029.02</v>
+        <v>53343450</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>247915.25</v>
+        <v>103181.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6470602.2</v>
+        <v>12043441.79</v>
       </c>
       <c r="L8" t="n">
-        <v>2658559.5</v>
+        <v>50708484</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2419200</v>
       </c>
     </row>
     <row r="9">
@@ -16554,34 +17798,37 @@
         <v>115525476</v>
       </c>
       <c r="C9" t="n">
-        <v>319195800</v>
+        <v>243749520</v>
       </c>
       <c r="D9" t="n">
-        <v>371033152.32</v>
+        <v>703033309.4400001</v>
       </c>
       <c r="E9" t="n">
-        <v>68314583.58</v>
+        <v>127922988.15</v>
       </c>
       <c r="F9" t="n">
         <v>916674</v>
       </c>
       <c r="G9" t="n">
-        <v>2404981.5</v>
+        <v>7004799</v>
       </c>
       <c r="H9" t="n">
-        <v>1045737</v>
+        <v>21546000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>554163.5</v>
+        <v>230641</v>
       </c>
       <c r="K9" t="n">
-        <v>5973520</v>
+        <v>10917331.04</v>
       </c>
       <c r="L9" t="n">
-        <v>2409693.46</v>
+        <v>45992610</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3024000</v>
       </c>
     </row>
     <row r="10">
@@ -16589,37 +17836,40 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>75343158</v>
+        <v>75342564</v>
       </c>
       <c r="C10" t="n">
-        <v>175495320</v>
+        <v>134014608</v>
       </c>
       <c r="D10" t="n">
-        <v>221016549.64</v>
+        <v>418781975.04</v>
       </c>
       <c r="E10" t="n">
-        <v>44864835.12</v>
+        <v>84011985</v>
       </c>
       <c r="F10" t="n">
         <v>1166676</v>
       </c>
       <c r="G10" t="n">
-        <v>1571760</v>
+        <v>4587840</v>
       </c>
       <c r="H10" t="n">
-        <v>1186828.5</v>
+        <v>24453000</v>
       </c>
       <c r="I10" t="n">
-        <v>735993.6</v>
+        <v>337949.76</v>
       </c>
       <c r="J10" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>3733450</v>
+        <v>7392651</v>
       </c>
       <c r="L10" t="n">
-        <v>1614468.37</v>
+        <v>30835296</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2043000</v>
       </c>
     </row>
     <row r="11">
@@ -16627,37 +17877,40 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>52932132</v>
+        <v>52931934</v>
       </c>
       <c r="C11" t="n">
-        <v>98877240</v>
+        <v>75506256</v>
       </c>
       <c r="D11" t="n">
-        <v>128603983</v>
+        <v>243678720.38</v>
       </c>
       <c r="E11" t="n">
-        <v>33092330.24</v>
+        <v>61967292.3</v>
       </c>
       <c r="F11" t="n">
         <v>625005</v>
       </c>
       <c r="G11" t="n">
-        <v>1181040</v>
+        <v>3447360</v>
       </c>
       <c r="H11" t="n">
-        <v>1560306</v>
+        <v>32148000</v>
       </c>
       <c r="I11" t="n">
-        <v>383330</v>
+        <v>174510.26</v>
       </c>
       <c r="J11" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>2496078</v>
+        <v>5104425.22</v>
       </c>
       <c r="L11" t="n">
-        <v>1542713.4</v>
+        <v>29430000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1323000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,34 +17921,37 @@
         <v>38462688</v>
       </c>
       <c r="C12" t="n">
-        <v>57408120</v>
+        <v>43838928</v>
       </c>
       <c r="D12" t="n">
-        <v>77035882.42</v>
+        <v>145967526.14</v>
       </c>
       <c r="E12" t="n">
-        <v>18229811.04</v>
+        <v>34136370</v>
       </c>
       <c r="F12" t="n">
         <v>416670</v>
       </c>
       <c r="G12" t="n">
-        <v>934065</v>
+        <v>2726460</v>
       </c>
       <c r="H12" t="n">
-        <v>531168</v>
+        <v>10944000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>1749388</v>
+        <v>3690935.78</v>
       </c>
       <c r="L12" t="n">
-        <v>1137747.6</v>
+        <v>21702600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>954000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,34 +17962,37 @@
         <v>21125016</v>
       </c>
       <c r="C13" t="n">
-        <v>23783760</v>
+        <v>18162144</v>
       </c>
       <c r="D13" t="n">
-        <v>32690042.52</v>
+        <v>61941065.47</v>
       </c>
       <c r="E13" t="n">
-        <v>9125982.029999999</v>
+        <v>17088926.4</v>
       </c>
       <c r="F13" t="n">
         <v>208335</v>
       </c>
       <c r="G13" t="n">
-        <v>572205</v>
+        <v>1670220</v>
       </c>
       <c r="H13" t="n">
-        <v>232386</v>
+        <v>4788000</v>
       </c>
       <c r="I13" t="n">
-        <v>383330</v>
+        <v>184415.69</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>725356</v>
+        <v>1567533.35</v>
       </c>
       <c r="L13" t="n">
-        <v>466290</v>
+        <v>8910000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>693000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,22 +18003,22 @@
         <v>7747146</v>
       </c>
       <c r="C14" t="n">
-        <v>13361040</v>
+        <v>10202976</v>
       </c>
       <c r="D14" t="n">
-        <v>18799510.09</v>
+        <v>35621296.13</v>
       </c>
       <c r="E14" t="n">
-        <v>4531154.34</v>
+        <v>8484847.199999999</v>
       </c>
       <c r="F14" t="n">
         <v>166668</v>
       </c>
       <c r="G14" t="n">
-        <v>181485</v>
+        <v>529740</v>
       </c>
       <c r="H14" t="n">
-        <v>124492.5</v>
+        <v>2565000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -16768,10 +18027,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>277342</v>
+        <v>613553.62</v>
       </c>
       <c r="L14" t="n">
-        <v>224949.6</v>
+        <v>4298400</v>
+      </c>
+      <c r="M14" t="n">
+        <v>288000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,22 +18044,22 @@
         <v>4665672</v>
       </c>
       <c r="C15" t="n">
-        <v>4573800</v>
+        <v>3492720</v>
       </c>
       <c r="D15" t="n">
-        <v>6528209.57</v>
+        <v>12369646.08</v>
       </c>
       <c r="E15" t="n">
-        <v>1285389.05</v>
+        <v>2406964.95</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>76035</v>
+        <v>221940</v>
       </c>
       <c r="H15" t="n">
-        <v>33198</v>
+        <v>684000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -16806,10 +18068,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>85336</v>
+        <v>191504.86</v>
       </c>
       <c r="L15" t="n">
-        <v>96366.60000000001</v>
+        <v>1841400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>288000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,22 +18085,22 @@
         <v>2479554</v>
       </c>
       <c r="C16" t="n">
-        <v>1330560</v>
+        <v>1016064</v>
       </c>
       <c r="D16" t="n">
-        <v>1926080.64</v>
+        <v>3649536</v>
       </c>
       <c r="E16" t="n">
-        <v>310059.34</v>
+        <v>580603.95</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>32190</v>
+        <v>93960</v>
       </c>
       <c r="H16" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -16844,10 +18109,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>42668</v>
+        <v>97112</v>
       </c>
       <c r="L16" t="n">
-        <v>28260</v>
+        <v>540000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="17">
@@ -16858,22 +18126,22 @@
         <v>1094940</v>
       </c>
       <c r="C17" t="n">
-        <v>637560</v>
+        <v>486864</v>
       </c>
       <c r="D17" t="n">
-        <v>922913.64</v>
+        <v>1748736</v>
       </c>
       <c r="E17" t="n">
-        <v>123234.45</v>
+        <v>230763.6</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -16882,10 +18150,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>42668</v>
+        <v>97112</v>
       </c>
       <c r="L17" t="n">
-        <v>17521.2</v>
+        <v>334800</v>
+      </c>
+      <c r="M17" t="n">
+        <v>198000</v>
       </c>
     </row>
     <row r="18">
@@ -16896,22 +18167,22 @@
         <v>538362</v>
       </c>
       <c r="C18" t="n">
-        <v>748440</v>
+        <v>571536</v>
       </c>
       <c r="D18" t="n">
-        <v>1083420.36</v>
+        <v>2052864</v>
       </c>
       <c r="E18" t="n">
-        <v>134526.52</v>
+        <v>251908.65</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>5550</v>
+        <v>16200</v>
       </c>
       <c r="H18" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -16923,7 +18194,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>35890.2</v>
+        <v>685800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>882000</v>
       </c>
     </row>
     <row r="19">
@@ -16934,10 +18208,10 @@
         <v>240966</v>
       </c>
       <c r="C19" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D19" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16946,7 +18220,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>70485</v>
+        <v>205740</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -16961,7 +18235,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>11304</v>
+        <v>216000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="20">
@@ -16972,10 +18249,10 @@
         <v>40986</v>
       </c>
       <c r="C20" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D20" t="n">
-        <v>200633.4</v>
+        <v>380160</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16987,7 +18264,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -16999,7 +18276,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M20" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="21">
@@ -17039,6 +18319,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17048,10 +18331,10 @@
         <v>14454</v>
       </c>
       <c r="C22" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D22" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17076,6 +18359,9 @@
       </c>
       <c r="L22" t="n">
         <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="23">
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>304920</v>
+        <v>232848</v>
       </c>
       <c r="D24" t="n">
-        <v>441393.48</v>
+        <v>836352</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>12616.92</v>
+        <v>12517.74</v>
       </c>
       <c r="C4" t="n">
         <v>3054240</v>
@@ -17308,7 +18609,7 @@
         <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>55710</v>
+        <v>53280</v>
       </c>
       <c r="H4" t="n">
         <v>7410</v>
@@ -17320,10 +18621,13 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L4" t="n">
-        <v>157080</v>
+        <v>153990</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32850</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>19994.04</v>
+        <v>19928.7</v>
       </c>
       <c r="C5" t="n">
         <v>3345048</v>
@@ -17346,7 +18650,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>66030</v>
+        <v>65040</v>
       </c>
       <c r="H5" t="n">
         <v>11940</v>
@@ -17358,10 +18662,13 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="L5" t="n">
-        <v>180060</v>
+        <v>178620</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13800</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>24517.89</v>
+        <v>24494.31</v>
       </c>
       <c r="C6" t="n">
         <v>3666096</v>
@@ -17384,7 +18691,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>65280</v>
+        <v>64710</v>
       </c>
       <c r="H6" t="n">
         <v>13020</v>
@@ -17396,10 +18703,13 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L6" t="n">
-        <v>186090</v>
+        <v>185550</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6240</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>24495.03</v>
+        <v>24492.42</v>
       </c>
       <c r="C7" t="n">
         <v>3989664</v>
@@ -17422,10 +18732,10 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>82260</v>
+        <v>81990</v>
       </c>
       <c r="H7" t="n">
-        <v>20940</v>
+        <v>20970</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -17437,7 +18747,10 @@
         <v>201</v>
       </c>
       <c r="L7" t="n">
-        <v>233910</v>
+        <v>232980</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4950</v>
       </c>
     </row>
     <row r="8">
@@ -17445,7 +18758,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27112.68</v>
+        <v>27112.23</v>
       </c>
       <c r="C8" t="n">
         <v>4039560</v>
@@ -17460,7 +18773,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>94200</v>
+        <v>93780</v>
       </c>
       <c r="H8" t="n">
         <v>5940</v>
@@ -17475,7 +18788,10 @@
         <v>218</v>
       </c>
       <c r="L8" t="n">
-        <v>242610</v>
+        <v>241890</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3990</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>98610</v>
+        <v>98310</v>
       </c>
       <c r="H9" t="n">
         <v>780</v>
@@ -17513,7 +18829,10 @@
         <v>202</v>
       </c>
       <c r="L9" t="n">
-        <v>215190</v>
+        <v>214890</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4740</v>
       </c>
     </row>
     <row r="10">
@@ -17551,7 +18870,10 @@
         <v>140</v>
       </c>
       <c r="L10" t="n">
-        <v>127260</v>
+        <v>127290</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3510</v>
       </c>
     </row>
     <row r="11">
@@ -17589,7 +18911,10 @@
         <v>77</v>
       </c>
       <c r="L11" t="n">
-        <v>70410</v>
+        <v>70140</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2700</v>
       </c>
     </row>
     <row r="12">
@@ -17624,10 +18949,13 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L12" t="n">
-        <v>35760</v>
+        <v>35610</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="13">
@@ -17650,7 +18978,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>10860</v>
+        <v>10890</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -17665,7 +18993,10 @@
         <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>10620</v>
+        <v>10650</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1320</v>
       </c>
     </row>
     <row r="14">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>4770</v>
       </c>
+      <c r="M14" t="n">
+        <v>570</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>1080</v>
       </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>330</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>150</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>240</v>
       </c>
+      <c r="M18" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>8997.32</v>
+        <v>8967.92</v>
       </c>
       <c r="C5" t="n">
         <v>1839776.4</v>
@@ -18290,10 +19666,13 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>65.09999999999999</v>
+        <v>48</v>
       </c>
       <c r="L5" t="n">
-        <v>37812.6</v>
+        <v>37510.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>19614.31</v>
+        <v>19595.45</v>
       </c>
       <c r="C6" t="n">
         <v>3299486.4</v>
@@ -18316,7 +19695,7 @@
         <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3264</v>
+        <v>3235.5</v>
       </c>
       <c r="H6" t="n">
         <v>7421.4</v>
@@ -18328,10 +19707,13 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>94.90000000000001</v>
+        <v>73.52</v>
       </c>
       <c r="L6" t="n">
-        <v>68853.3</v>
+        <v>68653.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>499.2</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>23270.28</v>
+        <v>23267.8</v>
       </c>
       <c r="C7" t="n">
         <v>3989664</v>
@@ -18354,22 +19736,25 @@
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>12339</v>
+        <v>12298.5</v>
       </c>
       <c r="H7" t="n">
-        <v>15286.2</v>
+        <v>15308.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>164.82</v>
+        <v>128.24</v>
       </c>
       <c r="L7" t="n">
-        <v>140346</v>
+        <v>139788</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1732.5</v>
       </c>
     </row>
     <row r="8">
@@ -18377,7 +19762,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27112.68</v>
+        <v>27112.23</v>
       </c>
       <c r="C8" t="n">
         <v>4039560</v>
@@ -18392,7 +19777,7 @@
         <v>9.5</v>
       </c>
       <c r="G8" t="n">
-        <v>61230</v>
+        <v>60957</v>
       </c>
       <c r="H8" t="n">
         <v>5049</v>
@@ -18404,10 +19789,13 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>196.2</v>
+        <v>160.45</v>
       </c>
       <c r="L8" t="n">
-        <v>172253.1</v>
+        <v>171741.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2394</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>83818.5</v>
+        <v>83563.5</v>
       </c>
       <c r="H9" t="n">
         <v>780</v>
@@ -18442,10 +19830,13 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>202</v>
+        <v>162.21</v>
       </c>
       <c r="L9" t="n">
-        <v>174303.9</v>
+        <v>174060.9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4740</v>
       </c>
     </row>
     <row r="10">
@@ -18480,10 +19871,13 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>140</v>
+        <v>121.8</v>
       </c>
       <c r="L10" t="n">
-        <v>113261.4</v>
+        <v>113288.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3510</v>
       </c>
     </row>
     <row r="11">
@@ -18518,10 +19912,13 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>77</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>70410</v>
+        <v>70140</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2700</v>
       </c>
     </row>
     <row r="12">
@@ -18556,10 +19953,13 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>43</v>
+        <v>40.79</v>
       </c>
       <c r="L12" t="n">
-        <v>35760</v>
+        <v>35610</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="13">
@@ -18582,7 +19982,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>10860</v>
+        <v>10890</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -18594,10 +19994,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>10.44</v>
       </c>
       <c r="L13" t="n">
-        <v>10620</v>
+        <v>10650</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1320</v>
       </c>
     </row>
     <row r="14">
@@ -18632,10 +20035,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="L14" t="n">
         <v>4770</v>
+      </c>
+      <c r="M14" t="n">
+        <v>570</v>
       </c>
     </row>
     <row r="15">
@@ -18670,10 +20076,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
         <v>1080</v>
+      </c>
+      <c r="M15" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>330</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>150</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>240</v>
       </c>
+      <c r="M18" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>19794099.6</v>
+        <v>19729413</v>
       </c>
       <c r="C5" t="n">
-        <v>101187702</v>
+        <v>77270608.8</v>
       </c>
       <c r="D5" t="n">
-        <v>88152176.58</v>
+        <v>167030671.1</v>
       </c>
       <c r="E5" t="n">
-        <v>37182563.26</v>
+        <v>69626488.95</v>
       </c>
       <c r="F5" t="n">
         <v>14166.78</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1189152.36</v>
+        <v>24500880</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>69999.60000000001</v>
+        <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1388843.4</v>
+        <v>2330445.22</v>
       </c>
       <c r="L5" t="n">
-        <v>356194.69</v>
+        <v>6751836</v>
+      </c>
+      <c r="M5" t="n">
+        <v>82800</v>
       </c>
     </row>
     <row r="6">
@@ -19233,37 +20684,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>43151486.4</v>
+        <v>43109985.6</v>
       </c>
       <c r="C6" t="n">
-        <v>181471752</v>
+        <v>138578428.8</v>
       </c>
       <c r="D6" t="n">
-        <v>147983905.45</v>
+        <v>280399781.38</v>
       </c>
       <c r="E6" t="n">
-        <v>54000136.01</v>
+        <v>101118361.5</v>
       </c>
       <c r="F6" t="n">
         <v>62500.5</v>
       </c>
       <c r="G6" t="n">
-        <v>60384</v>
+        <v>174717</v>
       </c>
       <c r="H6" t="n">
-        <v>2053130.31</v>
+        <v>42301980</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>2024596.6</v>
+        <v>3569594.34</v>
       </c>
       <c r="L6" t="n">
-        <v>648598.09</v>
+        <v>12357630</v>
+      </c>
+      <c r="M6" t="n">
+        <v>149760</v>
       </c>
     </row>
     <row r="7">
@@ -19271,37 +20725,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>51194612.7</v>
+        <v>51189157.8</v>
       </c>
       <c r="C7" t="n">
-        <v>219431520</v>
+        <v>167565888</v>
       </c>
       <c r="D7" t="n">
-        <v>202656105.69</v>
+        <v>383992621.06</v>
       </c>
       <c r="E7" t="n">
-        <v>59816331.19</v>
+        <v>112009521.6</v>
       </c>
       <c r="F7" t="n">
         <v>500004</v>
       </c>
       <c r="G7" t="n">
-        <v>228271.5</v>
+        <v>664119</v>
       </c>
       <c r="H7" t="n">
-        <v>4228927.23</v>
+        <v>87256170</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>408331</v>
+        <v>169946</v>
       </c>
       <c r="K7" t="n">
-        <v>3516269.88</v>
+        <v>6226724.33</v>
       </c>
       <c r="L7" t="n">
-        <v>1322059.32</v>
+        <v>25161840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>519750</v>
       </c>
     </row>
     <row r="8">
@@ -19309,37 +20766,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>59647896</v>
+        <v>59646906</v>
       </c>
       <c r="C8" t="n">
-        <v>222175800</v>
+        <v>169661520</v>
       </c>
       <c r="D8" t="n">
-        <v>236708890.39</v>
+        <v>448515809.28</v>
       </c>
       <c r="E8" t="n">
-        <v>60767949.21</v>
+        <v>113791481.1</v>
       </c>
       <c r="F8" t="n">
         <v>395836.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1132755</v>
+        <v>3291678</v>
       </c>
       <c r="H8" t="n">
-        <v>1396805.85</v>
+        <v>28779300</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>148749.15</v>
+        <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4185730.8</v>
+        <v>7790713.09</v>
       </c>
       <c r="L8" t="n">
-        <v>1622624.2</v>
+        <v>30913542</v>
+      </c>
+      <c r="M8" t="n">
+        <v>718200</v>
       </c>
     </row>
     <row r="9">
@@ -19350,34 +20810,37 @@
         <v>63848466</v>
       </c>
       <c r="C9" t="n">
-        <v>216714960</v>
+        <v>165491424</v>
       </c>
       <c r="D9" t="n">
-        <v>251909438.54</v>
+        <v>477317795.33</v>
       </c>
       <c r="E9" t="n">
-        <v>47629336.05</v>
+        <v>89188672.05</v>
       </c>
       <c r="F9" t="n">
         <v>666672</v>
       </c>
       <c r="G9" t="n">
-        <v>1550642.25</v>
+        <v>4512429</v>
       </c>
       <c r="H9" t="n">
-        <v>215787</v>
+        <v>4446000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>166249.05</v>
+        <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4309468</v>
+        <v>7876074.54</v>
       </c>
       <c r="L9" t="n">
-        <v>1641942.74</v>
+        <v>31330962</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1422000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,34 +20851,37 @@
         <v>55897578</v>
       </c>
       <c r="C10" t="n">
-        <v>131365080</v>
+        <v>100315152</v>
       </c>
       <c r="D10" t="n">
-        <v>165439492.77</v>
+        <v>313474613.76</v>
       </c>
       <c r="E10" t="n">
-        <v>33660648</v>
+        <v>63031500</v>
       </c>
       <c r="F10" t="n">
         <v>875007</v>
       </c>
       <c r="G10" t="n">
-        <v>1167720</v>
+        <v>3408480</v>
       </c>
       <c r="H10" t="n">
-        <v>116193</v>
+        <v>2394000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>2986760</v>
+        <v>5914120.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1066922.39</v>
+        <v>20391858</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1053000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,34 +20892,37 @@
         <v>37003626</v>
       </c>
       <c r="C11" t="n">
-        <v>59930640</v>
+        <v>45765216</v>
       </c>
       <c r="D11" t="n">
-        <v>77948363.12</v>
+        <v>147696493.82</v>
       </c>
       <c r="E11" t="n">
-        <v>19366148.09</v>
+        <v>36264226.5</v>
       </c>
       <c r="F11" t="n">
         <v>208335</v>
       </c>
       <c r="G11" t="n">
-        <v>621045</v>
+        <v>1812780</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>1642718</v>
+        <v>3359322.58</v>
       </c>
       <c r="L11" t="n">
-        <v>663262.2</v>
+        <v>12625200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>810000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>21653082</v>
       </c>
       <c r="C12" t="n">
-        <v>26444880</v>
+        <v>20194272</v>
       </c>
       <c r="D12" t="n">
-        <v>35486350.47</v>
+        <v>67239507.45999999</v>
       </c>
       <c r="E12" t="n">
-        <v>6737104.08</v>
+        <v>12615615</v>
       </c>
       <c r="F12" t="n">
         <v>83334</v>
       </c>
       <c r="G12" t="n">
-        <v>353535</v>
+        <v>1031940</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19485,13 +20954,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>917362</v>
+        <v>1980502.13</v>
       </c>
       <c r="L12" t="n">
-        <v>336859.2</v>
+        <v>6409800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>720000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,19 +20974,19 @@
         <v>10613988</v>
       </c>
       <c r="C13" t="n">
-        <v>6791400</v>
+        <v>5186160</v>
       </c>
       <c r="D13" t="n">
-        <v>9334569.25</v>
+        <v>17687134.08</v>
       </c>
       <c r="E13" t="n">
-        <v>1316247.41</v>
+        <v>2464749</v>
       </c>
       <c r="F13" t="n">
         <v>41667</v>
       </c>
       <c r="G13" t="n">
-        <v>200910</v>
+        <v>588060</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19526,10 +20998,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>234674</v>
+        <v>507143.14</v>
       </c>
       <c r="L13" t="n">
-        <v>100040.4</v>
+        <v>1917000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>396000</v>
       </c>
     </row>
     <row r="14">
@@ -19540,19 +21015,19 @@
         <v>3323826</v>
       </c>
       <c r="C14" t="n">
-        <v>3049200</v>
+        <v>2328480</v>
       </c>
       <c r="D14" t="n">
-        <v>4290344.63</v>
+        <v>8129341.44</v>
       </c>
       <c r="E14" t="n">
-        <v>283197.15</v>
+        <v>530302.95</v>
       </c>
       <c r="F14" t="n">
         <v>83334</v>
       </c>
       <c r="G14" t="n">
-        <v>54945</v>
+        <v>160380</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -19564,10 +21039,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>42668</v>
+        <v>94392.86</v>
       </c>
       <c r="L14" t="n">
-        <v>44933.4</v>
+        <v>858600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>171000</v>
       </c>
     </row>
     <row r="15">
@@ -19578,19 +21056,19 @@
         <v>1333530</v>
       </c>
       <c r="C15" t="n">
-        <v>609840</v>
+        <v>465696</v>
       </c>
       <c r="D15" t="n">
-        <v>870427.9399999999</v>
+        <v>1649286.14</v>
       </c>
       <c r="E15" t="n">
-        <v>98876.08</v>
+        <v>185151.15</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>11100</v>
+        <v>32400</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19602,10 +21080,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>21334</v>
+        <v>47876.22</v>
       </c>
       <c r="L15" t="n">
-        <v>10173.6</v>
+        <v>194400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="16">
@@ -19616,19 +21097,19 @@
         <v>524106</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
-        <v>103353.11</v>
+        <v>193534.65</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>15540</v>
+        <v>45360</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -19640,10 +21121,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>3108.6</v>
+        <v>59400</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="17">
@@ -19654,10 +21138,10 @@
         <v>263934</v>
       </c>
       <c r="C17" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D17" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19681,7 +21165,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1413</v>
+        <v>27000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="18">
@@ -19692,10 +21179,10 @@
         <v>256014</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19704,7 +21191,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -19719,7 +21206,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2260.8</v>
+        <v>43200</v>
+      </c>
+      <c r="M18" t="n">
+        <v>180000</v>
       </c>
     </row>
     <row r="19">
@@ -19742,7 +21232,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -19758,6 +21248,9 @@
       </c>
       <c r="L19" t="n">
         <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="20">
@@ -19768,10 +21261,10 @@
         <v>22374</v>
       </c>
       <c r="C20" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D20" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19796,6 +21289,9 @@
       </c>
       <c r="L20" t="n">
         <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="21">
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>18000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19844,10 +21343,10 @@
         <v>14454</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19872,6 +21371,9 @@
       </c>
       <c r="L22" t="n">
         <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="23">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19920,10 +21425,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D24" t="n">
-        <v>200633.4</v>
+        <v>380160</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19947,6 +21452,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,10 +21621,10 @@
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>140850</v>
+        <v>141120</v>
       </c>
       <c r="H4" t="n">
-        <v>24660</v>
+        <v>24750</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -20116,10 +21633,13 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>402390</v>
+        <v>401220</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,10 +21662,10 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>87660</v>
+        <v>87810</v>
       </c>
       <c r="H5" t="n">
-        <v>18840</v>
+        <v>18870</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20157,7 +21677,10 @@
         <v>153</v>
       </c>
       <c r="L5" t="n">
-        <v>216270</v>
+        <v>216240</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>53580</v>
+        <v>53820</v>
       </c>
       <c r="H6" t="n">
-        <v>21060</v>
+        <v>20970</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>93</v>
       </c>
       <c r="L6" t="n">
-        <v>115140</v>
+        <v>115350</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20221,7 +21747,7 @@
         <v>19290</v>
       </c>
       <c r="H7" t="n">
-        <v>3090</v>
+        <v>3210</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -20233,7 +21759,10 @@
         <v>34</v>
       </c>
       <c r="L7" t="n">
-        <v>46500</v>
+        <v>46530</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -20273,6 +21802,9 @@
       <c r="L8" t="n">
         <v>7020</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -20294,7 +21826,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -20309,7 +21841,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1770</v>
+        <v>1740</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>450</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>150</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>30</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21077,7 +22669,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6782.4</v>
+        <v>6793.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21086,10 +22678,13 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>64.26000000000001</v>
+        <v>50.64</v>
       </c>
       <c r="L5" t="n">
-        <v>45416.7</v>
+        <v>45410.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2679</v>
+        <v>2691</v>
       </c>
       <c r="H6" t="n">
-        <v>12004.2</v>
+        <v>11952.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>60.45</v>
+        <v>47.15</v>
       </c>
       <c r="L6" t="n">
-        <v>42601.8</v>
+        <v>42679.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21153,7 +22751,7 @@
         <v>2893.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2255.7</v>
+        <v>2343.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -21162,10 +22760,13 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>27.88</v>
+        <v>21.69</v>
       </c>
       <c r="L7" t="n">
-        <v>27900</v>
+        <v>27918</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21200,10 +22801,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
         <v>4984.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21226,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>102</v>
+        <v>127.5</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -21241,7 +22845,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1433.7</v>
+        <v>1409.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>400.5</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>150</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>30</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>31220372.7</v>
       </c>
       <c r="C5" t="n">
-        <v>95973570</v>
+        <v>73288908</v>
       </c>
       <c r="D5" t="n">
-        <v>83609756.15000001</v>
+        <v>158423696.64</v>
       </c>
       <c r="E5" t="n">
-        <v>6913432.81</v>
+        <v>12945800.7</v>
       </c>
       <c r="F5" t="n">
         <v>12500.1</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1876350.96</v>
+        <v>38721240</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1370922.84</v>
+        <v>2459021.51</v>
       </c>
       <c r="L5" t="n">
-        <v>427825.31</v>
+        <v>8173872</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,34 +23699,37 @@
         <v>20033481.6</v>
       </c>
       <c r="C6" t="n">
-        <v>74394936</v>
+        <v>56810678.4</v>
       </c>
       <c r="D6" t="n">
-        <v>60666484.2</v>
+        <v>114950803.97</v>
       </c>
       <c r="E6" t="n">
-        <v>4287504.31</v>
+        <v>8028598.5</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>49561.5</v>
+        <v>145314</v>
       </c>
       <c r="H6" t="n">
-        <v>3320961.93</v>
+        <v>68131530</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>1289640.3</v>
+        <v>2289463.96</v>
       </c>
       <c r="L6" t="n">
-        <v>401308.96</v>
+        <v>7682310</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,34 +23740,37 @@
         <v>12005482.5</v>
       </c>
       <c r="C7" t="n">
-        <v>31489920</v>
+        <v>24046848</v>
       </c>
       <c r="D7" t="n">
-        <v>29082533.61</v>
+        <v>55105560.58</v>
       </c>
       <c r="E7" t="n">
-        <v>1763453.16</v>
+        <v>3302167.5</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>53529.75</v>
+        <v>156249</v>
       </c>
       <c r="H7" t="n">
-        <v>624039.4</v>
+        <v>13356810</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>594791.92</v>
+        <v>1053276.75</v>
       </c>
       <c r="L7" t="n">
-        <v>262818</v>
+        <v>5025240</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,22 +23781,22 @@
         <v>709236</v>
       </c>
       <c r="C8" t="n">
-        <v>3575880</v>
+        <v>2730672</v>
       </c>
       <c r="D8" t="n">
-        <v>3809787.51</v>
+        <v>7218782.21</v>
       </c>
       <c r="E8" t="n">
-        <v>325397.32</v>
+        <v>609325.2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8297.25</v>
+        <v>24219</v>
       </c>
       <c r="H8" t="n">
-        <v>119927.78</v>
+        <v>2470950</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22132,10 +23805,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>57601.8</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
-        <v>46951.16</v>
+        <v>897156</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>111078</v>
       </c>
       <c r="C9" t="n">
-        <v>498960</v>
+        <v>381024</v>
       </c>
       <c r="D9" t="n">
-        <v>579991.03</v>
+        <v>1098966.53</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22158,10 +23834,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1887</v>
+        <v>6885</v>
       </c>
       <c r="H9" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13505.45</v>
+        <v>253692</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22184,10 +23863,10 @@
         <v>53460</v>
       </c>
       <c r="C10" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D10" t="n">
-        <v>104730.63</v>
+        <v>198443.52</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22199,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3772.71</v>
+        <v>72090</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22249,7 +23931,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1413</v>
+        <v>27000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -22275,7 +23960,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22287,7 +23972,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>1014</v>
+        <v>391</v>
       </c>
       <c r="L4" t="n">
         <v>1348260</v>
@@ -590,7 +590,7 @@
         <v>26</v>
       </c>
       <c r="K5" t="n">
-        <v>551</v>
+        <v>223</v>
       </c>
       <c r="L5" t="n">
         <v>834330</v>
@@ -631,7 +631,7 @@
         <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>490</v>
+        <v>176</v>
       </c>
       <c r="L6" t="n">
         <v>617700</v>
@@ -672,7 +672,7 @@
         <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>395</v>
+        <v>113</v>
       </c>
       <c r="L7" t="n">
         <v>493140</v>
@@ -713,7 +713,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>337</v>
+        <v>104</v>
       </c>
       <c r="L8" t="n">
         <v>396780</v>
@@ -754,7 +754,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
         <v>315450</v>
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>175</v>
+        <v>41</v>
       </c>
       <c r="L10" t="n">
         <v>192480</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
         <v>163500</v>
@@ -877,7 +877,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
         <v>120570</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>49500</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>23880</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>10230</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>3000</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1860</v>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
         <v>17520</v>
@@ -1594,7 +1594,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>24090</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>26250</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
         <v>35700</v>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
         <v>44370</v>
@@ -1758,7 +1758,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>45120</v>
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>49320</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>87180</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
         <v>81270</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>36870</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>17640</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>8790</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2370</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1380</v>
@@ -2598,7 +2598,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>2.65</v>
       </c>
       <c r="L5" t="n">
         <v>5058.9</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>12.68</v>
+        <v>4.56</v>
       </c>
       <c r="L6" t="n">
         <v>9712.5</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>10.85</v>
+        <v>7.02</v>
       </c>
       <c r="L7" t="n">
         <v>21420</v>
@@ -2721,7 +2721,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>17.66</v>
+        <v>8.1</v>
       </c>
       <c r="L8" t="n">
         <v>31502.7</v>
@@ -2762,7 +2762,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>17.67</v>
+        <v>3.21</v>
       </c>
       <c r="L9" t="n">
         <v>36547.2</v>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>22.62</v>
+        <v>2.61</v>
       </c>
       <c r="L10" t="n">
         <v>43894.8</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>34.14</v>
+        <v>4.49</v>
       </c>
       <c r="L11" t="n">
         <v>87180</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>35.23</v>
+        <v>6.49</v>
       </c>
       <c r="L12" t="n">
         <v>81270</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21.84</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>36870</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10.69</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>17640</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>8790</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2370</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1380</v>
@@ -3602,7 +3602,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>257152.58</v>
+        <v>128576.29</v>
       </c>
       <c r="L5" t="n">
         <v>910602</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>615447.3</v>
+        <v>221561.03</v>
       </c>
       <c r="L6" t="n">
         <v>1748250</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>526638.38</v>
+        <v>340766.01</v>
       </c>
       <c r="L7" t="n">
         <v>3855600</v>
@@ -3725,7 +3725,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>857693.1800000001</v>
+        <v>393109.38</v>
       </c>
       <c r="L8" t="n">
         <v>5670486</v>
@@ -3766,7 +3766,7 @@
         <v>115320.5</v>
       </c>
       <c r="K9" t="n">
-        <v>857790.3</v>
+        <v>155961.87</v>
       </c>
       <c r="L9" t="n">
         <v>6578496</v>
@@ -3807,7 +3807,7 @@
         <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>1098336.72</v>
+        <v>126731.16</v>
       </c>
       <c r="L10" t="n">
         <v>7901064</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1657847.51</v>
+        <v>218137.83</v>
       </c>
       <c r="L11" t="n">
         <v>15692400</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1710433.66</v>
+        <v>315079.88</v>
       </c>
       <c r="L12" t="n">
         <v>14628600</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1060390.21</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
         <v>6636600</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>519160.75</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>3175200</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>143628.65</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1582200</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>426600</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>248400</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
         <v>126300</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>47700</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>9540</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.95</v>
+        <v>3.31</v>
       </c>
       <c r="L5" t="n">
         <v>10017</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>3529.8</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>337512.76</v>
+        <v>160720.36</v>
       </c>
       <c r="L5" t="n">
         <v>1803060</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>635364</v>
@@ -7577,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
         <v>107190</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>34800</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>8700</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3210</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1320</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.94</v>
+        <v>1.66</v>
       </c>
       <c r="L5" t="n">
         <v>7308</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>3219</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1926</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>937.2</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>433944.97</v>
+        <v>80360.17999999999</v>
       </c>
       <c r="L5" t="n">
         <v>1315440</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>196943.14</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>579420</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>346680</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>35737.22</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>168696</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="L4" t="n">
         <v>193230</v>
@@ -10630,7 +10630,7 @@
         <v>11</v>
       </c>
       <c r="K5" t="n">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="L5" t="n">
         <v>186390</v>
@@ -10671,7 +10671,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="L6" t="n">
         <v>208980</v>
@@ -10712,7 +10712,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="L7" t="n">
         <v>143190</v>
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
         <v>84840</v>
@@ -10794,7 +10794,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="L9" t="n">
         <v>43950</v>
@@ -10835,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>11940</v>
@@ -11122,7 +11122,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>330</v>
@@ -11634,7 +11634,7 @@
         <v>7.8</v>
       </c>
       <c r="K5" t="n">
-        <v>182.38</v>
+        <v>73.81</v>
       </c>
       <c r="L5" t="n">
         <v>175209.3</v>
@@ -11675,7 +11675,7 @@
         <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>248.43</v>
+        <v>89.23</v>
       </c>
       <c r="L6" t="n">
         <v>228549</v>
@@ -11716,7 +11716,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>252.01</v>
+        <v>72.09</v>
       </c>
       <c r="L7" t="n">
         <v>295884</v>
@@ -11757,7 +11757,7 @@
         <v>4.25</v>
       </c>
       <c r="K8" t="n">
-        <v>248.03</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>281713.8</v>
@@ -11798,7 +11798,7 @@
         <v>9.5</v>
       </c>
       <c r="K9" t="n">
-        <v>224.84</v>
+        <v>60.22</v>
       </c>
       <c r="L9" t="n">
         <v>255514.5</v>
@@ -11839,7 +11839,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>152.25</v>
+        <v>35.67</v>
       </c>
       <c r="L10" t="n">
         <v>171307.2</v>
@@ -11880,7 +11880,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>105.12</v>
+        <v>15.27</v>
       </c>
       <c r="L11" t="n">
         <v>163500</v>
@@ -11921,7 +11921,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>76.01000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="L12" t="n">
         <v>120570</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>32.28</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>49500</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>12.64</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>23880</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>10230</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>3000</v>
@@ -12126,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1860</v>
@@ -12638,7 +12638,7 @@
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>55.28</v>
+        <v>28.14</v>
       </c>
       <c r="L5" t="n">
         <v>39141.9</v>
@@ -12679,7 +12679,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>110.02</v>
+        <v>42.08</v>
       </c>
       <c r="L6" t="n">
         <v>77322.60000000001</v>
@@ -12720,7 +12720,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>88.04000000000001</v>
+        <v>29.35</v>
       </c>
       <c r="L7" t="n">
         <v>85914</v>
@@ -12761,7 +12761,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>65.5</v>
+        <v>23.55</v>
       </c>
       <c r="L8" t="n">
         <v>60236.4</v>
@@ -12802,7 +12802,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>44.16</v>
+        <v>8.83</v>
       </c>
       <c r="L9" t="n">
         <v>35599.5</v>
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>7.83</v>
+        <v>1.74</v>
       </c>
       <c r="L10" t="n">
         <v>10626.6</v>
@@ -13130,7 +13130,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>330</v>
@@ -13642,7 +13642,7 @@
         <v>80117.39999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>2684030.01</v>
+        <v>1366123.06</v>
       </c>
       <c r="L5" t="n">
         <v>7045542</v>
@@ -13683,7 +13683,7 @@
         <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>5342082.56</v>
+        <v>2043285.04</v>
       </c>
       <c r="L6" t="n">
         <v>13918068</v>
@@ -13724,7 +13724,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4275064.46</v>
+        <v>1425021.49</v>
       </c>
       <c r="L7" t="n">
         <v>15464520</v>
@@ -13765,7 +13765,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3180612.22</v>
+        <v>1143590.91</v>
       </c>
       <c r="L8" t="n">
         <v>10842552</v>
@@ -13806,7 +13806,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2144475.74</v>
+        <v>428895.15</v>
       </c>
       <c r="L9" t="n">
         <v>6407910</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>380193.48</v>
+        <v>84487.44</v>
       </c>
       <c r="L10" t="n">
         <v>1912788</v>
@@ -14134,7 +14134,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>59400</v>
@@ -14605,7 +14605,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
         <v>289500</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>85830</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.62</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>18024.3</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321440.72</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>3244374</v>
@@ -17658,7 +17658,7 @@
         <v>189368.4</v>
       </c>
       <c r="K5" t="n">
-        <v>8855691.84</v>
+        <v>3584064.03</v>
       </c>
       <c r="L5" t="n">
         <v>31537674</v>
@@ -17699,7 +17699,7 @@
         <v>109251</v>
       </c>
       <c r="K6" t="n">
-        <v>12062767.08</v>
+        <v>4332748.99</v>
       </c>
       <c r="L6" t="n">
         <v>41138820</v>
@@ -17740,7 +17740,7 @@
         <v>237924.4</v>
       </c>
       <c r="K7" t="n">
-        <v>12236597.56</v>
+        <v>3500596.26</v>
       </c>
       <c r="L7" t="n">
         <v>53259120</v>
@@ -17781,7 +17781,7 @@
         <v>103181.5</v>
       </c>
       <c r="K8" t="n">
-        <v>12043441.79</v>
+        <v>3716670.46</v>
       </c>
       <c r="L8" t="n">
         <v>50708484</v>
@@ -17822,7 +17822,7 @@
         <v>230641</v>
       </c>
       <c r="K9" t="n">
-        <v>10917331.04</v>
+        <v>2924285.1</v>
       </c>
       <c r="L9" t="n">
         <v>45992610</v>
@@ -17863,7 +17863,7 @@
         <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>7392651</v>
+        <v>1731992.52</v>
       </c>
       <c r="L10" t="n">
         <v>30835296</v>
@@ -17904,7 +17904,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>5104425.22</v>
+        <v>741668.62</v>
       </c>
       <c r="L11" t="n">
         <v>29430000</v>
@@ -17945,7 +17945,7 @@
         <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>3690935.78</v>
+        <v>405102.71</v>
       </c>
       <c r="L12" t="n">
         <v>21702600</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1567533.35</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
         <v>8910000</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>613553.62</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>4298400</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>191504.86</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1841400</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>540000</v>
@@ -18150,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>334800</v>
@@ -18621,7 +18621,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="L4" t="n">
         <v>153990</v>
@@ -18662,7 +18662,7 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="L5" t="n">
         <v>178620</v>
@@ -18703,7 +18703,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
         <v>185550</v>
@@ -18744,7 +18744,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>201</v>
+        <v>50</v>
       </c>
       <c r="L7" t="n">
         <v>232980</v>
@@ -18785,7 +18785,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>218</v>
+        <v>61</v>
       </c>
       <c r="L8" t="n">
         <v>241890</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>202</v>
+        <v>59</v>
       </c>
       <c r="L9" t="n">
         <v>214890</v>
@@ -18867,7 +18867,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>140</v>
+        <v>36</v>
       </c>
       <c r="L10" t="n">
         <v>127290</v>
@@ -18908,7 +18908,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>70140</v>
@@ -18949,7 +18949,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>35610</v>
@@ -18990,7 +18990,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>10650</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>4770</v>
@@ -19072,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1080</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>330</v>
@@ -19666,7 +19666,7 @@
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>48</v>
+        <v>18.21</v>
       </c>
       <c r="L5" t="n">
         <v>37510.2</v>
@@ -19707,7 +19707,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>73.52</v>
+        <v>32.96</v>
       </c>
       <c r="L6" t="n">
         <v>68653.5</v>
@@ -19748,7 +19748,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>128.24</v>
+        <v>31.9</v>
       </c>
       <c r="L7" t="n">
         <v>139788</v>
@@ -19789,7 +19789,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>160.45</v>
+        <v>44.9</v>
       </c>
       <c r="L8" t="n">
         <v>171741.9</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>162.21</v>
+        <v>47.38</v>
       </c>
       <c r="L9" t="n">
         <v>174060.9</v>
@@ -19871,7 +19871,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>121.8</v>
+        <v>31.32</v>
       </c>
       <c r="L10" t="n">
         <v>113288.1</v>
@@ -19912,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>69.18000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="L11" t="n">
         <v>70140</v>
@@ -19953,7 +19953,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>40.79</v>
+        <v>1.85</v>
       </c>
       <c r="L12" t="n">
         <v>35610</v>
@@ -19994,7 +19994,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>10.44</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>10650</v>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>4770</v>
@@ -20076,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1080</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>330</v>
@@ -20670,7 +20670,7 @@
         <v>29133.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2330445.22</v>
+        <v>883961.98</v>
       </c>
       <c r="L5" t="n">
         <v>6751836</v>
@@ -20711,7 +20711,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>3569594.34</v>
+        <v>1600162.98</v>
       </c>
       <c r="L6" t="n">
         <v>12357630</v>
@@ -20752,7 +20752,7 @@
         <v>169946</v>
       </c>
       <c r="K7" t="n">
-        <v>6226724.33</v>
+        <v>1548936.4</v>
       </c>
       <c r="L7" t="n">
         <v>25161840</v>
@@ -20793,7 +20793,7 @@
         <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7790713.09</v>
+        <v>2179970.18</v>
       </c>
       <c r="L8" t="n">
         <v>30913542</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>7876074.54</v>
+        <v>2300437.61</v>
       </c>
       <c r="L9" t="n">
         <v>31330962</v>
@@ -20875,7 +20875,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>5914120.8</v>
+        <v>1520773.92</v>
       </c>
       <c r="L10" t="n">
         <v>20391858</v>
@@ -20916,7 +20916,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>3359322.58</v>
+        <v>436275.66</v>
       </c>
       <c r="L11" t="n">
         <v>12625200</v>
@@ -20957,7 +20957,7 @@
         <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>1980502.13</v>
+        <v>90022.82000000001</v>
       </c>
       <c r="L12" t="n">
         <v>6409800</v>
@@ -20998,7 +20998,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>507143.14</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1917000</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>94392.86</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>858600</v>
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>47876.22</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>194400</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>59400</v>
@@ -21633,7 +21633,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>89</v>
       </c>
       <c r="L4" t="n">
         <v>401220</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="L5" t="n">
         <v>216240</v>
@@ -21715,7 +21715,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="L6" t="n">
         <v>115350</v>
@@ -21756,7 +21756,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>46530</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>7020</v>
@@ -22678,7 +22678,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>50.64</v>
+        <v>16.22</v>
       </c>
       <c r="L5" t="n">
         <v>45410.4</v>
@@ -22719,7 +22719,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>47.15</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>42679.5</v>
@@ -22760,7 +22760,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>21.69</v>
+        <v>3.19</v>
       </c>
       <c r="L7" t="n">
         <v>27918</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>4984.2</v>
@@ -23682,7 +23682,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2459021.51</v>
+        <v>787529.76</v>
       </c>
       <c r="L5" t="n">
         <v>8173872</v>
@@ -23723,7 +23723,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2289463.96</v>
+        <v>467739.95</v>
       </c>
       <c r="L6" t="n">
         <v>7682310</v>
@@ -23764,7 +23764,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>1053276.75</v>
+        <v>154893.64</v>
       </c>
       <c r="L7" t="n">
         <v>5025240</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>107211.65</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>897156</v>

--- a/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Present_Breaches.xlsx
@@ -560,7 +560,7 @@
         <v>512430</v>
       </c>
       <c r="H4" t="n">
-        <v>67860</v>
+        <v>73470</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -572,22 +572,22 @@
         <v>391</v>
       </c>
       <c r="L4" t="n">
-        <v>1348260</v>
+        <v>1448640</v>
       </c>
       <c r="M4" t="n">
-        <v>63720</v>
+        <v>48810</v>
       </c>
       <c r="N4" t="n">
-        <v>79200</v>
+        <v>79890</v>
       </c>
       <c r="O4" t="n">
-        <v>227640</v>
+        <v>234540</v>
       </c>
       <c r="P4" t="n">
-        <v>46080</v>
+        <v>17460</v>
       </c>
       <c r="Q4" t="n">
-        <v>200942.16</v>
+        <v>2082344.17</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>332760</v>
       </c>
       <c r="H5" t="n">
-        <v>49350</v>
+        <v>56610</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -625,22 +625,22 @@
         <v>223</v>
       </c>
       <c r="L5" t="n">
-        <v>834330</v>
+        <v>880290</v>
       </c>
       <c r="M5" t="n">
-        <v>48510</v>
+        <v>32880</v>
       </c>
       <c r="N5" t="n">
-        <v>63210</v>
+        <v>77370</v>
       </c>
       <c r="O5" t="n">
-        <v>167430</v>
+        <v>192630</v>
       </c>
       <c r="P5" t="n">
-        <v>58860</v>
+        <v>37800</v>
       </c>
       <c r="Q5" t="n">
-        <v>134440.28</v>
+        <v>1393191.6</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>244650</v>
       </c>
       <c r="H6" t="n">
-        <v>51750</v>
+        <v>53430</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>176</v>
       </c>
       <c r="L6" t="n">
-        <v>617700</v>
+        <v>622170</v>
       </c>
       <c r="M6" t="n">
-        <v>30060</v>
+        <v>26280</v>
       </c>
       <c r="N6" t="n">
-        <v>16800</v>
+        <v>26880</v>
       </c>
       <c r="O6" t="n">
-        <v>107130</v>
+        <v>115500</v>
       </c>
       <c r="P6" t="n">
-        <v>59310</v>
+        <v>42540</v>
       </c>
       <c r="Q6" t="n">
-        <v>104266.21</v>
+        <v>1080500.6</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>195720</v>
       </c>
       <c r="H7" t="n">
-        <v>32640</v>
+        <v>32940</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -731,22 +731,22 @@
         <v>113</v>
       </c>
       <c r="L7" t="n">
-        <v>493140</v>
+        <v>488040</v>
       </c>
       <c r="M7" t="n">
-        <v>20610</v>
+        <v>26580</v>
       </c>
       <c r="N7" t="n">
-        <v>4950</v>
+        <v>8640</v>
       </c>
       <c r="O7" t="n">
-        <v>73500</v>
+        <v>83520</v>
       </c>
       <c r="P7" t="n">
-        <v>69630</v>
+        <v>52770</v>
       </c>
       <c r="Q7" t="n">
-        <v>87759.34</v>
+        <v>909441.53</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>155610</v>
       </c>
       <c r="H8" t="n">
-        <v>11010</v>
+        <v>13950</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -784,22 +784,22 @@
         <v>104</v>
       </c>
       <c r="L8" t="n">
-        <v>396780</v>
+        <v>413760</v>
       </c>
       <c r="M8" t="n">
-        <v>13440</v>
+        <v>30450</v>
       </c>
       <c r="N8" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="O8" t="n">
-        <v>61980</v>
+        <v>67020</v>
       </c>
       <c r="P8" t="n">
-        <v>69030</v>
+        <v>63720</v>
       </c>
       <c r="Q8" t="n">
-        <v>75880.75</v>
+        <v>786344.83</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>152610</v>
       </c>
       <c r="H9" t="n">
-        <v>3780</v>
+        <v>4320</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>315450</v>
+        <v>344730</v>
       </c>
       <c r="M9" t="n">
-        <v>10080</v>
+        <v>29700</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>39600</v>
+        <v>55050</v>
       </c>
       <c r="P9" t="n">
-        <v>72600</v>
+        <v>70200</v>
       </c>
       <c r="Q9" t="n">
-        <v>65114.36</v>
+        <v>674773.8</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>84960</v>
       </c>
       <c r="H10" t="n">
-        <v>4290</v>
+        <v>4200</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -890,22 +890,22 @@
         <v>41</v>
       </c>
       <c r="L10" t="n">
-        <v>192480</v>
+        <v>228240</v>
       </c>
       <c r="M10" t="n">
-        <v>6810</v>
+        <v>25350</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14760</v>
+        <v>26670</v>
       </c>
       <c r="P10" t="n">
-        <v>80190</v>
+        <v>89550</v>
       </c>
       <c r="Q10" t="n">
-        <v>42465.81</v>
+        <v>440069.07</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>63840</v>
       </c>
       <c r="H11" t="n">
-        <v>5640</v>
+        <v>5880</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -943,22 +943,22 @@
         <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>163500</v>
+        <v>201780</v>
       </c>
       <c r="M11" t="n">
-        <v>4410</v>
+        <v>24690</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6420</v>
+        <v>16500</v>
       </c>
       <c r="P11" t="n">
-        <v>67680</v>
+        <v>103020</v>
       </c>
       <c r="Q11" t="n">
-        <v>29834.36</v>
+        <v>309170.61</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>50490</v>
       </c>
       <c r="H12" t="n">
-        <v>1920</v>
+        <v>2910</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>120570</v>
+        <v>166560</v>
       </c>
       <c r="M12" t="n">
-        <v>3180</v>
+        <v>15960</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2670</v>
+        <v>4080</v>
       </c>
       <c r="P12" t="n">
-        <v>48570</v>
+        <v>81840</v>
       </c>
       <c r="Q12" t="n">
-        <v>21678.97</v>
+        <v>224657.06</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>30930</v>
       </c>
       <c r="H13" t="n">
-        <v>840</v>
+        <v>930</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1049,22 +1049,22 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>49500</v>
+        <v>73470</v>
       </c>
       <c r="M13" t="n">
-        <v>2310</v>
+        <v>21780</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2040</v>
+        <v>2160</v>
       </c>
       <c r="P13" t="n">
-        <v>33240</v>
+        <v>54060</v>
       </c>
       <c r="Q13" t="n">
-        <v>11906.83</v>
+        <v>123389.3</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>9810</v>
       </c>
       <c r="H14" t="n">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1102,22 +1102,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>23880</v>
+        <v>38070</v>
       </c>
       <c r="M14" t="n">
-        <v>960</v>
+        <v>7380</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2430</v>
+        <v>2850</v>
       </c>
       <c r="P14" t="n">
-        <v>27870</v>
+        <v>28770</v>
       </c>
       <c r="Q14" t="n">
-        <v>4366.57</v>
+        <v>45250.38</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>4110</v>
       </c>
       <c r="H15" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>10230</v>
+        <v>26610</v>
       </c>
       <c r="M15" t="n">
-        <v>960</v>
+        <v>3840</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="P15" t="n">
-        <v>36420</v>
+        <v>47400</v>
       </c>
       <c r="Q15" t="n">
-        <v>2629.74</v>
+        <v>27251.77</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>1740</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3000</v>
+        <v>11430</v>
       </c>
       <c r="M16" t="n">
-        <v>150</v>
+        <v>1950</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>26370</v>
+        <v>45030</v>
       </c>
       <c r="Q16" t="n">
-        <v>1397.57</v>
+        <v>14482.85</v>
       </c>
     </row>
     <row r="17">
@@ -1261,22 +1261,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1860</v>
+        <v>7950</v>
       </c>
       <c r="M17" t="n">
-        <v>660</v>
+        <v>1770</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>19140</v>
+        <v>25080</v>
       </c>
       <c r="Q17" t="n">
-        <v>617.15</v>
+        <v>6395.44</v>
       </c>
     </row>
     <row r="18">
@@ -1302,7 +1302,7 @@
         <v>300</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1314,22 +1314,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3810</v>
+        <v>6360</v>
       </c>
       <c r="M18" t="n">
-        <v>2940</v>
+        <v>3480</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>19470</v>
+        <v>28110</v>
       </c>
       <c r="Q18" t="n">
-        <v>303.44</v>
+        <v>3144.52</v>
       </c>
     </row>
     <row r="19">
@@ -1367,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1200</v>
+        <v>3960</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>2100</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>8970</v>
+        <v>20280</v>
       </c>
       <c r="Q19" t="n">
-        <v>135.82</v>
+        <v>1407.46</v>
       </c>
     </row>
     <row r="20">
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.1</v>
+        <v>239.4</v>
       </c>
     </row>
     <row r="21">
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.13</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="22">
@@ -1526,10 +1526,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M22" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.15</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="23">
@@ -1852,7 +1852,7 @@
         <v>7650</v>
       </c>
       <c r="H4" t="n">
-        <v>3600</v>
+        <v>4050</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>17520</v>
+        <v>16620</v>
       </c>
       <c r="M4" t="n">
-        <v>4170</v>
+        <v>2280</v>
       </c>
       <c r="N4" t="n">
-        <v>1080</v>
+        <v>510</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>173.96</v>
+        <v>19715.58</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>8850</v>
       </c>
       <c r="H5" t="n">
-        <v>2580</v>
+        <v>3930</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>24090</v>
+        <v>19770</v>
       </c>
       <c r="M5" t="n">
-        <v>10620</v>
+        <v>5760</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>720</v>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>412.56</v>
+        <v>46756.8</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>8190</v>
       </c>
       <c r="H6" t="n">
-        <v>1860</v>
+        <v>1650</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,22 +1970,22 @@
         <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>26250</v>
+        <v>20460</v>
       </c>
       <c r="M6" t="n">
-        <v>9450</v>
+        <v>5580</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>840</v>
+        <v>510</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>867.27</v>
+        <v>98290.25999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>13320</v>
       </c>
       <c r="H7" t="n">
-        <v>3510</v>
+        <v>2880</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>11</v>
       </c>
       <c r="L7" t="n">
-        <v>35700</v>
+        <v>29130</v>
       </c>
       <c r="M7" t="n">
-        <v>6660</v>
+        <v>2610</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>330</v>
+        <v>570</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1267.08</v>
+        <v>143602.74</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>18300</v>
       </c>
       <c r="H8" t="n">
-        <v>3960</v>
+        <v>5130</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -2076,10 +2076,10 @@
         <v>11</v>
       </c>
       <c r="L8" t="n">
-        <v>44370</v>
+        <v>40950</v>
       </c>
       <c r="M8" t="n">
-        <v>4500</v>
+        <v>2760</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1316.28</v>
+        <v>149178.06</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>21270</v>
       </c>
       <c r="H9" t="n">
-        <v>2910</v>
+        <v>2790</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>45120</v>
+        <v>47670</v>
       </c>
       <c r="M9" t="n">
-        <v>2760</v>
+        <v>1350</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1350.03</v>
+        <v>153003.06</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>17430</v>
       </c>
       <c r="H10" t="n">
-        <v>3810</v>
+        <v>3450</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -2182,22 +2182,22 @@
         <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>49320</v>
+        <v>48300</v>
       </c>
       <c r="M10" t="n">
-        <v>1830</v>
+        <v>2490</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1197.69</v>
+        <v>135738.54</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>28530</v>
       </c>
       <c r="H11" t="n">
-        <v>5580</v>
+        <v>5490</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -2235,22 +2235,22 @@
         <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>87180</v>
+        <v>82320</v>
       </c>
       <c r="M11" t="n">
-        <v>1290</v>
+        <v>3480</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1614.76</v>
+        <v>183006.36</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>30930</v>
       </c>
       <c r="H12" t="n">
-        <v>1890</v>
+        <v>2670</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>81270</v>
+        <v>93270</v>
       </c>
       <c r="M12" t="n">
-        <v>450</v>
+        <v>3360</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1968.84</v>
+        <v>223135.2</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>19590</v>
       </c>
       <c r="H13" t="n">
-        <v>840</v>
+        <v>930</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2341,10 +2341,10 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>36870</v>
+        <v>43680</v>
       </c>
       <c r="M13" t="n">
-        <v>480</v>
+        <v>3810</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1212.3</v>
+        <v>137394</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>6330</v>
       </c>
       <c r="H14" t="n">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>17640</v>
+        <v>23610</v>
       </c>
       <c r="M14" t="n">
-        <v>240</v>
+        <v>3510</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>469.07</v>
+        <v>53161.38</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>3330</v>
       </c>
       <c r="H15" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>8790</v>
+        <v>14070</v>
       </c>
       <c r="M15" t="n">
-        <v>870</v>
+        <v>2430</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>352.97</v>
+        <v>40003.38</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>840</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2370</v>
+        <v>5550</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>1080</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>139.78</v>
+        <v>15841.62</v>
       </c>
     </row>
     <row r="17">
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1380</v>
+        <v>2880</v>
       </c>
       <c r="M17" t="n">
-        <v>330</v>
+        <v>1170</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.31</v>
+        <v>7175.7</v>
       </c>
     </row>
     <row r="18">
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2910</v>
+        <v>3210</v>
       </c>
       <c r="M18" t="n">
-        <v>2310</v>
+        <v>2730</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>25.57</v>
+        <v>2897.82</v>
       </c>
     </row>
     <row r="19">
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1080</v>
+        <v>3360</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2070</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.99</v>
+        <v>1132.2</v>
       </c>
     </row>
     <row r="20">
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2712,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.54</v>
+        <v>287.64</v>
       </c>
     </row>
     <row r="21">
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.59</v>
+        <v>67.31999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>928.8</v>
+        <v>1414.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>2.65</v>
       </c>
       <c r="L5" t="n">
-        <v>5058.9</v>
+        <v>4151.7</v>
       </c>
       <c r="M5" t="n">
-        <v>212.4</v>
+        <v>115.2</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.63</v>
+        <v>2337.84</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>409.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1060.2</v>
+        <v>940.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,22 +3262,22 @@
         <v>4.56</v>
       </c>
       <c r="L6" t="n">
-        <v>9712.5</v>
+        <v>7570.2</v>
       </c>
       <c r="M6" t="n">
-        <v>756</v>
+        <v>446.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>210</v>
+        <v>127.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>650.45</v>
+        <v>73717.69</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>1998</v>
       </c>
       <c r="H7" t="n">
-        <v>2562.3</v>
+        <v>2102.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>7.02</v>
       </c>
       <c r="L7" t="n">
-        <v>21420</v>
+        <v>17478</v>
       </c>
       <c r="M7" t="n">
-        <v>2331</v>
+        <v>913.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>115.5</v>
+        <v>199.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1013.67</v>
+        <v>114882.19</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>11895</v>
       </c>
       <c r="H8" t="n">
-        <v>3366</v>
+        <v>4360.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -3368,10 +3368,10 @@
         <v>8.1</v>
       </c>
       <c r="L8" t="n">
-        <v>31502.7</v>
+        <v>29074.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2475</v>
+        <v>1518</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1250.46</v>
+        <v>141719.16</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>18079.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2910</v>
+        <v>2790</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>3.21</v>
       </c>
       <c r="L9" t="n">
-        <v>36547.2</v>
+        <v>38612.7</v>
       </c>
       <c r="M9" t="n">
-        <v>1932</v>
+        <v>945</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1309.53</v>
+        <v>148412.97</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>17430</v>
       </c>
       <c r="H10" t="n">
-        <v>3810</v>
+        <v>3450</v>
       </c>
       <c r="I10" t="n">
         <v>0.87</v>
@@ -3474,22 +3474,22 @@
         <v>2.61</v>
       </c>
       <c r="L10" t="n">
-        <v>43894.8</v>
+        <v>42987</v>
       </c>
       <c r="M10" t="n">
-        <v>1555.5</v>
+        <v>2116.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1197.69</v>
+        <v>135738.54</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>28530</v>
       </c>
       <c r="H11" t="n">
-        <v>5580</v>
+        <v>5490</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -3527,22 +3527,22 @@
         <v>4.49</v>
       </c>
       <c r="L11" t="n">
-        <v>87180</v>
+        <v>82320</v>
       </c>
       <c r="M11" t="n">
-        <v>1161</v>
+        <v>3132</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>178.5</v>
+        <v>229.5</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1614.76</v>
+        <v>183006.36</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>30930</v>
       </c>
       <c r="H12" t="n">
-        <v>1890</v>
+        <v>2670</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,10 +3580,10 @@
         <v>6.49</v>
       </c>
       <c r="L12" t="n">
-        <v>81270</v>
+        <v>93270</v>
       </c>
       <c r="M12" t="n">
-        <v>427.5</v>
+        <v>3192</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1968.84</v>
+        <v>223135.2</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>19590</v>
       </c>
       <c r="H13" t="n">
-        <v>840</v>
+        <v>930</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
@@ -3633,10 +3633,10 @@
         <v>0.95</v>
       </c>
       <c r="L13" t="n">
-        <v>36870</v>
+        <v>43680</v>
       </c>
       <c r="M13" t="n">
-        <v>480</v>
+        <v>3810</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1212.3</v>
+        <v>137394</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>6330</v>
       </c>
       <c r="H14" t="n">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>17640</v>
+        <v>23610</v>
       </c>
       <c r="M14" t="n">
-        <v>240</v>
+        <v>3510</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>469.07</v>
+        <v>53161.38</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>3330</v>
       </c>
       <c r="H15" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>8790</v>
+        <v>14070</v>
       </c>
       <c r="M15" t="n">
-        <v>870</v>
+        <v>2430</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>352.97</v>
+        <v>40003.38</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>840</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2370</v>
+        <v>5550</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>1080</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>139.78</v>
+        <v>15841.62</v>
       </c>
     </row>
     <row r="17">
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1380</v>
+        <v>2880</v>
       </c>
       <c r="M17" t="n">
-        <v>330</v>
+        <v>1170</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>63.32</v>
+        <v>7175.7</v>
       </c>
     </row>
     <row r="18">
@@ -3886,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2910</v>
+        <v>3210</v>
       </c>
       <c r="M18" t="n">
-        <v>2310</v>
+        <v>2730</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>25.57</v>
+        <v>2897.82</v>
       </c>
     </row>
     <row r="19">
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1080</v>
+        <v>3360</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2070</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.99</v>
+        <v>1132.2</v>
       </c>
     </row>
     <row r="20">
@@ -3992,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.54</v>
+        <v>287.64</v>
       </c>
     </row>
     <row r="21">
@@ -4057,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.59</v>
+        <v>67.31999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5294160</v>
+        <v>8064360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>128576.29</v>
       </c>
       <c r="L5" t="n">
-        <v>910602</v>
+        <v>747306</v>
       </c>
       <c r="M5" t="n">
-        <v>74340</v>
+        <v>40320</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>1224</v>
       </c>
       <c r="O5" t="n">
-        <v>255</v>
+        <v>510</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>12376.8</v>
+        <v>1402704</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>22113</v>
       </c>
       <c r="H6" t="n">
-        <v>6043140</v>
+        <v>5360850</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,22 +4554,22 @@
         <v>221561.03</v>
       </c>
       <c r="L6" t="n">
-        <v>1748250</v>
+        <v>1362636</v>
       </c>
       <c r="M6" t="n">
-        <v>264600</v>
+        <v>156240</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>35700</v>
+        <v>21675</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>390270.15</v>
+        <v>44230617</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>107892</v>
       </c>
       <c r="H7" t="n">
-        <v>14605110</v>
+        <v>11983680</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>340766.01</v>
       </c>
       <c r="L7" t="n">
-        <v>3855600</v>
+        <v>3146040</v>
       </c>
       <c r="M7" t="n">
-        <v>815850</v>
+        <v>319725</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>19635</v>
+        <v>33915</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>608199.84</v>
+        <v>68929315.2</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>642330</v>
       </c>
       <c r="H8" t="n">
-        <v>19186200</v>
+        <v>24854850</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -4660,10 +4660,10 @@
         <v>393109.38</v>
       </c>
       <c r="L8" t="n">
-        <v>5670486</v>
+        <v>5233410</v>
       </c>
       <c r="M8" t="n">
-        <v>866250</v>
+        <v>531300</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>750277.89</v>
+        <v>85031494.2</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>976293</v>
       </c>
       <c r="H9" t="n">
-        <v>16587000</v>
+        <v>15903000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>155961.87</v>
       </c>
       <c r="L9" t="n">
-        <v>6578496</v>
+        <v>6950286</v>
       </c>
       <c r="M9" t="n">
-        <v>676200</v>
+        <v>330750</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>11220</v>
+        <v>22440</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>785715.71</v>
+        <v>89047780.92</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>941220</v>
       </c>
       <c r="H10" t="n">
-        <v>21717000</v>
+        <v>19665000</v>
       </c>
       <c r="I10" t="n">
         <v>168974.88</v>
@@ -4766,22 +4766,22 @@
         <v>126731.16</v>
       </c>
       <c r="L10" t="n">
-        <v>7901064</v>
+        <v>7737660</v>
       </c>
       <c r="M10" t="n">
-        <v>544425</v>
+        <v>740775</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>10710</v>
+        <v>3570</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>718615.8</v>
+        <v>81443124</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>1540620</v>
       </c>
       <c r="H11" t="n">
-        <v>31806000</v>
+        <v>31293000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -4819,22 +4819,22 @@
         <v>218137.83</v>
       </c>
       <c r="L11" t="n">
-        <v>15692400</v>
+        <v>14817600</v>
       </c>
       <c r="M11" t="n">
-        <v>406350</v>
+        <v>1096200</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>30345</v>
+        <v>39015</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>968857.2</v>
+        <v>109803816</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1670220</v>
       </c>
       <c r="H12" t="n">
-        <v>10773000</v>
+        <v>15219000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         <v>315079.88</v>
       </c>
       <c r="L12" t="n">
-        <v>14628600</v>
+        <v>16788600</v>
       </c>
       <c r="M12" t="n">
-        <v>149625</v>
+        <v>1117200</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1181304</v>
+        <v>133881120</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>1057860</v>
       </c>
       <c r="H13" t="n">
-        <v>4788000</v>
+        <v>5301000</v>
       </c>
       <c r="I13" t="n">
         <v>184415.69</v>
@@ -4925,10 +4925,10 @@
         <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>6636600</v>
+        <v>7862400</v>
       </c>
       <c r="M13" t="n">
-        <v>168000</v>
+        <v>1333500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>727380</v>
+        <v>82436400</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>341820</v>
       </c>
       <c r="H14" t="n">
-        <v>2565000</v>
+        <v>3591000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3175200</v>
+        <v>4249800</v>
       </c>
       <c r="M14" t="n">
-        <v>84000</v>
+        <v>1228500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>281442.6</v>
+        <v>31896828</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>179820</v>
       </c>
       <c r="H15" t="n">
-        <v>684000</v>
+        <v>1026000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1582200</v>
+        <v>2532600</v>
       </c>
       <c r="M15" t="n">
-        <v>304500</v>
+        <v>850500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>211782.6</v>
+        <v>24002028</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>45360</v>
       </c>
       <c r="H16" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>426600</v>
+        <v>999000</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>378000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>83867.39999999999</v>
+        <v>9504972</v>
       </c>
     </row>
     <row r="17">
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>248400</v>
+        <v>518400</v>
       </c>
       <c r="M17" t="n">
-        <v>115500</v>
+        <v>409500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37989</v>
+        <v>4305420</v>
       </c>
     </row>
     <row r="18">
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>523800</v>
+        <v>577800</v>
       </c>
       <c r="M18" t="n">
-        <v>808500</v>
+        <v>955500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15341.4</v>
+        <v>1738692</v>
       </c>
     </row>
     <row r="19">
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>194400</v>
+        <v>604800</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>724500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5994</v>
+        <v>679320</v>
       </c>
     </row>
     <row r="20">
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -5296,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>5400</v>
+        <v>129600</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1522.8</v>
+        <v>172584</v>
       </c>
     </row>
     <row r="21">
@@ -5349,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>356.4</v>
+        <v>40392</v>
       </c>
     </row>
     <row r="22">
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>41700</v>
       </c>
       <c r="H4" t="n">
-        <v>4440</v>
+        <v>6360</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>126300</v>
+        <v>146640</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>8790</v>
+        <v>7530</v>
       </c>
       <c r="O4" t="n">
-        <v>18900</v>
+        <v>20700</v>
       </c>
       <c r="P4" t="n">
-        <v>11100</v>
+        <v>8520</v>
       </c>
       <c r="Q4" t="n">
-        <v>22686.91</v>
+        <v>119404.8</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>14610</v>
       </c>
       <c r="H5" t="n">
-        <v>510</v>
+        <v>1380</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>47700</v>
+        <v>63210</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8640</v>
+        <v>10530</v>
       </c>
       <c r="O5" t="n">
-        <v>6360</v>
+        <v>10230</v>
       </c>
       <c r="P5" t="n">
-        <v>8580</v>
+        <v>11850</v>
       </c>
       <c r="Q5" t="n">
-        <v>9417.24</v>
+        <v>49564.44</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1740</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9540</v>
+        <v>14700</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>240</v>
+        <v>630</v>
       </c>
       <c r="O6" t="n">
-        <v>360</v>
+        <v>1170</v>
       </c>
       <c r="P6" t="n">
-        <v>6090</v>
+        <v>9090</v>
       </c>
       <c r="Q6" t="n">
-        <v>825.9299999999999</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>480</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2190</v>
+        <v>3930</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5580</v>
+        <v>8340</v>
       </c>
       <c r="Q7" t="n">
-        <v>84.95</v>
+        <v>447.12</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>420</v>
+        <v>1950</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5100</v>
+        <v>10200</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.35</v>
+        <v>238.68</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>780</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4110</v>
+        <v>10170</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.16</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1560</v>
+        <v>4350</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.44</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>183.6</v>
+        <v>496.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>3.31</v>
       </c>
       <c r="L5" t="n">
-        <v>10017</v>
+        <v>13274.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>86.40000000000001</v>
+        <v>105.3</v>
       </c>
       <c r="O5" t="n">
-        <v>318</v>
+        <v>511.5</v>
       </c>
       <c r="P5" t="n">
-        <v>171.6</v>
+        <v>237</v>
       </c>
       <c r="Q5" t="n">
-        <v>470.86</v>
+        <v>2478.22</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>87</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3529.8</v>
+        <v>5439</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>31.5</v>
       </c>
       <c r="O6" t="n">
-        <v>90</v>
+        <v>292.5</v>
       </c>
       <c r="P6" t="n">
-        <v>913.5</v>
+        <v>1363.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>619.45</v>
+        <v>3260.25</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>72</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>109.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1314</v>
+        <v>2358</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1395</v>
+        <v>2085</v>
       </c>
       <c r="Q7" t="n">
-        <v>67.95999999999999</v>
+        <v>357.7</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>298.2</v>
+        <v>1384.5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1938</v>
+        <v>3876</v>
       </c>
       <c r="Q8" t="n">
-        <v>43.08</v>
+        <v>226.75</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121.5</v>
+        <v>631.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2055</v>
+        <v>5085</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.5</v>
+        <v>113.14</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>106.8</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1326</v>
+        <v>3697.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.44</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1046520</v>
+        <v>2831760</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>160720.36</v>
       </c>
       <c r="L5" t="n">
-        <v>1803060</v>
+        <v>2389338</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>14688</v>
+        <v>17901</v>
       </c>
       <c r="O5" t="n">
-        <v>54060</v>
+        <v>86955</v>
       </c>
       <c r="P5" t="n">
-        <v>11154</v>
+        <v>15405</v>
       </c>
       <c r="Q5" t="n">
-        <v>282517.31</v>
+        <v>1486933.2</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>4698</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>635364</v>
+        <v>979020</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2040</v>
+        <v>5355</v>
       </c>
       <c r="O6" t="n">
-        <v>15300</v>
+        <v>49725</v>
       </c>
       <c r="P6" t="n">
-        <v>59377.5</v>
+        <v>88627.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>371668.5</v>
+        <v>1956150</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>3888</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>624150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>236520</v>
+        <v>424440</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>90675</v>
+        <v>135525</v>
       </c>
       <c r="Q7" t="n">
-        <v>40777.34</v>
+        <v>214617.6</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>53676</v>
+        <v>249210</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>125970</v>
+        <v>251940</v>
       </c>
       <c r="Q8" t="n">
-        <v>25849.04</v>
+        <v>136047.6</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21870</v>
+        <v>113724</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>133575</v>
+        <v>330525</v>
       </c>
       <c r="Q9" t="n">
-        <v>12898.05</v>
+        <v>67884.48</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>19224</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>86190</v>
+        <v>240337.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>5663.52</v>
+        <v>29808</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>72120</v>
       </c>
       <c r="H4" t="n">
-        <v>4650</v>
+        <v>4770</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>107190</v>
+        <v>128880</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18930</v>
+        <v>21900</v>
       </c>
       <c r="O4" t="n">
-        <v>31620</v>
+        <v>31860</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>28209.98</v>
+        <v>153077.4</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>19080</v>
       </c>
       <c r="H5" t="n">
-        <v>3060</v>
+        <v>3780</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>34800</v>
+        <v>42510</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7620</v>
+        <v>8820</v>
       </c>
       <c r="O5" t="n">
-        <v>26340</v>
+        <v>26610</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6333.72</v>
+        <v>34369.02</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>6360</v>
       </c>
       <c r="H6" t="n">
-        <v>1140</v>
+        <v>1650</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8700</v>
+        <v>14430</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3600</v>
+        <v>4290</v>
       </c>
       <c r="O6" t="n">
-        <v>21660</v>
+        <v>23580</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>908.02</v>
+        <v>4927.23</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>2040</v>
       </c>
       <c r="H7" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3210</v>
+        <v>5040</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1110</v>
+        <v>2520</v>
       </c>
       <c r="O7" t="n">
-        <v>9180</v>
+        <v>11280</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>237.54</v>
+        <v>1288.98</v>
       </c>
     </row>
     <row r="8">
@@ -9816,7 +9816,7 @@
         <v>390</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1320</v>
+        <v>2400</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="O8" t="n">
-        <v>2070</v>
+        <v>4290</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>80.56999999999999</v>
+        <v>437.22</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>360</v>
+        <v>810</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>17.64</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1101.6</v>
+        <v>1360.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>1.66</v>
       </c>
       <c r="L5" t="n">
-        <v>7308</v>
+        <v>8927.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>76.2</v>
+        <v>88.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1317</v>
+        <v>1330.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>316.69</v>
+        <v>1718.45</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>318</v>
       </c>
       <c r="H6" t="n">
-        <v>649.8</v>
+        <v>940.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3219</v>
+        <v>5339.1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>180</v>
+        <v>214.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5415</v>
+        <v>5895</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>681.01</v>
+        <v>3695.42</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>306</v>
       </c>
       <c r="H7" t="n">
-        <v>131.4</v>
+        <v>350.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1926</v>
+        <v>3024</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>77.7</v>
+        <v>176.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3213</v>
+        <v>3948</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>190.03</v>
+        <v>1031.18</v>
       </c>
     </row>
     <row r="8">
@@ -11108,7 +11108,7 @@
         <v>253.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>937.2</v>
+        <v>1704</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="O8" t="n">
-        <v>931.5</v>
+        <v>1930.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>76.54000000000001</v>
+        <v>415.36</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>198</v>
+        <v>445.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6279120</v>
+        <v>7756560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>80360.17999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1315440</v>
+        <v>1606878</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>12954</v>
+        <v>14994</v>
       </c>
       <c r="O5" t="n">
-        <v>223890</v>
+        <v>226185</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>190011.58</v>
+        <v>1031070.6</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>17172</v>
       </c>
       <c r="H6" t="n">
-        <v>3703860</v>
+        <v>5360850</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>579420</v>
+        <v>961038</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>30600</v>
+        <v>36465</v>
       </c>
       <c r="O6" t="n">
-        <v>920550</v>
+        <v>1002150</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>408608.14</v>
+        <v>2217253.5</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>16524</v>
       </c>
       <c r="H7" t="n">
-        <v>748980</v>
+        <v>1997280</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>346680</v>
+        <v>544320</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>13209</v>
+        <v>29988</v>
       </c>
       <c r="O7" t="n">
-        <v>546210</v>
+        <v>671160</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>114019.49</v>
+        <v>618710.4</v>
       </c>
     </row>
     <row r="8">
@@ -12400,7 +12400,7 @@
         <v>13689</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>168696</v>
+        <v>306720</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3060</v>
+        <v>11220</v>
       </c>
       <c r="O8" t="n">
-        <v>158355</v>
+        <v>328185</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>45926.84</v>
+        <v>249215.4</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>33660</v>
+        <v>75735</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1891.97</v>
+        <v>10266.48</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>81210</v>
       </c>
       <c r="H4" t="n">
-        <v>8880</v>
+        <v>9840</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -13492,19 +13492,19 @@
         <v>136</v>
       </c>
       <c r="L4" t="n">
-        <v>193230</v>
+        <v>192270</v>
       </c>
       <c r="M4" t="n">
-        <v>16890</v>
+        <v>870</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>37920</v>
+        <v>41730</v>
       </c>
       <c r="P4" t="n">
-        <v>23310</v>
+        <v>4650</v>
       </c>
       <c r="Q4" t="n">
         <v>34379.5</v>
@@ -13533,7 +13533,7 @@
         <v>83490</v>
       </c>
       <c r="H5" t="n">
-        <v>7440</v>
+        <v>8040</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -13545,19 +13545,19 @@
         <v>85</v>
       </c>
       <c r="L5" t="n">
-        <v>186390</v>
+        <v>175560</v>
       </c>
       <c r="M5" t="n">
-        <v>18450</v>
+        <v>1710</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>30450</v>
+        <v>38040</v>
       </c>
       <c r="P5" t="n">
-        <v>34440</v>
+        <v>15420</v>
       </c>
       <c r="Q5" t="n">
         <v>35760.88</v>
@@ -13586,7 +13586,7 @@
         <v>86220</v>
       </c>
       <c r="H6" t="n">
-        <v>12150</v>
+        <v>12630</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>83</v>
       </c>
       <c r="L6" t="n">
-        <v>208980</v>
+        <v>191760</v>
       </c>
       <c r="M6" t="n">
-        <v>11100</v>
+        <v>3930</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>23640</v>
+        <v>21330</v>
       </c>
       <c r="P6" t="n">
-        <v>34350</v>
+        <v>21990</v>
       </c>
       <c r="Q6" t="n">
         <v>43015.55</v>
@@ -13639,7 +13639,7 @@
         <v>66270</v>
       </c>
       <c r="H7" t="n">
-        <v>4530</v>
+        <v>4800</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -13651,19 +13651,19 @@
         <v>46</v>
       </c>
       <c r="L7" t="n">
-        <v>143190</v>
+        <v>132930</v>
       </c>
       <c r="M7" t="n">
-        <v>7020</v>
+        <v>4860</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>20670</v>
+        <v>22650</v>
       </c>
       <c r="P7" t="n">
-        <v>35880</v>
+        <v>28620</v>
       </c>
       <c r="Q7" t="n">
         <v>35550.07</v>
@@ -13692,7 +13692,7 @@
         <v>35610</v>
       </c>
       <c r="H8" t="n">
-        <v>600</v>
+        <v>780</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -13704,19 +13704,19 @@
         <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>84840</v>
+        <v>91920</v>
       </c>
       <c r="M8" t="n">
-        <v>3630</v>
+        <v>10230</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26490</v>
+        <v>24120</v>
       </c>
       <c r="P8" t="n">
-        <v>32100</v>
+        <v>32790</v>
       </c>
       <c r="Q8" t="n">
         <v>29154.05</v>
@@ -13745,7 +13745,7 @@
         <v>28290</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13757,19 +13757,19 @@
         <v>11</v>
       </c>
       <c r="L9" t="n">
-        <v>43950</v>
+        <v>51180</v>
       </c>
       <c r="M9" t="n">
-        <v>2220</v>
+        <v>12420</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>13980</v>
+        <v>20160</v>
       </c>
       <c r="P9" t="n">
-        <v>35550</v>
+        <v>35640</v>
       </c>
       <c r="Q9" t="n">
         <v>18888.3</v>
@@ -13810,19 +13810,19 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>11940</v>
+        <v>23700</v>
       </c>
       <c r="M10" t="n">
-        <v>1170</v>
+        <v>10470</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1290</v>
+        <v>2850</v>
       </c>
       <c r="P10" t="n">
-        <v>38070</v>
+        <v>43500</v>
       </c>
       <c r="Q10" t="n">
         <v>2747.82</v>
@@ -13863,19 +13863,19 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>5040</v>
+        <v>29700</v>
       </c>
       <c r="M11" t="n">
-        <v>330</v>
+        <v>10530</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P11" t="n">
-        <v>32730</v>
+        <v>48000</v>
       </c>
       <c r="Q11" t="n">
         <v>494.05</v>
@@ -13904,7 +13904,7 @@
         <v>300</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3540</v>
+        <v>24210</v>
       </c>
       <c r="M12" t="n">
-        <v>270</v>
+        <v>5880</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>26130</v>
+        <v>45450</v>
       </c>
       <c r="Q12" t="n">
         <v>238.04</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1920</v>
+        <v>13140</v>
       </c>
       <c r="M13" t="n">
-        <v>480</v>
+        <v>10200</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>16050</v>
+        <v>31740</v>
       </c>
       <c r="Q13" t="n">
         <v>169.41</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>990</v>
+        <v>3720</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>1230</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>10860</v>
+        <v>9630</v>
       </c>
       <c r="Q14" t="n">
         <v>17.3</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>360</v>
+        <v>5850</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>570</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12030</v>
+        <v>20130</v>
       </c>
       <c r="Q15" t="n">
         <v>21.2</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>2880</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11400</v>
+        <v>24630</v>
       </c>
       <c r="Q16" t="n">
         <v>13.84</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>330</v>
+        <v>3510</v>
       </c>
       <c r="M17" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3900</v>
+        <v>9900</v>
       </c>
       <c r="Q17" t="n">
         <v>6.58</v>
@@ -14234,10 +14234,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>1200</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1260</v>
+        <v>2460</v>
       </c>
       <c r="Q18" t="n">
         <v>3.68</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17766</v>
+        <v>20379.6</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -14837,22 +14837,22 @@
         <v>73.81</v>
       </c>
       <c r="L5" t="n">
-        <v>175209.3</v>
+        <v>184860.9</v>
       </c>
       <c r="M5" t="n">
-        <v>970.2</v>
+        <v>657.6</v>
       </c>
       <c r="N5" t="n">
-        <v>632.1</v>
+        <v>773.7</v>
       </c>
       <c r="O5" t="n">
-        <v>8371.5</v>
+        <v>9631.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1177.2</v>
+        <v>756</v>
       </c>
       <c r="Q5" t="n">
-        <v>6722.01</v>
+        <v>69659.58</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>12232.5</v>
       </c>
       <c r="H6" t="n">
-        <v>29497.5</v>
+        <v>30455.1</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>89.23</v>
       </c>
       <c r="L6" t="n">
-        <v>228549</v>
+        <v>230202.9</v>
       </c>
       <c r="M6" t="n">
-        <v>2404.8</v>
+        <v>2102.4</v>
       </c>
       <c r="N6" t="n">
-        <v>840</v>
+        <v>1344</v>
       </c>
       <c r="O6" t="n">
-        <v>26782.5</v>
+        <v>28875</v>
       </c>
       <c r="P6" t="n">
-        <v>8896.5</v>
+        <v>6381</v>
       </c>
       <c r="Q6" t="n">
-        <v>78199.64999999999</v>
+        <v>810375.45</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>29358</v>
       </c>
       <c r="H7" t="n">
-        <v>23827.2</v>
+        <v>24046.2</v>
       </c>
       <c r="I7" t="n">
         <v>2.55</v>
@@ -14943,22 +14943,22 @@
         <v>72.09</v>
       </c>
       <c r="L7" t="n">
-        <v>295884</v>
+        <v>292824</v>
       </c>
       <c r="M7" t="n">
-        <v>7213.5</v>
+        <v>9303</v>
       </c>
       <c r="N7" t="n">
-        <v>346.5</v>
+        <v>604.8</v>
       </c>
       <c r="O7" t="n">
-        <v>25725</v>
+        <v>29232</v>
       </c>
       <c r="P7" t="n">
-        <v>17407.5</v>
+        <v>13192.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>70207.47</v>
+        <v>727553.22</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>101146.5</v>
       </c>
       <c r="H8" t="n">
-        <v>9358.5</v>
+        <v>11857.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -14996,22 +14996,22 @@
         <v>76.54000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>281713.8</v>
+        <v>293769.6</v>
       </c>
       <c r="M8" t="n">
-        <v>7392</v>
+        <v>16747.5</v>
       </c>
       <c r="N8" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="O8" t="n">
-        <v>27891</v>
+        <v>30159</v>
       </c>
       <c r="P8" t="n">
-        <v>26231.4</v>
+        <v>24213.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>72086.71000000001</v>
+        <v>747027.59</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>129718.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3780</v>
+        <v>4320</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>60.22</v>
       </c>
       <c r="L9" t="n">
-        <v>255514.5</v>
+        <v>279231.3</v>
       </c>
       <c r="M9" t="n">
-        <v>7056</v>
+        <v>20790</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>21780</v>
+        <v>30277.5</v>
       </c>
       <c r="P9" t="n">
-        <v>36300</v>
+        <v>35100</v>
       </c>
       <c r="Q9" t="n">
-        <v>63160.93</v>
+        <v>654530.59</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>84960</v>
       </c>
       <c r="H10" t="n">
-        <v>4290</v>
+        <v>4200</v>
       </c>
       <c r="I10" t="n">
         <v>1.74</v>
@@ -15102,22 +15102,22 @@
         <v>35.67</v>
       </c>
       <c r="L10" t="n">
-        <v>171307.2</v>
+        <v>203133.6</v>
       </c>
       <c r="M10" t="n">
-        <v>5788.5</v>
+        <v>21547.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>10332</v>
+        <v>18669</v>
       </c>
       <c r="P10" t="n">
-        <v>68161.5</v>
+        <v>76117.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>42465.81</v>
+        <v>440069.07</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>63840</v>
       </c>
       <c r="H11" t="n">
-        <v>5640</v>
+        <v>5880</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -15155,22 +15155,22 @@
         <v>15.27</v>
       </c>
       <c r="L11" t="n">
-        <v>163500</v>
+        <v>201780</v>
       </c>
       <c r="M11" t="n">
-        <v>3969</v>
+        <v>22221</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5457</v>
+        <v>14025</v>
       </c>
       <c r="P11" t="n">
-        <v>60912</v>
+        <v>92718</v>
       </c>
       <c r="Q11" t="n">
-        <v>29834.36</v>
+        <v>309170.61</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>50490</v>
       </c>
       <c r="H12" t="n">
-        <v>1920</v>
+        <v>2910</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>8.34</v>
       </c>
       <c r="L12" t="n">
-        <v>120570</v>
+        <v>166560</v>
       </c>
       <c r="M12" t="n">
-        <v>3021</v>
+        <v>15162</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2670</v>
+        <v>4080</v>
       </c>
       <c r="P12" t="n">
-        <v>48570</v>
+        <v>81840</v>
       </c>
       <c r="Q12" t="n">
-        <v>21678.97</v>
+        <v>224657.06</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>30930</v>
       </c>
       <c r="H13" t="n">
-        <v>840</v>
+        <v>930</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
@@ -15261,22 +15261,22 @@
         <v>0.95</v>
       </c>
       <c r="L13" t="n">
-        <v>49500</v>
+        <v>73470</v>
       </c>
       <c r="M13" t="n">
-        <v>2310</v>
+        <v>21780</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2040</v>
+        <v>2160</v>
       </c>
       <c r="P13" t="n">
-        <v>33240</v>
+        <v>54060</v>
       </c>
       <c r="Q13" t="n">
-        <v>11906.83</v>
+        <v>123389.3</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>9810</v>
       </c>
       <c r="H14" t="n">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -15314,22 +15314,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>23880</v>
+        <v>38070</v>
       </c>
       <c r="M14" t="n">
-        <v>960</v>
+        <v>7380</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2430</v>
+        <v>2850</v>
       </c>
       <c r="P14" t="n">
-        <v>27870</v>
+        <v>28770</v>
       </c>
       <c r="Q14" t="n">
-        <v>4366.57</v>
+        <v>45250.38</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>4110</v>
       </c>
       <c r="H15" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>10230</v>
+        <v>26610</v>
       </c>
       <c r="M15" t="n">
-        <v>960</v>
+        <v>3840</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="P15" t="n">
-        <v>36420</v>
+        <v>47400</v>
       </c>
       <c r="Q15" t="n">
-        <v>2629.74</v>
+        <v>27251.77</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>1740</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3000</v>
+        <v>11430</v>
       </c>
       <c r="M16" t="n">
-        <v>150</v>
+        <v>1950</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>26370</v>
+        <v>45030</v>
       </c>
       <c r="Q16" t="n">
-        <v>1397.57</v>
+        <v>14482.85</v>
       </c>
     </row>
     <row r="17">
@@ -15473,22 +15473,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1860</v>
+        <v>7950</v>
       </c>
       <c r="M17" t="n">
-        <v>660</v>
+        <v>1770</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>19140</v>
+        <v>25080</v>
       </c>
       <c r="Q17" t="n">
-        <v>617.15</v>
+        <v>6395.44</v>
       </c>
     </row>
     <row r="18">
@@ -15514,7 +15514,7 @@
         <v>300</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -15526,22 +15526,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3810</v>
+        <v>6360</v>
       </c>
       <c r="M18" t="n">
-        <v>2940</v>
+        <v>3480</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>19470</v>
+        <v>28110</v>
       </c>
       <c r="Q18" t="n">
-        <v>303.44</v>
+        <v>3144.52</v>
       </c>
     </row>
     <row r="19">
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1200</v>
+        <v>3960</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>2100</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -15591,10 +15591,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>8970</v>
+        <v>20280</v>
       </c>
       <c r="Q19" t="n">
-        <v>135.82</v>
+        <v>1407.46</v>
       </c>
     </row>
     <row r="20">
@@ -15620,7 +15620,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.1</v>
+        <v>239.4</v>
       </c>
     </row>
     <row r="21">
@@ -15685,10 +15685,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.13</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="22">
@@ -15738,10 +15738,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M22" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.15</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="23">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2678.4</v>
+        <v>2894.4</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -16129,19 +16129,19 @@
         <v>28.14</v>
       </c>
       <c r="L5" t="n">
-        <v>39141.9</v>
+        <v>36867.6</v>
       </c>
       <c r="M5" t="n">
-        <v>369</v>
+        <v>34.2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1522.5</v>
+        <v>1902</v>
       </c>
       <c r="P5" t="n">
-        <v>688.8</v>
+        <v>308.4</v>
       </c>
       <c r="Q5" t="n">
         <v>1788.04</v>
@@ -16170,7 +16170,7 @@
         <v>4311</v>
       </c>
       <c r="H6" t="n">
-        <v>6925.5</v>
+        <v>7199.1</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>42.08</v>
       </c>
       <c r="L6" t="n">
-        <v>77322.60000000001</v>
+        <v>70951.2</v>
       </c>
       <c r="M6" t="n">
-        <v>888</v>
+        <v>314.4</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5910</v>
+        <v>5332.5</v>
       </c>
       <c r="P6" t="n">
-        <v>5152.5</v>
+        <v>3298.5</v>
       </c>
       <c r="Q6" t="n">
         <v>32261.66</v>
@@ -16223,7 +16223,7 @@
         <v>9940.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3306.9</v>
+        <v>3504</v>
       </c>
       <c r="I7" t="n">
         <v>1.91</v>
@@ -16235,19 +16235,19 @@
         <v>29.35</v>
       </c>
       <c r="L7" t="n">
-        <v>85914</v>
+        <v>79758</v>
       </c>
       <c r="M7" t="n">
-        <v>2457</v>
+        <v>1701</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>7234.5</v>
+        <v>7927.5</v>
       </c>
       <c r="P7" t="n">
-        <v>8970</v>
+        <v>7155</v>
       </c>
       <c r="Q7" t="n">
         <v>28440.05</v>
@@ -16276,7 +16276,7 @@
         <v>23146.5</v>
       </c>
       <c r="H8" t="n">
-        <v>510</v>
+        <v>663</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16288,19 +16288,19 @@
         <v>23.55</v>
       </c>
       <c r="L8" t="n">
-        <v>60236.4</v>
+        <v>65263.2</v>
       </c>
       <c r="M8" t="n">
-        <v>1996.5</v>
+        <v>5626.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>11920.5</v>
+        <v>10854</v>
       </c>
       <c r="P8" t="n">
-        <v>12198</v>
+        <v>12460.2</v>
       </c>
       <c r="Q8" t="n">
         <v>27696.35</v>
@@ -16329,7 +16329,7 @@
         <v>24046.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>8.83</v>
       </c>
       <c r="L9" t="n">
-        <v>35599.5</v>
+        <v>41455.8</v>
       </c>
       <c r="M9" t="n">
-        <v>1554</v>
+        <v>8694</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>7689</v>
+        <v>11088</v>
       </c>
       <c r="P9" t="n">
-        <v>17775</v>
+        <v>17820</v>
       </c>
       <c r="Q9" t="n">
         <v>18321.65</v>
@@ -16394,19 +16394,19 @@
         <v>1.74</v>
       </c>
       <c r="L10" t="n">
-        <v>10626.6</v>
+        <v>21093</v>
       </c>
       <c r="M10" t="n">
-        <v>994.5</v>
+        <v>8899.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>903</v>
+        <v>1995</v>
       </c>
       <c r="P10" t="n">
-        <v>32359.5</v>
+        <v>36975</v>
       </c>
       <c r="Q10" t="n">
         <v>2747.82</v>
@@ -16447,19 +16447,19 @@
         <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>5040</v>
+        <v>29700</v>
       </c>
       <c r="M11" t="n">
-        <v>297</v>
+        <v>9477</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="P11" t="n">
-        <v>29457</v>
+        <v>43200</v>
       </c>
       <c r="Q11" t="n">
         <v>494.05</v>
@@ -16488,7 +16488,7 @@
         <v>300</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3540</v>
+        <v>24210</v>
       </c>
       <c r="M12" t="n">
-        <v>256.5</v>
+        <v>5586</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>26130</v>
+        <v>45450</v>
       </c>
       <c r="Q12" t="n">
         <v>238.04</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1920</v>
+        <v>13140</v>
       </c>
       <c r="M13" t="n">
-        <v>480</v>
+        <v>10200</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>16050</v>
+        <v>31740</v>
       </c>
       <c r="Q13" t="n">
         <v>169.41</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>990</v>
+        <v>3720</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>1230</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>10860</v>
+        <v>9630</v>
       </c>
       <c r="Q14" t="n">
         <v>17.3</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>360</v>
+        <v>5850</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>570</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12030</v>
+        <v>20130</v>
       </c>
       <c r="Q15" t="n">
         <v>21.2</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>2880</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11400</v>
+        <v>24630</v>
       </c>
       <c r="Q16" t="n">
         <v>13.84</v>
@@ -16765,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>330</v>
+        <v>3510</v>
       </c>
       <c r="M17" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3900</v>
+        <v>9900</v>
       </c>
       <c r="Q17" t="n">
         <v>6.58</v>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>1200</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1260</v>
+        <v>2460</v>
       </c>
       <c r="Q18" t="n">
         <v>3.68</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>15266880</v>
+        <v>16498080</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -17421,19 +17421,19 @@
         <v>1366123.06</v>
       </c>
       <c r="L5" t="n">
-        <v>7045542</v>
+        <v>6636168</v>
       </c>
       <c r="M5" t="n">
-        <v>129150</v>
+        <v>11970</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>258825</v>
+        <v>323340</v>
       </c>
       <c r="P5" t="n">
-        <v>44772</v>
+        <v>20046</v>
       </c>
       <c r="Q5" t="n">
         <v>1072826.42</v>
@@ -17462,7 +17462,7 @@
         <v>232794</v>
       </c>
       <c r="H6" t="n">
-        <v>39475350</v>
+        <v>41034870</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>2043285.04</v>
       </c>
       <c r="L6" t="n">
-        <v>13918068</v>
+        <v>12771216</v>
       </c>
       <c r="M6" t="n">
-        <v>310800</v>
+        <v>110040</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1004700</v>
+        <v>906525</v>
       </c>
       <c r="P6" t="n">
-        <v>334912.5</v>
+        <v>214402.5</v>
       </c>
       <c r="Q6" t="n">
         <v>19356997.68</v>
@@ -17515,7 +17515,7 @@
         <v>536787</v>
       </c>
       <c r="H7" t="n">
-        <v>18849330</v>
+        <v>19972800</v>
       </c>
       <c r="I7" t="n">
         <v>371744.74</v>
@@ -17527,19 +17527,19 @@
         <v>1425021.49</v>
       </c>
       <c r="L7" t="n">
-        <v>15464520</v>
+        <v>14356440</v>
       </c>
       <c r="M7" t="n">
-        <v>859950</v>
+        <v>595350</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1229865</v>
+        <v>1347675</v>
       </c>
       <c r="P7" t="n">
-        <v>583050</v>
+        <v>465075</v>
       </c>
       <c r="Q7" t="n">
         <v>17064032.83</v>
@@ -17568,7 +17568,7 @@
         <v>1249911</v>
       </c>
       <c r="H8" t="n">
-        <v>2907000</v>
+        <v>3779100</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -17580,19 +17580,19 @@
         <v>1143590.91</v>
       </c>
       <c r="L8" t="n">
-        <v>10842552</v>
+        <v>11747376</v>
       </c>
       <c r="M8" t="n">
-        <v>698775</v>
+        <v>1969275</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2026485</v>
+        <v>1845180</v>
       </c>
       <c r="P8" t="n">
-        <v>792870</v>
+        <v>809913</v>
       </c>
       <c r="Q8" t="n">
         <v>16617808.04</v>
@@ -17621,7 +17621,7 @@
         <v>1298511</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>855000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>428895.15</v>
       </c>
       <c r="L9" t="n">
-        <v>6407910</v>
+        <v>7462044</v>
       </c>
       <c r="M9" t="n">
-        <v>543900</v>
+        <v>3042900</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1307130</v>
+        <v>1884960</v>
       </c>
       <c r="P9" t="n">
-        <v>1155375</v>
+        <v>1158300</v>
       </c>
       <c r="Q9" t="n">
         <v>10992990.6</v>
@@ -17686,19 +17686,19 @@
         <v>84487.44</v>
       </c>
       <c r="L10" t="n">
-        <v>1912788</v>
+        <v>3796740</v>
       </c>
       <c r="M10" t="n">
-        <v>348075</v>
+        <v>3114825</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>153510</v>
+        <v>339150</v>
       </c>
       <c r="P10" t="n">
-        <v>2103367.5</v>
+        <v>2403375</v>
       </c>
       <c r="Q10" t="n">
         <v>1648689.12</v>
@@ -17739,19 +17739,19 @@
         <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>907200</v>
+        <v>5346000</v>
       </c>
       <c r="M11" t="n">
-        <v>103950</v>
+        <v>3316950</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>13005</v>
       </c>
       <c r="P11" t="n">
-        <v>1914705</v>
+        <v>2808000</v>
       </c>
       <c r="Q11" t="n">
         <v>296431.92</v>
@@ -17780,7 +17780,7 @@
         <v>16200</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>637200</v>
+        <v>4357800</v>
       </c>
       <c r="M12" t="n">
-        <v>89775</v>
+        <v>1955100</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P12" t="n">
-        <v>1698450</v>
+        <v>2954250</v>
       </c>
       <c r="Q12" t="n">
         <v>142825.68</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>345600</v>
+        <v>2365200</v>
       </c>
       <c r="M13" t="n">
-        <v>168000</v>
+        <v>3570000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1043250</v>
+        <v>2063100</v>
       </c>
       <c r="Q13" t="n">
         <v>101645.28</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>178200</v>
+        <v>669600</v>
       </c>
       <c r="M14" t="n">
-        <v>52500</v>
+        <v>430500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>705900</v>
+        <v>625950</v>
       </c>
       <c r="Q14" t="n">
         <v>10378.8</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>64800</v>
+        <v>1053000</v>
       </c>
       <c r="M15" t="n">
-        <v>10500</v>
+        <v>199500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>781950</v>
+        <v>1308450</v>
       </c>
       <c r="Q15" t="n">
         <v>12722.4</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>54000</v>
+        <v>518400</v>
       </c>
       <c r="M16" t="n">
-        <v>10500</v>
+        <v>52500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>741000</v>
+        <v>1600950</v>
       </c>
       <c r="Q16" t="n">
         <v>8303.040000000001</v>
@@ -18057,10 +18057,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>59400</v>
+        <v>631800</v>
       </c>
       <c r="M17" t="n">
-        <v>94500</v>
+        <v>105000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>253500</v>
+        <v>643500</v>
       </c>
       <c r="Q17" t="n">
         <v>3950.64</v>
@@ -18110,10 +18110,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>118800</v>
+        <v>216000</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>31500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>81900</v>
+        <v>159900</v>
       </c>
       <c r="Q18" t="n">
         <v>2209.68</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>21600</v>
+        <v>86400</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>89070</v>
       </c>
       <c r="H4" t="n">
-        <v>10320</v>
+        <v>13110</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>289500</v>
+        <v>331860</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>15630</v>
+        <v>12510</v>
       </c>
       <c r="O4" t="n">
-        <v>51180</v>
+        <v>54270</v>
       </c>
       <c r="P4" t="n">
-        <v>6300</v>
+        <v>2880</v>
       </c>
       <c r="Q4" t="n">
-        <v>28506.64</v>
+        <v>326638.62</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>20280</v>
       </c>
       <c r="H5" t="n">
-        <v>2010</v>
+        <v>3420</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>85830</v>
+        <v>114210</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>21660</v>
+        <v>26970</v>
       </c>
       <c r="O5" t="n">
-        <v>26760</v>
+        <v>38340</v>
       </c>
       <c r="P5" t="n">
-        <v>5520</v>
+        <v>7590</v>
       </c>
       <c r="Q5" t="n">
-        <v>8221.389999999999</v>
+        <v>94203.45</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>2130</v>
       </c>
       <c r="H6" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12930</v>
+        <v>20940</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3060</v>
+        <v>7020</v>
       </c>
       <c r="O6" t="n">
-        <v>4260</v>
+        <v>6420</v>
       </c>
       <c r="P6" t="n">
-        <v>3480</v>
+        <v>7110</v>
       </c>
       <c r="Q6" t="n">
-        <v>727.14</v>
+        <v>8331.84</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1230</v>
+        <v>4290</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="O7" t="n">
-        <v>330</v>
+        <v>900</v>
       </c>
       <c r="P7" t="n">
-        <v>3690</v>
+        <v>9210</v>
       </c>
       <c r="Q7" t="n">
-        <v>105.49</v>
+        <v>1208.79</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>210</v>
+        <v>540</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.78</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>723.6</v>
+        <v>1231.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>18024.3</v>
+        <v>23984.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>216.6</v>
+        <v>269.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1338</v>
+        <v>1917</v>
       </c>
       <c r="P5" t="n">
-        <v>110.4</v>
+        <v>151.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>411.07</v>
+        <v>4710.17</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>106.5</v>
       </c>
       <c r="H6" t="n">
-        <v>171</v>
+        <v>239.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4784.1</v>
+        <v>7747.8</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>153</v>
+        <v>351</v>
       </c>
       <c r="O6" t="n">
-        <v>1065</v>
+        <v>1605</v>
       </c>
       <c r="P6" t="n">
-        <v>522</v>
+        <v>1066.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>545.36</v>
+        <v>6248.88</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>738</v>
+        <v>2574</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>16.8</v>
       </c>
       <c r="O7" t="n">
-        <v>115.5</v>
+        <v>315</v>
       </c>
       <c r="P7" t="n">
-        <v>922.5</v>
+        <v>2302.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>84.40000000000001</v>
+        <v>967.03</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>149.1</v>
+        <v>383.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>456</v>
+        <v>1596</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.39</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>133.5</v>
+        <v>160.2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4124520</v>
+        <v>7017840</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>3244374</v>
+        <v>4317138</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>36822</v>
+        <v>45849</v>
       </c>
       <c r="O5" t="n">
-        <v>227460</v>
+        <v>325890</v>
       </c>
       <c r="P5" t="n">
-        <v>7176</v>
+        <v>9867</v>
       </c>
       <c r="Q5" t="n">
-        <v>246641.76</v>
+        <v>2826103.5</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>5751</v>
       </c>
       <c r="H6" t="n">
-        <v>974700</v>
+        <v>1364580</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>861138</v>
+        <v>1394604</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>26010</v>
+        <v>59670</v>
       </c>
       <c r="O6" t="n">
-        <v>181050</v>
+        <v>272850</v>
       </c>
       <c r="P6" t="n">
-        <v>33930</v>
+        <v>69322.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>327214.08</v>
+        <v>3749328</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>132840</v>
+        <v>463320</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>714</v>
+        <v>2856</v>
       </c>
       <c r="O7" t="n">
-        <v>19635</v>
+        <v>53550</v>
       </c>
       <c r="P7" t="n">
-        <v>59962.5</v>
+        <v>149662.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>50637.31</v>
+        <v>580219.2</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26838</v>
+        <v>69012</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>29640</v>
+        <v>103740</v>
       </c>
       <c r="Q8" t="n">
-        <v>4432.32</v>
+        <v>50787</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24030</v>
+        <v>28836</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>27000</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>101266200</v>
+        <v>116163720</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -22589,22 +22589,22 @@
         <v>3584064.03</v>
       </c>
       <c r="L5" t="n">
-        <v>31537674</v>
+        <v>33274962</v>
       </c>
       <c r="M5" t="n">
-        <v>339570</v>
+        <v>230160</v>
       </c>
       <c r="N5" t="n">
-        <v>107457</v>
+        <v>131529</v>
       </c>
       <c r="O5" t="n">
-        <v>1423155</v>
+        <v>1637355</v>
       </c>
       <c r="P5" t="n">
-        <v>76518</v>
+        <v>49140</v>
       </c>
       <c r="Q5" t="n">
-        <v>4033208.38</v>
+        <v>41795748.09</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>660555</v>
       </c>
       <c r="H6" t="n">
-        <v>168135750</v>
+        <v>173594070</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>4332748.99</v>
       </c>
       <c r="L6" t="n">
-        <v>41138820</v>
+        <v>41436522</v>
       </c>
       <c r="M6" t="n">
-        <v>841680</v>
+        <v>735840</v>
       </c>
       <c r="N6" t="n">
-        <v>142800</v>
+        <v>228480</v>
       </c>
       <c r="O6" t="n">
-        <v>4553025</v>
+        <v>4908750</v>
       </c>
       <c r="P6" t="n">
-        <v>578272.5</v>
+        <v>414765</v>
       </c>
       <c r="Q6" t="n">
-        <v>46919792.7</v>
+        <v>486225271.12</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1585332</v>
       </c>
       <c r="H7" t="n">
-        <v>135815040</v>
+        <v>137063340</v>
       </c>
       <c r="I7" t="n">
         <v>495659.65</v>
@@ -22695,22 +22695,22 @@
         <v>3500596.26</v>
       </c>
       <c r="L7" t="n">
-        <v>53259120</v>
+        <v>52708320</v>
       </c>
       <c r="M7" t="n">
-        <v>2524725</v>
+        <v>3256050</v>
       </c>
       <c r="N7" t="n">
-        <v>58905</v>
+        <v>102816</v>
       </c>
       <c r="O7" t="n">
-        <v>4373250</v>
+        <v>4969440</v>
       </c>
       <c r="P7" t="n">
-        <v>1131487.5</v>
+        <v>857512.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>42124482.43</v>
+        <v>436531934.88</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>5461911</v>
       </c>
       <c r="H8" t="n">
-        <v>53343450</v>
+        <v>67587750</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -22748,22 +22748,22 @@
         <v>3716670.46</v>
       </c>
       <c r="L8" t="n">
-        <v>50708484</v>
+        <v>52878528</v>
       </c>
       <c r="M8" t="n">
-        <v>2587200</v>
+        <v>5861625</v>
       </c>
       <c r="N8" t="n">
-        <v>4080</v>
+        <v>17340</v>
       </c>
       <c r="O8" t="n">
-        <v>4741470</v>
+        <v>5127030</v>
       </c>
       <c r="P8" t="n">
-        <v>1705041</v>
+        <v>1573884</v>
       </c>
       <c r="Q8" t="n">
-        <v>43252025.22</v>
+        <v>448216551.68</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>7004799</v>
       </c>
       <c r="H9" t="n">
-        <v>21546000</v>
+        <v>24624000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>2924285.1</v>
       </c>
       <c r="L9" t="n">
-        <v>45992610</v>
+        <v>50261634</v>
       </c>
       <c r="M9" t="n">
-        <v>2469600</v>
+        <v>7276500</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3702600</v>
+        <v>5147175</v>
       </c>
       <c r="P9" t="n">
-        <v>2359500</v>
+        <v>2281500</v>
       </c>
       <c r="Q9" t="n">
-        <v>37896557.05</v>
+        <v>392718353.35</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>4587840</v>
       </c>
       <c r="H10" t="n">
-        <v>24453000</v>
+        <v>23940000</v>
       </c>
       <c r="I10" t="n">
         <v>337949.76</v>
@@ -22854,22 +22854,22 @@
         <v>1731992.52</v>
       </c>
       <c r="L10" t="n">
-        <v>30835296</v>
+        <v>36564048</v>
       </c>
       <c r="M10" t="n">
-        <v>2025975</v>
+        <v>7541625</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1756440</v>
+        <v>3173730</v>
       </c>
       <c r="P10" t="n">
-        <v>4430497.5</v>
+        <v>4947637.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>25479485.28</v>
+        <v>264041440.2</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>3447360</v>
       </c>
       <c r="H11" t="n">
-        <v>32148000</v>
+        <v>33516000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -22907,22 +22907,22 @@
         <v>741668.62</v>
       </c>
       <c r="L11" t="n">
-        <v>29430000</v>
+        <v>36320400</v>
       </c>
       <c r="M11" t="n">
-        <v>1389150</v>
+        <v>7777350</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>927690</v>
+        <v>2384250</v>
       </c>
       <c r="P11" t="n">
-        <v>3959280</v>
+        <v>6026670</v>
       </c>
       <c r="Q11" t="n">
-        <v>17900617.68</v>
+        <v>185502368.7</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>2726460</v>
       </c>
       <c r="H12" t="n">
-        <v>10944000</v>
+        <v>16587000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>405102.71</v>
       </c>
       <c r="L12" t="n">
-        <v>21702600</v>
+        <v>29980800</v>
       </c>
       <c r="M12" t="n">
-        <v>1057350</v>
+        <v>5306700</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>453900</v>
+        <v>693600</v>
       </c>
       <c r="P12" t="n">
-        <v>3157050</v>
+        <v>5319600</v>
       </c>
       <c r="Q12" t="n">
-        <v>13007381.76</v>
+        <v>134794238.4</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>1670220</v>
       </c>
       <c r="H13" t="n">
-        <v>4788000</v>
+        <v>5301000</v>
       </c>
       <c r="I13" t="n">
         <v>184415.69</v>
@@ -23013,22 +23013,22 @@
         <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>8910000</v>
+        <v>13224600</v>
       </c>
       <c r="M13" t="n">
-        <v>808500</v>
+        <v>7623000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>346800</v>
+        <v>367200</v>
       </c>
       <c r="P13" t="n">
-        <v>2160600</v>
+        <v>3513900</v>
       </c>
       <c r="Q13" t="n">
-        <v>7144096.32</v>
+        <v>74033578.8</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>529740</v>
       </c>
       <c r="H14" t="n">
-        <v>2565000</v>
+        <v>3591000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23066,22 +23066,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4298400</v>
+        <v>6852600</v>
       </c>
       <c r="M14" t="n">
-        <v>336000</v>
+        <v>2583000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>413100</v>
+        <v>484500</v>
       </c>
       <c r="P14" t="n">
-        <v>1811550</v>
+        <v>1870050</v>
       </c>
       <c r="Q14" t="n">
-        <v>2619943.92</v>
+        <v>27150225.3</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>221940</v>
       </c>
       <c r="H15" t="n">
-        <v>684000</v>
+        <v>1026000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1841400</v>
+        <v>4789800</v>
       </c>
       <c r="M15" t="n">
-        <v>336000</v>
+        <v>1344000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>15300</v>
+        <v>76500</v>
       </c>
       <c r="P15" t="n">
-        <v>2367300</v>
+        <v>3081000</v>
       </c>
       <c r="Q15" t="n">
-        <v>1577845.44</v>
+        <v>16351059.6</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>93960</v>
       </c>
       <c r="H16" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,22 +23172,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>540000</v>
+        <v>2057400</v>
       </c>
       <c r="M16" t="n">
-        <v>52500</v>
+        <v>682500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1714050</v>
+        <v>2926950</v>
       </c>
       <c r="Q16" t="n">
-        <v>838540.08</v>
+        <v>8689709.699999999</v>
       </c>
     </row>
     <row r="17">
@@ -23225,22 +23225,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>334800</v>
+        <v>1431000</v>
       </c>
       <c r="M17" t="n">
-        <v>231000</v>
+        <v>619500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="P17" t="n">
-        <v>1244100</v>
+        <v>1630200</v>
       </c>
       <c r="Q17" t="n">
-        <v>370288.8</v>
+        <v>3837267</v>
       </c>
     </row>
     <row r="18">
@@ -23266,7 +23266,7 @@
         <v>16200</v>
       </c>
       <c r="H18" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23278,22 +23278,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>685800</v>
+        <v>1144800</v>
       </c>
       <c r="M18" t="n">
-        <v>1029000</v>
+        <v>1218000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P18" t="n">
-        <v>1265550</v>
+        <v>1827150</v>
       </c>
       <c r="Q18" t="n">
-        <v>182064.24</v>
+        <v>1886714.1</v>
       </c>
     </row>
     <row r="19">
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>216000</v>
+        <v>712800</v>
       </c>
       <c r="M19" t="n">
-        <v>21000</v>
+        <v>735000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23343,10 +23343,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>583050</v>
+        <v>1318200</v>
       </c>
       <c r="Q19" t="n">
-        <v>81490.32000000001</v>
+        <v>844476.3</v>
       </c>
     </row>
     <row r="20">
@@ -23372,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>5400</v>
+        <v>129600</v>
       </c>
       <c r="M20" t="n">
-        <v>10500</v>
+        <v>168000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q20" t="n">
-        <v>13860.72</v>
+        <v>143637.3</v>
       </c>
     </row>
     <row r="21">
@@ -23437,10 +23437,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M21" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -23452,7 +23452,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2477.52</v>
+        <v>25674.3</v>
       </c>
     </row>
     <row r="22">
@@ -23490,10 +23490,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M22" t="n">
-        <v>73500</v>
+        <v>115500</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4888.08</v>
+        <v>50654.7</v>
       </c>
     </row>
     <row r="23">
@@ -23816,7 +23816,7 @@
         <v>53280</v>
       </c>
       <c r="H4" t="n">
-        <v>7410</v>
+        <v>6930</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -23828,22 +23828,22 @@
         <v>61</v>
       </c>
       <c r="L4" t="n">
-        <v>153990</v>
+        <v>139230</v>
       </c>
       <c r="M4" t="n">
-        <v>32850</v>
+        <v>41580</v>
       </c>
       <c r="N4" t="n">
-        <v>19710</v>
+        <v>19620</v>
       </c>
       <c r="O4" t="n">
-        <v>15810</v>
+        <v>16980</v>
       </c>
       <c r="P4" t="n">
-        <v>2310</v>
+        <v>1020</v>
       </c>
       <c r="Q4" t="n">
-        <v>12768.09</v>
+        <v>125177.4</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>65040</v>
       </c>
       <c r="H5" t="n">
-        <v>11940</v>
+        <v>12390</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>55</v>
       </c>
       <c r="L5" t="n">
-        <v>178620</v>
+        <v>166560</v>
       </c>
       <c r="M5" t="n">
-        <v>13800</v>
+        <v>22920</v>
       </c>
       <c r="N5" t="n">
-        <v>16980</v>
+        <v>19260</v>
       </c>
       <c r="O5" t="n">
-        <v>20640</v>
+        <v>21450</v>
       </c>
       <c r="P5" t="n">
-        <v>3360</v>
+        <v>1080</v>
       </c>
       <c r="Q5" t="n">
-        <v>20327.27</v>
+        <v>199287</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>64710</v>
       </c>
       <c r="H6" t="n">
-        <v>13020</v>
+        <v>13050</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>185550</v>
+        <v>183300</v>
       </c>
       <c r="M6" t="n">
-        <v>6240</v>
+        <v>13860</v>
       </c>
       <c r="N6" t="n">
-        <v>8160</v>
+        <v>11220</v>
       </c>
       <c r="O6" t="n">
-        <v>19260</v>
+        <v>19590</v>
       </c>
       <c r="P6" t="n">
-        <v>3990</v>
+        <v>1980</v>
       </c>
       <c r="Q6" t="n">
-        <v>24984.2</v>
+        <v>244943.1</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>81990</v>
       </c>
       <c r="H7" t="n">
-        <v>20970</v>
+        <v>20340</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -23987,22 +23987,22 @@
         <v>50</v>
       </c>
       <c r="L7" t="n">
-        <v>232980</v>
+        <v>230850</v>
       </c>
       <c r="M7" t="n">
-        <v>4950</v>
+        <v>14010</v>
       </c>
       <c r="N7" t="n">
-        <v>2790</v>
+        <v>3870</v>
       </c>
       <c r="O7" t="n">
-        <v>23100</v>
+        <v>24570</v>
       </c>
       <c r="P7" t="n">
-        <v>5520</v>
+        <v>3660</v>
       </c>
       <c r="Q7" t="n">
-        <v>24982.27</v>
+        <v>244924.2</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>93780</v>
       </c>
       <c r="H8" t="n">
-        <v>5940</v>
+        <v>7290</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>61</v>
       </c>
       <c r="L8" t="n">
-        <v>241890</v>
+        <v>249450</v>
       </c>
       <c r="M8" t="n">
-        <v>3990</v>
+        <v>11640</v>
       </c>
       <c r="N8" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="O8" t="n">
-        <v>20460</v>
+        <v>21600</v>
       </c>
       <c r="P8" t="n">
-        <v>8460</v>
+        <v>6270</v>
       </c>
       <c r="Q8" t="n">
-        <v>27654.47</v>
+        <v>271122.3</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>98310</v>
       </c>
       <c r="H9" t="n">
-        <v>780</v>
+        <v>1230</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -24093,22 +24093,22 @@
         <v>59</v>
       </c>
       <c r="L9" t="n">
-        <v>214890</v>
+        <v>229350</v>
       </c>
       <c r="M9" t="n">
-        <v>4740</v>
+        <v>9600</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>22020</v>
+        <v>24540</v>
       </c>
       <c r="P9" t="n">
-        <v>10560</v>
+        <v>5640</v>
       </c>
       <c r="Q9" t="n">
-        <v>29602.47</v>
+        <v>290220.3</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>63120</v>
       </c>
       <c r="H10" t="n">
-        <v>420</v>
+        <v>570</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>36</v>
       </c>
       <c r="L10" t="n">
-        <v>127290</v>
+        <v>147510</v>
       </c>
       <c r="M10" t="n">
-        <v>3510</v>
+        <v>7710</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>12960</v>
+        <v>20880</v>
       </c>
       <c r="P10" t="n">
-        <v>14760</v>
+        <v>7350</v>
       </c>
       <c r="Q10" t="n">
-        <v>25916.15</v>
+        <v>254079.9</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>33570</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>70140</v>
+        <v>84360</v>
       </c>
       <c r="M11" t="n">
-        <v>2700</v>
+        <v>5430</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6330</v>
+        <v>16110</v>
       </c>
       <c r="P11" t="n">
-        <v>15420</v>
+        <v>15240</v>
       </c>
       <c r="Q11" t="n">
-        <v>17156.23</v>
+        <v>168198.3</v>
       </c>
     </row>
     <row r="12">
@@ -24252,22 +24252,22 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>35610</v>
+        <v>46230</v>
       </c>
       <c r="M12" t="n">
-        <v>2400</v>
+        <v>4440</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2670</v>
+        <v>4080</v>
       </c>
       <c r="P12" t="n">
-        <v>12600</v>
+        <v>12750</v>
       </c>
       <c r="Q12" t="n">
-        <v>10039.16</v>
+        <v>98423.10000000001</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10650</v>
+        <v>16230</v>
       </c>
       <c r="M13" t="n">
-        <v>1320</v>
+        <v>5400</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2040</v>
+        <v>2160</v>
       </c>
       <c r="P13" t="n">
-        <v>12810</v>
+        <v>12030</v>
       </c>
       <c r="Q13" t="n">
-        <v>4921.03</v>
+        <v>48245.4</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4770</v>
+        <v>10140</v>
       </c>
       <c r="M14" t="n">
-        <v>570</v>
+        <v>2370</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2430</v>
+        <v>2850</v>
       </c>
       <c r="P14" t="n">
-        <v>15180</v>
+        <v>16140</v>
       </c>
       <c r="Q14" t="n">
-        <v>1541.05</v>
+        <v>15108.3</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1080</v>
+        <v>6690</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="P15" t="n">
-        <v>24090</v>
+        <v>26670</v>
       </c>
       <c r="Q15" t="n">
-        <v>618.27</v>
+        <v>6061.5</v>
       </c>
     </row>
     <row r="16">
@@ -24464,22 +24464,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>330</v>
+        <v>3000</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>720</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>14970</v>
+        <v>20400</v>
       </c>
       <c r="Q16" t="n">
-        <v>242.99</v>
+        <v>2382.3</v>
       </c>
     </row>
     <row r="17">
@@ -24517,22 +24517,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>150</v>
+        <v>1560</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>15240</v>
+        <v>15180</v>
       </c>
       <c r="Q17" t="n">
-        <v>122.37</v>
+        <v>1199.7</v>
       </c>
     </row>
     <row r="18">
@@ -24570,22 +24570,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>240</v>
+        <v>1950</v>
       </c>
       <c r="M18" t="n">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18240</v>
+        <v>25680</v>
       </c>
       <c r="Q18" t="n">
-        <v>118.7</v>
+        <v>1163.7</v>
       </c>
     </row>
     <row r="19">
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>8970</v>
+        <v>20280</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.02</v>
+        <v>568.8</v>
       </c>
     </row>
     <row r="20">
@@ -24679,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.37</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="21">
@@ -24732,7 +24732,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -24744,7 +24744,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.38</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="22">
@@ -24785,7 +24785,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -24797,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="23">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4298.4</v>
+        <v>4460.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>18.21</v>
       </c>
       <c r="L5" t="n">
-        <v>37510.2</v>
+        <v>34977.6</v>
       </c>
       <c r="M5" t="n">
-        <v>276</v>
+        <v>458.4</v>
       </c>
       <c r="N5" t="n">
-        <v>169.8</v>
+        <v>192.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1032</v>
+        <v>1072.5</v>
       </c>
       <c r="P5" t="n">
-        <v>67.2</v>
+        <v>21.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1016.36</v>
+        <v>9964.35</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3235.5</v>
       </c>
       <c r="H6" t="n">
-        <v>7421.4</v>
+        <v>7438.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>32.96</v>
       </c>
       <c r="L6" t="n">
-        <v>68653.5</v>
+        <v>67821</v>
       </c>
       <c r="M6" t="n">
-        <v>499.2</v>
+        <v>1108.8</v>
       </c>
       <c r="N6" t="n">
-        <v>408</v>
+        <v>561</v>
       </c>
       <c r="O6" t="n">
-        <v>4815</v>
+        <v>4897.5</v>
       </c>
       <c r="P6" t="n">
-        <v>598.5</v>
+        <v>297</v>
       </c>
       <c r="Q6" t="n">
-        <v>18738.15</v>
+        <v>183707.32</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>12298.5</v>
       </c>
       <c r="H7" t="n">
-        <v>15308.1</v>
+        <v>14848.2</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -25279,22 +25279,22 @@
         <v>31.9</v>
       </c>
       <c r="L7" t="n">
-        <v>139788</v>
+        <v>138510</v>
       </c>
       <c r="M7" t="n">
-        <v>1732.5</v>
+        <v>4903.5</v>
       </c>
       <c r="N7" t="n">
-        <v>195.3</v>
+        <v>270.9</v>
       </c>
       <c r="O7" t="n">
-        <v>8085</v>
+        <v>8599.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1380</v>
+        <v>915</v>
       </c>
       <c r="Q7" t="n">
-        <v>19985.81</v>
+        <v>195939.36</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>60957</v>
       </c>
       <c r="H8" t="n">
-        <v>5049</v>
+        <v>6196.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>44.9</v>
       </c>
       <c r="L8" t="n">
-        <v>171741.9</v>
+        <v>177109.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2194.5</v>
+        <v>6402</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>9207</v>
+        <v>9720</v>
       </c>
       <c r="P8" t="n">
-        <v>3214.8</v>
+        <v>2382.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>26271.75</v>
+        <v>257566.18</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>83563.5</v>
       </c>
       <c r="H9" t="n">
-        <v>780</v>
+        <v>1230</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -25385,22 +25385,22 @@
         <v>47.38</v>
       </c>
       <c r="L9" t="n">
-        <v>174060.9</v>
+        <v>185773.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3318</v>
+        <v>6720</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>12111</v>
+        <v>13497</v>
       </c>
       <c r="P9" t="n">
-        <v>5280</v>
+        <v>2820</v>
       </c>
       <c r="Q9" t="n">
-        <v>28714.4</v>
+        <v>281513.69</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>63120</v>
       </c>
       <c r="H10" t="n">
-        <v>420</v>
+        <v>570</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>31.32</v>
       </c>
       <c r="L10" t="n">
-        <v>113288.1</v>
+        <v>131283.9</v>
       </c>
       <c r="M10" t="n">
-        <v>2983.5</v>
+        <v>6553.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>9072</v>
+        <v>14616</v>
       </c>
       <c r="P10" t="n">
-        <v>12546</v>
+        <v>6247.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>25916.15</v>
+        <v>254079.9</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>33570</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>8.98</v>
       </c>
       <c r="L11" t="n">
-        <v>70140</v>
+        <v>84360</v>
       </c>
       <c r="M11" t="n">
-        <v>2430</v>
+        <v>4887</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5380.5</v>
+        <v>13693.5</v>
       </c>
       <c r="P11" t="n">
-        <v>13878</v>
+        <v>13716</v>
       </c>
       <c r="Q11" t="n">
-        <v>17156.23</v>
+        <v>168198.3</v>
       </c>
     </row>
     <row r="12">
@@ -25544,22 +25544,22 @@
         <v>1.85</v>
       </c>
       <c r="L12" t="n">
-        <v>35610</v>
+        <v>46230</v>
       </c>
       <c r="M12" t="n">
-        <v>2280</v>
+        <v>4218</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2670</v>
+        <v>4080</v>
       </c>
       <c r="P12" t="n">
-        <v>12600</v>
+        <v>12750</v>
       </c>
       <c r="Q12" t="n">
-        <v>10039.16</v>
+        <v>98423.10000000001</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10650</v>
+        <v>16230</v>
       </c>
       <c r="M13" t="n">
-        <v>1320</v>
+        <v>5400</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2040</v>
+        <v>2160</v>
       </c>
       <c r="P13" t="n">
-        <v>12810</v>
+        <v>12030</v>
       </c>
       <c r="Q13" t="n">
-        <v>4921.03</v>
+        <v>48245.4</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4770</v>
+        <v>10140</v>
       </c>
       <c r="M14" t="n">
-        <v>570</v>
+        <v>2370</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2430</v>
+        <v>2850</v>
       </c>
       <c r="P14" t="n">
-        <v>15180</v>
+        <v>16140</v>
       </c>
       <c r="Q14" t="n">
-        <v>1541.05</v>
+        <v>15108.3</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1080</v>
+        <v>6690</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="P15" t="n">
-        <v>24090</v>
+        <v>26670</v>
       </c>
       <c r="Q15" t="n">
-        <v>618.27</v>
+        <v>6061.5</v>
       </c>
     </row>
     <row r="16">
@@ -25756,22 +25756,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>330</v>
+        <v>3000</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>720</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>14970</v>
+        <v>20400</v>
       </c>
       <c r="Q16" t="n">
-        <v>242.99</v>
+        <v>2382.3</v>
       </c>
     </row>
     <row r="17">
@@ -25809,22 +25809,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>150</v>
+        <v>1560</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>15240</v>
+        <v>15180</v>
       </c>
       <c r="Q17" t="n">
-        <v>122.37</v>
+        <v>1199.7</v>
       </c>
     </row>
     <row r="18">
@@ -25862,22 +25862,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>240</v>
+        <v>1950</v>
       </c>
       <c r="M18" t="n">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18240</v>
+        <v>25680</v>
       </c>
       <c r="Q18" t="n">
-        <v>118.7</v>
+        <v>1163.7</v>
       </c>
     </row>
     <row r="19">
@@ -25915,10 +25915,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M19" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -25927,10 +25927,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>8970</v>
+        <v>20280</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.02</v>
+        <v>568.8</v>
       </c>
     </row>
     <row r="20">
@@ -25971,7 +25971,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.37</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="21">
@@ -26024,7 +26024,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.38</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="22">
@@ -26077,7 +26077,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="23">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>24500880</v>
+        <v>25424280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>883961.98</v>
       </c>
       <c r="L5" t="n">
-        <v>6751836</v>
+        <v>6295968</v>
       </c>
       <c r="M5" t="n">
-        <v>96600</v>
+        <v>160440</v>
       </c>
       <c r="N5" t="n">
-        <v>28866</v>
+        <v>32742</v>
       </c>
       <c r="O5" t="n">
-        <v>175440</v>
+        <v>182325</v>
       </c>
       <c r="P5" t="n">
-        <v>4368</v>
+        <v>1404</v>
       </c>
       <c r="Q5" t="n">
-        <v>609818.22</v>
+        <v>5978610</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>174717</v>
       </c>
       <c r="H6" t="n">
-        <v>42301980</v>
+        <v>42399450</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1600162.98</v>
       </c>
       <c r="L6" t="n">
-        <v>12357630</v>
+        <v>12207780</v>
       </c>
       <c r="M6" t="n">
-        <v>174720</v>
+        <v>388080</v>
       </c>
       <c r="N6" t="n">
-        <v>69360</v>
+        <v>95370</v>
       </c>
       <c r="O6" t="n">
-        <v>818550</v>
+        <v>832575</v>
       </c>
       <c r="P6" t="n">
-        <v>38902.5</v>
+        <v>19305</v>
       </c>
       <c r="Q6" t="n">
-        <v>11242888.29</v>
+        <v>110224395</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>664119</v>
       </c>
       <c r="H7" t="n">
-        <v>87256170</v>
+        <v>84634740</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -26571,22 +26571,22 @@
         <v>1548936.4</v>
       </c>
       <c r="L7" t="n">
-        <v>25161840</v>
+        <v>24931800</v>
       </c>
       <c r="M7" t="n">
-        <v>606375</v>
+        <v>1716225</v>
       </c>
       <c r="N7" t="n">
-        <v>33201</v>
+        <v>46053</v>
       </c>
       <c r="O7" t="n">
-        <v>1374450</v>
+        <v>1461915</v>
       </c>
       <c r="P7" t="n">
-        <v>89700</v>
+        <v>59475</v>
       </c>
       <c r="Q7" t="n">
-        <v>11991488.83</v>
+        <v>117563616</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>3291678</v>
       </c>
       <c r="H8" t="n">
-        <v>28779300</v>
+        <v>35320050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>2179970.18</v>
       </c>
       <c r="L8" t="n">
-        <v>30913542</v>
+        <v>31879710</v>
       </c>
       <c r="M8" t="n">
-        <v>768075</v>
+        <v>2240700</v>
       </c>
       <c r="N8" t="n">
-        <v>1020</v>
+        <v>3060</v>
       </c>
       <c r="O8" t="n">
-        <v>1565190</v>
+        <v>1652400</v>
       </c>
       <c r="P8" t="n">
-        <v>208962</v>
+        <v>154869</v>
       </c>
       <c r="Q8" t="n">
-        <v>15763050.52</v>
+        <v>154539711</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>4512429</v>
       </c>
       <c r="H9" t="n">
-        <v>4446000</v>
+        <v>7011000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -26677,22 +26677,22 @@
         <v>2300437.61</v>
       </c>
       <c r="L9" t="n">
-        <v>31330962</v>
+        <v>33439230</v>
       </c>
       <c r="M9" t="n">
-        <v>1161300</v>
+        <v>2352000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2058870</v>
+        <v>2294490</v>
       </c>
       <c r="P9" t="n">
-        <v>343200</v>
+        <v>183300</v>
       </c>
       <c r="Q9" t="n">
-        <v>17228637.89</v>
+        <v>168908214.6</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>3408480</v>
       </c>
       <c r="H10" t="n">
-        <v>2394000</v>
+        <v>3249000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>1520773.92</v>
       </c>
       <c r="L10" t="n">
-        <v>20391858</v>
+        <v>23631102</v>
       </c>
       <c r="M10" t="n">
-        <v>1044225</v>
+        <v>2293725</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1542240</v>
+        <v>2484720</v>
       </c>
       <c r="P10" t="n">
-        <v>815490</v>
+        <v>406087.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>15549689.88</v>
+        <v>152447940</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>1812780</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>436275.66</v>
       </c>
       <c r="L11" t="n">
-        <v>12625200</v>
+        <v>15184800</v>
       </c>
       <c r="M11" t="n">
-        <v>850500</v>
+        <v>1710450</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>914685</v>
+        <v>2327895</v>
       </c>
       <c r="P11" t="n">
-        <v>902070</v>
+        <v>891540</v>
       </c>
       <c r="Q11" t="n">
-        <v>10293735.96</v>
+        <v>100918980</v>
       </c>
     </row>
     <row r="12">
@@ -26836,22 +26836,22 @@
         <v>90022.82000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>6409800</v>
+        <v>8321400</v>
       </c>
       <c r="M12" t="n">
-        <v>798000</v>
+        <v>1476300</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>453900</v>
+        <v>693600</v>
       </c>
       <c r="P12" t="n">
-        <v>819000</v>
+        <v>828750</v>
       </c>
       <c r="Q12" t="n">
-        <v>6023493.72</v>
+        <v>59053860</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1917000</v>
+        <v>2921400</v>
       </c>
       <c r="M13" t="n">
-        <v>462000</v>
+        <v>1890000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>346800</v>
+        <v>367200</v>
       </c>
       <c r="P13" t="n">
-        <v>832650</v>
+        <v>781950</v>
       </c>
       <c r="Q13" t="n">
-        <v>2952618.48</v>
+        <v>28947240</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>858600</v>
+        <v>1825200</v>
       </c>
       <c r="M14" t="n">
-        <v>199500</v>
+        <v>829500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>413100</v>
+        <v>484500</v>
       </c>
       <c r="P14" t="n">
-        <v>986700</v>
+        <v>1049100</v>
       </c>
       <c r="Q14" t="n">
-        <v>924627.96</v>
+        <v>9064980</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>194400</v>
+        <v>1204200</v>
       </c>
       <c r="M15" t="n">
-        <v>21000</v>
+        <v>283500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>15300</v>
+        <v>76500</v>
       </c>
       <c r="P15" t="n">
-        <v>1565850</v>
+        <v>1733550</v>
       </c>
       <c r="Q15" t="n">
-        <v>370963.8</v>
+        <v>3636900</v>
       </c>
     </row>
     <row r="16">
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>59400</v>
+        <v>540000</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>252000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>973050</v>
+        <v>1326000</v>
       </c>
       <c r="Q16" t="n">
-        <v>145796.76</v>
+        <v>1429380</v>
       </c>
     </row>
     <row r="17">
@@ -27101,22 +27101,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>27000</v>
+        <v>280800</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>105000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="P17" t="n">
-        <v>990600</v>
+        <v>986700</v>
       </c>
       <c r="Q17" t="n">
-        <v>73421.64</v>
+        <v>719820</v>
       </c>
     </row>
     <row r="18">
@@ -27154,22 +27154,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>43200</v>
+        <v>351000</v>
       </c>
       <c r="M18" t="n">
-        <v>210000</v>
+        <v>231000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P18" t="n">
-        <v>1185600</v>
+        <v>1669200</v>
       </c>
       <c r="Q18" t="n">
-        <v>71218.44</v>
+        <v>698220</v>
       </c>
     </row>
     <row r="19">
@@ -27207,10 +27207,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M19" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -27219,10 +27219,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>583050</v>
+        <v>1318200</v>
       </c>
       <c r="Q19" t="n">
-        <v>34810.56</v>
+        <v>341280</v>
       </c>
     </row>
     <row r="20">
@@ -27263,7 +27263,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>10500</v>
+        <v>31500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q20" t="n">
-        <v>6224.04</v>
+        <v>61020</v>
       </c>
     </row>
     <row r="21">
@@ -27316,7 +27316,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -27328,7 +27328,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>826.2</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="22">
@@ -27369,7 +27369,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>73500</v>
+        <v>115500</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -27381,7 +27381,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4020.84</v>
+        <v>39420</v>
       </c>
     </row>
     <row r="23">
@@ -27692,7 +27692,7 @@
         <v>141120</v>
       </c>
       <c r="H4" t="n">
-        <v>24750</v>
+        <v>24120</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -27704,7 +27704,7 @@
         <v>89</v>
       </c>
       <c r="L4" t="n">
-        <v>401220</v>
+        <v>433830</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>70590</v>
+        <v>67320</v>
       </c>
       <c r="P4" t="n">
-        <v>720</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>42141.54</v>
+        <v>586780.92</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>87810</v>
       </c>
       <c r="H5" t="n">
-        <v>18870</v>
+        <v>20370</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>49</v>
       </c>
       <c r="L5" t="n">
-        <v>216240</v>
+        <v>236220</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>50790</v>
+        <v>52830</v>
       </c>
       <c r="P5" t="n">
-        <v>1050</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>24913.23</v>
+        <v>346893.03</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>53820</v>
       </c>
       <c r="H6" t="n">
-        <v>20970</v>
+        <v>21600</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>19</v>
       </c>
       <c r="L6" t="n">
-        <v>115350</v>
+        <v>123510</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>33180</v>
+        <v>37950</v>
       </c>
       <c r="P6" t="n">
-        <v>2220</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8992.299999999999</v>
+        <v>125209.26</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>19290</v>
       </c>
       <c r="H7" t="n">
-        <v>3210</v>
+        <v>3750</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>46530</v>
+        <v>50640</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>15030</v>
+        <v>18450</v>
       </c>
       <c r="P7" t="n">
-        <v>3150</v>
+        <v>360</v>
       </c>
       <c r="Q7" t="n">
-        <v>4537.96</v>
+        <v>63186.75</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>690</v>
       </c>
       <c r="H8" t="n">
-        <v>510</v>
+        <v>660</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7020</v>
+        <v>8700</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>6300</v>
+        <v>9780</v>
       </c>
       <c r="P8" t="n">
-        <v>4890</v>
+        <v>990</v>
       </c>
       <c r="Q8" t="n">
-        <v>254.68</v>
+        <v>3546.18</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>150</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1740</v>
+        <v>2820</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2730</v>
+        <v>8850</v>
       </c>
       <c r="P9" t="n">
-        <v>5010</v>
+        <v>3540</v>
       </c>
       <c r="Q9" t="n">
-        <v>39.89</v>
+        <v>555.39</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>450</v>
+        <v>2340</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>450</v>
+        <v>2970</v>
       </c>
       <c r="P10" t="n">
-        <v>5820</v>
+        <v>9000</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.2</v>
+        <v>267.3</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>150</v>
+        <v>1740</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P11" t="n">
-        <v>2640</v>
+        <v>6600</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.62</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1800</v>
+        <v>5730</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="13">
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>420</v>
+        <v>1560</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,7 +28246,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>330</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6793.2</v>
+        <v>7333.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>16.22</v>
       </c>
       <c r="L5" t="n">
-        <v>45410.4</v>
+        <v>49606.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2539.5</v>
+        <v>2641.5</v>
       </c>
       <c r="P5" t="n">
-        <v>21</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1245.66</v>
+        <v>17344.65</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2691</v>
       </c>
       <c r="H6" t="n">
-        <v>11952.9</v>
+        <v>12312</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>42679.5</v>
+        <v>45698.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8295</v>
+        <v>9487.5</v>
       </c>
       <c r="P6" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6744.23</v>
+        <v>93906.94</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>2893.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2343.3</v>
+        <v>2737.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>3.19</v>
       </c>
       <c r="L7" t="n">
-        <v>27918</v>
+        <v>30384</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5260.5</v>
+        <v>6457.5</v>
       </c>
       <c r="P7" t="n">
-        <v>787.5</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="n">
-        <v>3630.37</v>
+        <v>50549.4</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>448.5</v>
       </c>
       <c r="H8" t="n">
-        <v>433.5</v>
+        <v>561</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4984.2</v>
+        <v>6177</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2835</v>
+        <v>4401</v>
       </c>
       <c r="P8" t="n">
-        <v>1858.2</v>
+        <v>376.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>241.95</v>
+        <v>3368.87</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>127.5</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1409.4</v>
+        <v>2284.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1501.5</v>
+        <v>4867.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2505</v>
+        <v>1770</v>
       </c>
       <c r="Q9" t="n">
-        <v>38.69</v>
+        <v>538.73</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>400.5</v>
+        <v>2082.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>315</v>
+        <v>2079</v>
       </c>
       <c r="P10" t="n">
-        <v>4947</v>
+        <v>7650</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.2</v>
+        <v>267.3</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>150</v>
+        <v>1740</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="P11" t="n">
-        <v>2376</v>
+        <v>5940</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.62</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1800</v>
+        <v>5730</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="13">
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>420</v>
+        <v>1560</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,7 +29538,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>330</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>38721240</v>
+        <v>41799240</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>787529.76</v>
       </c>
       <c r="L5" t="n">
-        <v>8173872</v>
+        <v>8929116</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>431715</v>
+        <v>449055</v>
       </c>
       <c r="P5" t="n">
-        <v>1365</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>747396.8</v>
+        <v>10406790.9</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>145314</v>
       </c>
       <c r="H6" t="n">
-        <v>68131530</v>
+        <v>70178400</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>467739.95</v>
       </c>
       <c r="L6" t="n">
-        <v>7682310</v>
+        <v>8225766</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1410150</v>
+        <v>1612875</v>
       </c>
       <c r="P6" t="n">
-        <v>21645</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4046535.63</v>
+        <v>56344167</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>156249</v>
       </c>
       <c r="H7" t="n">
-        <v>13356810</v>
+        <v>15603750</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>154893.64</v>
       </c>
       <c r="L7" t="n">
-        <v>5025240</v>
+        <v>5469120</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>894285</v>
+        <v>1097775</v>
       </c>
       <c r="P7" t="n">
-        <v>51187.5</v>
+        <v>5850</v>
       </c>
       <c r="Q7" t="n">
-        <v>2178219.6</v>
+        <v>30329640</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>24219</v>
       </c>
       <c r="H8" t="n">
-        <v>2470950</v>
+        <v>3197700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>897156</v>
+        <v>1111860</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>481950</v>
+        <v>748170</v>
       </c>
       <c r="P8" t="n">
-        <v>120783</v>
+        <v>24453</v>
       </c>
       <c r="Q8" t="n">
-        <v>145167.71</v>
+        <v>2021322.6</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>6885</v>
       </c>
       <c r="H9" t="n">
-        <v>513000</v>
+        <v>1026000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>253692</v>
+        <v>411156</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>255255</v>
+        <v>827475</v>
       </c>
       <c r="P9" t="n">
-        <v>162825</v>
+        <v>115050</v>
       </c>
       <c r="Q9" t="n">
-        <v>23214.29</v>
+        <v>323236.98</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>342000</v>
+        <v>513000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>72090</v>
+        <v>374868</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>53550</v>
+        <v>353430</v>
       </c>
       <c r="P10" t="n">
-        <v>321555</v>
+        <v>497250</v>
       </c>
       <c r="Q10" t="n">
-        <v>11518.2</v>
+        <v>160380</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1539000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>27000</v>
+        <v>313200</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>17340</v>
       </c>
       <c r="P11" t="n">
-        <v>154440</v>
+        <v>386100</v>
       </c>
       <c r="Q11" t="n">
-        <v>2772.9</v>
+        <v>38610</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5400</v>
+        <v>221400</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>117000</v>
+        <v>372450</v>
       </c>
       <c r="Q12" t="n">
-        <v>298.62</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="13">
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>70200</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>27300</v>
+        <v>101400</v>
       </c>
       <c r="Q13" t="n">
-        <v>127.98</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,7 +30830,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1950</v>
+        <v>21450</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
